--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -14685,115 +14685,220 @@
       <c r="A131" s="5" t="n">
         <v>46080</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="8" t="n">
         <v>13232163.74933001</v>
       </c>
-      <c r="C131" t="n">
-        <v>1</v>
-      </c>
-      <c r="D131" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" t="n">
+      <c r="C131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="G131" t="n">
-        <v>1</v>
-      </c>
-      <c r="H131" t="n">
-        <v>1</v>
-      </c>
-      <c r="I131" t="n">
+      <c r="G131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J131" t="n">
-        <v>4</v>
-      </c>
-      <c r="K131" t="n">
-        <v>1</v>
-      </c>
-      <c r="L131" t="n">
-        <v>1</v>
-      </c>
-      <c r="M131" t="n">
-        <v>2</v>
-      </c>
-      <c r="N131" t="n">
-        <v>2</v>
-      </c>
-      <c r="O131" t="n">
-        <v>1</v>
-      </c>
-      <c r="P131" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q131" t="n">
+      <c r="J131" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M131" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N131" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P131" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q131" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="R131" t="n">
-        <v>1</v>
-      </c>
-      <c r="S131" t="n">
+      <c r="R131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S131" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="T131" t="n">
+      <c r="T131" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="U131" t="n">
-        <v>1</v>
-      </c>
-      <c r="V131" t="n">
-        <v>5</v>
-      </c>
-      <c r="W131" t="n">
-        <v>1</v>
-      </c>
-      <c r="X131" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ131" t="n">
+      <c r="U131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V131" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X131" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y131" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z131" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ131" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
         <v>46083</v>
+      </c>
+      <c r="B132" t="n">
+        <v>13416883.74933002</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" t="n">
+        <v>53</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>11</v>
+      </c>
+      <c r="J132" t="n">
+        <v>4</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" t="n">
+        <v>2</v>
+      </c>
+      <c r="N132" t="n">
+        <v>2</v>
+      </c>
+      <c r="O132" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>6</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="n">
+        <v>5</v>
+      </c>
+      <c r="T132" t="n">
+        <v>6</v>
+      </c>
+      <c r="U132" t="n">
+        <v>1</v>
+      </c>
+      <c r="V132" t="n">
+        <v>5</v>
+      </c>
+      <c r="W132" t="n">
+        <v>1</v>
+      </c>
+      <c r="X132" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -14795,115 +14795,220 @@
       <c r="A132" s="5" t="n">
         <v>46083</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="8" t="n">
         <v>13416883.74933002</v>
       </c>
-      <c r="C132" t="n">
-        <v>1</v>
-      </c>
-      <c r="D132" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" t="n">
-        <v>1</v>
-      </c>
-      <c r="F132" t="n">
+      <c r="C132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="G132" t="n">
-        <v>1</v>
-      </c>
-      <c r="H132" t="n">
-        <v>1</v>
-      </c>
-      <c r="I132" t="n">
+      <c r="G132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="J132" t="n">
-        <v>4</v>
-      </c>
-      <c r="K132" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" t="n">
-        <v>1</v>
-      </c>
-      <c r="M132" t="n">
-        <v>2</v>
-      </c>
-      <c r="N132" t="n">
-        <v>2</v>
-      </c>
-      <c r="O132" t="n">
-        <v>1</v>
-      </c>
-      <c r="P132" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q132" t="n">
+      <c r="J132" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M132" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N132" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P132" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q132" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="R132" t="n">
-        <v>1</v>
-      </c>
-      <c r="S132" t="n">
-        <v>5</v>
-      </c>
-      <c r="T132" t="n">
+      <c r="R132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T132" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="U132" t="n">
-        <v>1</v>
-      </c>
-      <c r="V132" t="n">
-        <v>5</v>
-      </c>
-      <c r="W132" t="n">
-        <v>1</v>
-      </c>
-      <c r="X132" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ132" t="n">
+      <c r="U132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V132" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X132" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y132" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z132" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
         <v>46084</v>
+      </c>
+      <c r="B133" t="n">
+        <v>13236197.74933002</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" t="n">
+        <v>54</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" t="n">
+        <v>10</v>
+      </c>
+      <c r="J133" t="n">
+        <v>4</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="n">
+        <v>2</v>
+      </c>
+      <c r="N133" t="n">
+        <v>2</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>6</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="n">
+        <v>5</v>
+      </c>
+      <c r="U133" t="n">
+        <v>1</v>
+      </c>
+      <c r="V133" t="n">
+        <v>5</v>
+      </c>
+      <c r="W133" t="n">
+        <v>1</v>
+      </c>
+      <c r="X133" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -14905,115 +14905,220 @@
       <c r="A133" s="5" t="n">
         <v>46084</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" s="8" t="n">
         <v>13236197.74933002</v>
       </c>
-      <c r="C133" t="n">
-        <v>1</v>
-      </c>
-      <c r="D133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" t="n">
-        <v>1</v>
-      </c>
-      <c r="F133" t="n">
+      <c r="C133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="8" t="n">
         <v>54</v>
       </c>
-      <c r="G133" t="n">
-        <v>1</v>
-      </c>
-      <c r="H133" t="n">
-        <v>1</v>
-      </c>
-      <c r="I133" t="n">
+      <c r="G133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J133" t="n">
-        <v>4</v>
-      </c>
-      <c r="K133" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" t="n">
-        <v>1</v>
-      </c>
-      <c r="M133" t="n">
-        <v>2</v>
-      </c>
-      <c r="N133" t="n">
-        <v>2</v>
-      </c>
-      <c r="O133" t="n">
-        <v>1</v>
-      </c>
-      <c r="P133" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q133" t="n">
+      <c r="J133" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N133" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q133" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="R133" t="n">
-        <v>1</v>
-      </c>
-      <c r="S133" t="n">
-        <v>5</v>
-      </c>
-      <c r="T133" t="n">
-        <v>5</v>
-      </c>
-      <c r="U133" t="n">
-        <v>1</v>
-      </c>
-      <c r="V133" t="n">
-        <v>5</v>
-      </c>
-      <c r="W133" t="n">
-        <v>1</v>
-      </c>
-      <c r="X133" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ133" t="n">
+      <c r="R133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V133" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X133" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y133" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z133" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA133" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF133" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG133" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
         <v>46085</v>
+      </c>
+      <c r="B134" t="n">
+        <v>13275360.18233003</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" t="n">
+        <v>52</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" t="n">
+        <v>10</v>
+      </c>
+      <c r="J134" t="n">
+        <v>4</v>
+      </c>
+      <c r="K134" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" t="n">
+        <v>1</v>
+      </c>
+      <c r="N134" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>6</v>
+      </c>
+      <c r="R134" t="n">
+        <v>1</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="n">
+        <v>5</v>
+      </c>
+      <c r="U134" t="n">
+        <v>1</v>
+      </c>
+      <c r="V134" t="n">
+        <v>5</v>
+      </c>
+      <c r="W134" t="n">
+        <v>1</v>
+      </c>
+      <c r="X134" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -15015,115 +15015,220 @@
       <c r="A134" s="5" t="n">
         <v>46085</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="8" t="n">
         <v>13275360.18233003</v>
       </c>
-      <c r="C134" t="n">
-        <v>1</v>
-      </c>
-      <c r="D134" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" t="n">
-        <v>1</v>
-      </c>
-      <c r="F134" t="n">
+      <c r="C134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="G134" t="n">
-        <v>1</v>
-      </c>
-      <c r="H134" t="n">
-        <v>1</v>
-      </c>
-      <c r="I134" t="n">
+      <c r="G134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J134" t="n">
-        <v>4</v>
-      </c>
-      <c r="K134" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" t="n">
-        <v>1</v>
-      </c>
-      <c r="M134" t="n">
-        <v>1</v>
-      </c>
-      <c r="N134" t="n">
-        <v>2</v>
-      </c>
-      <c r="O134" t="n">
-        <v>1</v>
-      </c>
-      <c r="P134" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q134" t="n">
+      <c r="J134" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N134" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P134" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q134" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="R134" t="n">
-        <v>1</v>
-      </c>
-      <c r="S134" t="n">
-        <v>5</v>
-      </c>
-      <c r="T134" t="n">
-        <v>5</v>
-      </c>
-      <c r="U134" t="n">
-        <v>1</v>
-      </c>
-      <c r="V134" t="n">
-        <v>5</v>
-      </c>
-      <c r="W134" t="n">
-        <v>1</v>
-      </c>
-      <c r="X134" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ134" t="n">
+      <c r="R134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S134" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V134" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X134" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y134" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z134" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB134" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF134" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG134" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ134" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
         <v>46086</v>
+      </c>
+      <c r="B135" t="n">
+        <v>13326676.18233002</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>52</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" t="n">
+        <v>10</v>
+      </c>
+      <c r="J135" t="n">
+        <v>4</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" t="n">
+        <v>2</v>
+      </c>
+      <c r="N135" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" t="n">
+        <v>1</v>
+      </c>
+      <c r="P135" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>6</v>
+      </c>
+      <c r="R135" t="n">
+        <v>1</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="n">
+        <v>5</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1</v>
+      </c>
+      <c r="V135" t="n">
+        <v>5</v>
+      </c>
+      <c r="W135" t="n">
+        <v>1</v>
+      </c>
+      <c r="X135" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -15125,115 +15125,220 @@
       <c r="A135" s="5" t="n">
         <v>46086</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="8" t="n">
         <v>13326676.18233002</v>
       </c>
-      <c r="C135" t="n">
-        <v>1</v>
-      </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F135" t="n">
+      <c r="C135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="G135" t="n">
-        <v>1</v>
-      </c>
-      <c r="H135" t="n">
-        <v>1</v>
-      </c>
-      <c r="I135" t="n">
+      <c r="G135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J135" t="n">
-        <v>4</v>
-      </c>
-      <c r="K135" t="n">
-        <v>1</v>
-      </c>
-      <c r="L135" t="n">
-        <v>1</v>
-      </c>
-      <c r="M135" t="n">
-        <v>2</v>
-      </c>
-      <c r="N135" t="n">
-        <v>2</v>
-      </c>
-      <c r="O135" t="n">
-        <v>1</v>
-      </c>
-      <c r="P135" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q135" t="n">
+      <c r="J135" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M135" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N135" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P135" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q135" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="R135" t="n">
-        <v>1</v>
-      </c>
-      <c r="S135" t="n">
-        <v>5</v>
-      </c>
-      <c r="T135" t="n">
-        <v>5</v>
-      </c>
-      <c r="U135" t="n">
-        <v>1</v>
-      </c>
-      <c r="V135" t="n">
-        <v>5</v>
-      </c>
-      <c r="W135" t="n">
-        <v>1</v>
-      </c>
-      <c r="X135" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ135" t="n">
+      <c r="R135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S135" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V135" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X135" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y135" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z135" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA135" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF135" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG135" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ135" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
         <v>46087</v>
+      </c>
+      <c r="B136" t="n">
+        <v>13386218.68233001</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>53</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" t="n">
+        <v>10</v>
+      </c>
+      <c r="J136" t="n">
+        <v>4</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" t="n">
+        <v>2</v>
+      </c>
+      <c r="N136" t="n">
+        <v>2</v>
+      </c>
+      <c r="O136" t="n">
+        <v>1</v>
+      </c>
+      <c r="P136" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>5</v>
+      </c>
+      <c r="R136" t="n">
+        <v>1</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="n">
+        <v>5</v>
+      </c>
+      <c r="U136" t="n">
+        <v>1</v>
+      </c>
+      <c r="V136" t="n">
+        <v>5</v>
+      </c>
+      <c r="W136" t="n">
+        <v>1</v>
+      </c>
+      <c r="X136" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -15235,115 +15235,220 @@
       <c r="A136" s="5" t="n">
         <v>46087</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="8" t="n">
         <v>13386218.68233001</v>
       </c>
-      <c r="C136" t="n">
-        <v>1</v>
-      </c>
-      <c r="D136" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" t="n">
-        <v>1</v>
-      </c>
-      <c r="F136" t="n">
+      <c r="C136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="8" t="n">
         <v>53</v>
       </c>
-      <c r="G136" t="n">
-        <v>1</v>
-      </c>
-      <c r="H136" t="n">
-        <v>1</v>
-      </c>
-      <c r="I136" t="n">
+      <c r="G136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="J136" t="n">
-        <v>4</v>
-      </c>
-      <c r="K136" t="n">
-        <v>1</v>
-      </c>
-      <c r="L136" t="n">
-        <v>1</v>
-      </c>
-      <c r="M136" t="n">
-        <v>2</v>
-      </c>
-      <c r="N136" t="n">
-        <v>2</v>
-      </c>
-      <c r="O136" t="n">
-        <v>1</v>
-      </c>
-      <c r="P136" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>5</v>
-      </c>
-      <c r="R136" t="n">
-        <v>1</v>
-      </c>
-      <c r="S136" t="n">
-        <v>5</v>
-      </c>
-      <c r="T136" t="n">
-        <v>5</v>
-      </c>
-      <c r="U136" t="n">
-        <v>1</v>
-      </c>
-      <c r="V136" t="n">
-        <v>5</v>
-      </c>
-      <c r="W136" t="n">
-        <v>1</v>
-      </c>
-      <c r="X136" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ136" t="n">
+      <c r="J136" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N136" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P136" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q136" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S136" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V136" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X136" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y136" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z136" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA136" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF136" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG136" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ136" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
         <v>46090</v>
+      </c>
+      <c r="B137" t="n">
+        <v>13404906.90333002</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" t="n">
+        <v>57</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" t="n">
+        <v>9</v>
+      </c>
+      <c r="J137" t="n">
+        <v>4</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" t="n">
+        <v>2</v>
+      </c>
+      <c r="O137" t="n">
+        <v>1</v>
+      </c>
+      <c r="P137" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>5</v>
+      </c>
+      <c r="R137" t="n">
+        <v>1</v>
+      </c>
+      <c r="S137" t="n">
+        <v>4</v>
+      </c>
+      <c r="T137" t="n">
+        <v>5</v>
+      </c>
+      <c r="U137" t="n">
+        <v>1</v>
+      </c>
+      <c r="V137" t="n">
+        <v>5</v>
+      </c>
+      <c r="W137" t="n">
+        <v>1</v>
+      </c>
+      <c r="X137" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -15345,115 +15345,220 @@
       <c r="A137" s="5" t="n">
         <v>46090</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="8" t="n">
         <v>13404906.90333002</v>
       </c>
-      <c r="C137" t="n">
-        <v>1</v>
-      </c>
-      <c r="D137" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" t="n">
-        <v>1</v>
-      </c>
-      <c r="F137" t="n">
+      <c r="C137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G137" t="n">
-        <v>1</v>
-      </c>
-      <c r="H137" t="n">
-        <v>1</v>
-      </c>
-      <c r="I137" t="n">
+      <c r="G137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I137" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J137" t="n">
-        <v>4</v>
-      </c>
-      <c r="K137" t="n">
-        <v>1</v>
-      </c>
-      <c r="L137" t="n">
-        <v>1</v>
-      </c>
-      <c r="M137" t="n">
-        <v>1</v>
-      </c>
-      <c r="N137" t="n">
-        <v>2</v>
-      </c>
-      <c r="O137" t="n">
-        <v>1</v>
-      </c>
-      <c r="P137" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>5</v>
-      </c>
-      <c r="R137" t="n">
-        <v>1</v>
-      </c>
-      <c r="S137" t="n">
-        <v>4</v>
-      </c>
-      <c r="T137" t="n">
-        <v>5</v>
-      </c>
-      <c r="U137" t="n">
-        <v>1</v>
-      </c>
-      <c r="V137" t="n">
-        <v>5</v>
-      </c>
-      <c r="W137" t="n">
-        <v>1</v>
-      </c>
-      <c r="X137" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ137" t="n">
+      <c r="J137" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N137" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P137" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q137" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S137" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T137" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V137" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X137" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y137" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z137" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA137" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF137" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG137" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
         <v>46091</v>
+      </c>
+      <c r="B138" t="n">
+        <v>13361547.78633003</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" t="n">
+        <v>58</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" t="n">
+        <v>9</v>
+      </c>
+      <c r="J138" t="n">
+        <v>3</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" t="n">
+        <v>2</v>
+      </c>
+      <c r="O138" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>5</v>
+      </c>
+      <c r="R138" t="n">
+        <v>1</v>
+      </c>
+      <c r="S138" t="n">
+        <v>4</v>
+      </c>
+      <c r="T138" t="n">
+        <v>5</v>
+      </c>
+      <c r="U138" t="n">
+        <v>1</v>
+      </c>
+      <c r="V138" t="n">
+        <v>5</v>
+      </c>
+      <c r="W138" t="n">
+        <v>1</v>
+      </c>
+      <c r="X138" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -15455,115 +15455,220 @@
       <c r="A138" s="5" t="n">
         <v>46091</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" s="8" t="n">
         <v>13361547.78633003</v>
       </c>
-      <c r="C138" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" t="n">
+      <c r="C138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="G138" t="n">
-        <v>1</v>
-      </c>
-      <c r="H138" t="n">
-        <v>1</v>
-      </c>
-      <c r="I138" t="n">
+      <c r="G138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I138" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J138" t="n">
-        <v>3</v>
-      </c>
-      <c r="K138" t="n">
-        <v>1</v>
-      </c>
-      <c r="L138" t="n">
-        <v>1</v>
-      </c>
-      <c r="M138" t="n">
-        <v>1</v>
-      </c>
-      <c r="N138" t="n">
-        <v>2</v>
-      </c>
-      <c r="O138" t="n">
-        <v>1</v>
-      </c>
-      <c r="P138" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>5</v>
-      </c>
-      <c r="R138" t="n">
-        <v>1</v>
-      </c>
-      <c r="S138" t="n">
-        <v>4</v>
-      </c>
-      <c r="T138" t="n">
-        <v>5</v>
-      </c>
-      <c r="U138" t="n">
-        <v>1</v>
-      </c>
-      <c r="V138" t="n">
-        <v>5</v>
-      </c>
-      <c r="W138" t="n">
-        <v>1</v>
-      </c>
-      <c r="X138" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y138" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z138" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI138" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ138" t="n">
+      <c r="J138" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N138" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P138" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q138" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S138" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T138" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V138" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X138" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y138" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z138" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ138" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
         <v>46092</v>
+      </c>
+      <c r="B139" t="n">
+        <v>13362756.98133003</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="n">
+        <v>57</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>9</v>
+      </c>
+      <c r="J139" t="n">
+        <v>3</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" t="n">
+        <v>2</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>5</v>
+      </c>
+      <c r="R139" t="n">
+        <v>1</v>
+      </c>
+      <c r="S139" t="n">
+        <v>4</v>
+      </c>
+      <c r="T139" t="n">
+        <v>5</v>
+      </c>
+      <c r="U139" t="n">
+        <v>1</v>
+      </c>
+      <c r="V139" t="n">
+        <v>5</v>
+      </c>
+      <c r="W139" t="n">
+        <v>1</v>
+      </c>
+      <c r="X139" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -15565,115 +15565,220 @@
       <c r="A139" s="5" t="n">
         <v>46092</v>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" s="8" t="n">
         <v>13362756.98133003</v>
       </c>
-      <c r="C139" t="n">
-        <v>1</v>
-      </c>
-      <c r="D139" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" t="n">
+      <c r="C139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G139" t="n">
-        <v>1</v>
-      </c>
-      <c r="H139" t="n">
-        <v>1</v>
-      </c>
-      <c r="I139" t="n">
+      <c r="G139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J139" t="n">
-        <v>3</v>
-      </c>
-      <c r="K139" t="n">
-        <v>1</v>
-      </c>
-      <c r="L139" t="n">
-        <v>1</v>
-      </c>
-      <c r="M139" t="n">
-        <v>1</v>
-      </c>
-      <c r="N139" t="n">
-        <v>2</v>
-      </c>
-      <c r="O139" t="n">
-        <v>1</v>
-      </c>
-      <c r="P139" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>5</v>
-      </c>
-      <c r="R139" t="n">
-        <v>1</v>
-      </c>
-      <c r="S139" t="n">
-        <v>4</v>
-      </c>
-      <c r="T139" t="n">
-        <v>5</v>
-      </c>
-      <c r="U139" t="n">
-        <v>1</v>
-      </c>
-      <c r="V139" t="n">
-        <v>5</v>
-      </c>
-      <c r="W139" t="n">
-        <v>1</v>
-      </c>
-      <c r="X139" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y139" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z139" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI139" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ139" t="n">
+      <c r="J139" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P139" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q139" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S139" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T139" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V139" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X139" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y139" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z139" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ139" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
         <v>46093</v>
+      </c>
+      <c r="B140" t="n">
+        <v>13433801.98133002</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" t="n">
+        <v>57</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" t="n">
+        <v>9</v>
+      </c>
+      <c r="J140" t="n">
+        <v>3</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" t="n">
+        <v>2</v>
+      </c>
+      <c r="O140" t="n">
+        <v>1</v>
+      </c>
+      <c r="P140" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>4</v>
+      </c>
+      <c r="R140" t="n">
+        <v>1</v>
+      </c>
+      <c r="S140" t="n">
+        <v>4</v>
+      </c>
+      <c r="T140" t="n">
+        <v>5</v>
+      </c>
+      <c r="U140" t="n">
+        <v>1</v>
+      </c>
+      <c r="V140" t="n">
+        <v>5</v>
+      </c>
+      <c r="W140" t="n">
+        <v>1</v>
+      </c>
+      <c r="X140" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -15675,115 +15675,220 @@
       <c r="A140" s="5" t="n">
         <v>46093</v>
       </c>
-      <c r="B140" t="n">
+      <c r="B140" s="8" t="n">
         <v>13433801.98133002</v>
       </c>
-      <c r="C140" t="n">
-        <v>1</v>
-      </c>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" t="n">
+      <c r="C140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G140" t="n">
-        <v>1</v>
-      </c>
-      <c r="H140" t="n">
-        <v>1</v>
-      </c>
-      <c r="I140" t="n">
+      <c r="G140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I140" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J140" t="n">
-        <v>3</v>
-      </c>
-      <c r="K140" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" t="n">
-        <v>1</v>
-      </c>
-      <c r="M140" t="n">
-        <v>1</v>
-      </c>
-      <c r="N140" t="n">
-        <v>2</v>
-      </c>
-      <c r="O140" t="n">
-        <v>1</v>
-      </c>
-      <c r="P140" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>4</v>
-      </c>
-      <c r="R140" t="n">
-        <v>1</v>
-      </c>
-      <c r="S140" t="n">
-        <v>4</v>
-      </c>
-      <c r="T140" t="n">
-        <v>5</v>
-      </c>
-      <c r="U140" t="n">
-        <v>1</v>
-      </c>
-      <c r="V140" t="n">
-        <v>5</v>
-      </c>
-      <c r="W140" t="n">
-        <v>1</v>
-      </c>
-      <c r="X140" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ140" t="n">
+      <c r="J140" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N140" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P140" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q140" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S140" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T140" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V140" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X140" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y140" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z140" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ140" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
         <v>46094</v>
+      </c>
+      <c r="B141" t="n">
+        <v>13353572.48133002</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" t="n">
+        <v>58</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="n">
+        <v>9</v>
+      </c>
+      <c r="J141" t="n">
+        <v>3</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1</v>
+      </c>
+      <c r="L141" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1</v>
+      </c>
+      <c r="N141" t="n">
+        <v>2</v>
+      </c>
+      <c r="O141" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>4</v>
+      </c>
+      <c r="R141" t="n">
+        <v>1</v>
+      </c>
+      <c r="S141" t="n">
+        <v>4</v>
+      </c>
+      <c r="T141" t="n">
+        <v>5</v>
+      </c>
+      <c r="U141" t="n">
+        <v>1</v>
+      </c>
+      <c r="V141" t="n">
+        <v>5</v>
+      </c>
+      <c r="W141" t="n">
+        <v>1</v>
+      </c>
+      <c r="X141" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -15785,115 +15785,220 @@
       <c r="A141" s="5" t="n">
         <v>46094</v>
       </c>
-      <c r="B141" t="n">
+      <c r="B141" s="8" t="n">
         <v>13353572.48133002</v>
       </c>
-      <c r="C141" t="n">
-        <v>1</v>
-      </c>
-      <c r="D141" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" t="n">
-        <v>1</v>
-      </c>
-      <c r="F141" t="n">
+      <c r="C141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="G141" t="n">
-        <v>1</v>
-      </c>
-      <c r="H141" t="n">
-        <v>1</v>
-      </c>
-      <c r="I141" t="n">
+      <c r="G141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J141" t="n">
-        <v>3</v>
-      </c>
-      <c r="K141" t="n">
-        <v>1</v>
-      </c>
-      <c r="L141" t="n">
-        <v>1</v>
-      </c>
-      <c r="M141" t="n">
-        <v>1</v>
-      </c>
-      <c r="N141" t="n">
-        <v>2</v>
-      </c>
-      <c r="O141" t="n">
-        <v>1</v>
-      </c>
-      <c r="P141" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>4</v>
-      </c>
-      <c r="R141" t="n">
-        <v>1</v>
-      </c>
-      <c r="S141" t="n">
-        <v>4</v>
-      </c>
-      <c r="T141" t="n">
-        <v>5</v>
-      </c>
-      <c r="U141" t="n">
-        <v>1</v>
-      </c>
-      <c r="V141" t="n">
-        <v>5</v>
-      </c>
-      <c r="W141" t="n">
-        <v>1</v>
-      </c>
-      <c r="X141" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y141" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z141" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI141" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ141" t="n">
+      <c r="J141" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N141" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P141" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q141" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S141" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T141" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V141" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X141" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y141" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
         <v>46097</v>
+      </c>
+      <c r="B142" t="n">
+        <v>13280568.48133002</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" t="n">
+        <v>57</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" t="n">
+        <v>9</v>
+      </c>
+      <c r="J142" t="n">
+        <v>3</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" t="n">
+        <v>1</v>
+      </c>
+      <c r="P142" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>5</v>
+      </c>
+      <c r="R142" t="n">
+        <v>1</v>
+      </c>
+      <c r="S142" t="n">
+        <v>4</v>
+      </c>
+      <c r="T142" t="n">
+        <v>5</v>
+      </c>
+      <c r="U142" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" t="n">
+        <v>5</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1</v>
+      </c>
+      <c r="X142" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -15895,115 +15895,220 @@
       <c r="A142" s="5" t="n">
         <v>46097</v>
       </c>
-      <c r="B142" t="n">
+      <c r="B142" s="8" t="n">
         <v>13280568.48133002</v>
       </c>
-      <c r="C142" t="n">
-        <v>1</v>
-      </c>
-      <c r="D142" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" t="n">
+      <c r="C142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G142" t="n">
-        <v>1</v>
-      </c>
-      <c r="H142" t="n">
-        <v>1</v>
-      </c>
-      <c r="I142" t="n">
+      <c r="G142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J142" t="n">
-        <v>3</v>
-      </c>
-      <c r="K142" t="n">
-        <v>1</v>
-      </c>
-      <c r="L142" t="n">
-        <v>1</v>
-      </c>
-      <c r="M142" t="n">
-        <v>1</v>
-      </c>
-      <c r="N142" t="n">
-        <v>2</v>
-      </c>
-      <c r="O142" t="n">
-        <v>1</v>
-      </c>
-      <c r="P142" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>5</v>
-      </c>
-      <c r="R142" t="n">
-        <v>1</v>
-      </c>
-      <c r="S142" t="n">
-        <v>4</v>
-      </c>
-      <c r="T142" t="n">
-        <v>5</v>
-      </c>
-      <c r="U142" t="n">
-        <v>1</v>
-      </c>
-      <c r="V142" t="n">
-        <v>5</v>
-      </c>
-      <c r="W142" t="n">
-        <v>1</v>
-      </c>
-      <c r="X142" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ142" t="n">
+      <c r="J142" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P142" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q142" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S142" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T142" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V142" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X142" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y142" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z142" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ142" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
         <v>46098</v>
+      </c>
+      <c r="B143" t="n">
+        <v>13190170.48133003</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" t="n">
+        <v>57</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" t="n">
+        <v>9</v>
+      </c>
+      <c r="J143" t="n">
+        <v>3</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" t="n">
+        <v>1</v>
+      </c>
+      <c r="P143" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>4</v>
+      </c>
+      <c r="R143" t="n">
+        <v>1</v>
+      </c>
+      <c r="S143" t="n">
+        <v>4</v>
+      </c>
+      <c r="T143" t="n">
+        <v>5</v>
+      </c>
+      <c r="U143" t="n">
+        <v>1</v>
+      </c>
+      <c r="V143" t="n">
+        <v>5</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1</v>
+      </c>
+      <c r="X143" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -16005,115 +16005,220 @@
       <c r="A143" s="5" t="n">
         <v>46098</v>
       </c>
-      <c r="B143" t="n">
+      <c r="B143" s="8" t="n">
         <v>13190170.48133003</v>
       </c>
-      <c r="C143" t="n">
-        <v>1</v>
-      </c>
-      <c r="D143" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" t="n">
-        <v>1</v>
-      </c>
-      <c r="F143" t="n">
+      <c r="C143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G143" t="n">
-        <v>1</v>
-      </c>
-      <c r="H143" t="n">
-        <v>1</v>
-      </c>
-      <c r="I143" t="n">
+      <c r="G143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J143" t="n">
-        <v>3</v>
-      </c>
-      <c r="K143" t="n">
-        <v>1</v>
-      </c>
-      <c r="L143" t="n">
-        <v>1</v>
-      </c>
-      <c r="M143" t="n">
-        <v>1</v>
-      </c>
-      <c r="N143" t="n">
-        <v>2</v>
-      </c>
-      <c r="O143" t="n">
-        <v>1</v>
-      </c>
-      <c r="P143" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>4</v>
-      </c>
-      <c r="R143" t="n">
-        <v>1</v>
-      </c>
-      <c r="S143" t="n">
-        <v>4</v>
-      </c>
-      <c r="T143" t="n">
-        <v>5</v>
-      </c>
-      <c r="U143" t="n">
-        <v>1</v>
-      </c>
-      <c r="V143" t="n">
-        <v>5</v>
-      </c>
-      <c r="W143" t="n">
-        <v>1</v>
-      </c>
-      <c r="X143" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y143" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ143" t="n">
+      <c r="J143" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P143" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q143" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S143" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T143" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V143" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X143" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y143" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z143" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ143" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
         <v>46099</v>
+      </c>
+      <c r="B144" t="n">
+        <v>13235708.48133003</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" t="n">
+        <v>57</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>9</v>
+      </c>
+      <c r="J144" t="n">
+        <v>3</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1</v>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" t="n">
+        <v>1</v>
+      </c>
+      <c r="N144" t="n">
+        <v>2</v>
+      </c>
+      <c r="O144" t="n">
+        <v>1</v>
+      </c>
+      <c r="P144" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>4</v>
+      </c>
+      <c r="R144" t="n">
+        <v>1</v>
+      </c>
+      <c r="S144" t="n">
+        <v>4</v>
+      </c>
+      <c r="T144" t="n">
+        <v>5</v>
+      </c>
+      <c r="U144" t="n">
+        <v>1</v>
+      </c>
+      <c r="V144" t="n">
+        <v>5</v>
+      </c>
+      <c r="W144" t="n">
+        <v>1</v>
+      </c>
+      <c r="X144" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -16115,115 +16115,220 @@
       <c r="A144" s="5" t="n">
         <v>46099</v>
       </c>
-      <c r="B144" t="n">
+      <c r="B144" s="8" t="n">
         <v>13235708.48133003</v>
       </c>
-      <c r="C144" t="n">
-        <v>1</v>
-      </c>
-      <c r="D144" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" t="n">
-        <v>1</v>
-      </c>
-      <c r="F144" t="n">
+      <c r="C144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G144" t="n">
-        <v>1</v>
-      </c>
-      <c r="H144" t="n">
-        <v>1</v>
-      </c>
-      <c r="I144" t="n">
+      <c r="G144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J144" t="n">
-        <v>3</v>
-      </c>
-      <c r="K144" t="n">
-        <v>1</v>
-      </c>
-      <c r="L144" t="n">
-        <v>1</v>
-      </c>
-      <c r="M144" t="n">
-        <v>1</v>
-      </c>
-      <c r="N144" t="n">
-        <v>2</v>
-      </c>
-      <c r="O144" t="n">
-        <v>1</v>
-      </c>
-      <c r="P144" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>4</v>
-      </c>
-      <c r="R144" t="n">
-        <v>1</v>
-      </c>
-      <c r="S144" t="n">
-        <v>4</v>
-      </c>
-      <c r="T144" t="n">
-        <v>5</v>
-      </c>
-      <c r="U144" t="n">
-        <v>1</v>
-      </c>
-      <c r="V144" t="n">
-        <v>5</v>
-      </c>
-      <c r="W144" t="n">
-        <v>1</v>
-      </c>
-      <c r="X144" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y144" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z144" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI144" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ144" t="n">
+      <c r="J144" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N144" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P144" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q144" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S144" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T144" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V144" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X144" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y144" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z144" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ144" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
         <v>46100</v>
+      </c>
+      <c r="B145" t="n">
+        <v>13165188.13381002</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" t="n">
+        <v>58</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" t="n">
+        <v>8</v>
+      </c>
+      <c r="J145" t="n">
+        <v>3</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" t="n">
+        <v>2</v>
+      </c>
+      <c r="O145" t="n">
+        <v>1</v>
+      </c>
+      <c r="P145" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>4</v>
+      </c>
+      <c r="R145" t="n">
+        <v>1</v>
+      </c>
+      <c r="S145" t="n">
+        <v>4</v>
+      </c>
+      <c r="T145" t="n">
+        <v>5</v>
+      </c>
+      <c r="U145" t="n">
+        <v>1</v>
+      </c>
+      <c r="V145" t="n">
+        <v>5</v>
+      </c>
+      <c r="W145" t="n">
+        <v>1</v>
+      </c>
+      <c r="X145" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -16225,115 +16225,220 @@
       <c r="A145" s="5" t="n">
         <v>46100</v>
       </c>
-      <c r="B145" t="n">
+      <c r="B145" s="8" t="n">
         <v>13165188.13381002</v>
       </c>
-      <c r="C145" t="n">
-        <v>1</v>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" t="n">
+      <c r="C145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="G145" t="n">
-        <v>1</v>
-      </c>
-      <c r="H145" t="n">
-        <v>1</v>
-      </c>
-      <c r="I145" t="n">
+      <c r="G145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I145" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J145" t="n">
-        <v>3</v>
-      </c>
-      <c r="K145" t="n">
-        <v>1</v>
-      </c>
-      <c r="L145" t="n">
-        <v>1</v>
-      </c>
-      <c r="M145" t="n">
-        <v>1</v>
-      </c>
-      <c r="N145" t="n">
-        <v>2</v>
-      </c>
-      <c r="O145" t="n">
-        <v>1</v>
-      </c>
-      <c r="P145" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>4</v>
-      </c>
-      <c r="R145" t="n">
-        <v>1</v>
-      </c>
-      <c r="S145" t="n">
-        <v>4</v>
-      </c>
-      <c r="T145" t="n">
-        <v>5</v>
-      </c>
-      <c r="U145" t="n">
-        <v>1</v>
-      </c>
-      <c r="V145" t="n">
-        <v>5</v>
-      </c>
-      <c r="W145" t="n">
-        <v>1</v>
-      </c>
-      <c r="X145" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y145" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI145" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ145" t="n">
+      <c r="J145" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N145" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P145" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q145" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S145" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T145" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V145" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W145" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X145" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y145" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI145" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ145" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
         <v>46101</v>
+      </c>
+      <c r="B146" t="n">
+        <v>12995467.00281003</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>57</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" t="n">
+        <v>8</v>
+      </c>
+      <c r="J146" t="n">
+        <v>3</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1</v>
+      </c>
+      <c r="N146" t="n">
+        <v>2</v>
+      </c>
+      <c r="O146" t="n">
+        <v>1</v>
+      </c>
+      <c r="P146" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>4</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1</v>
+      </c>
+      <c r="S146" t="n">
+        <v>4</v>
+      </c>
+      <c r="T146" t="n">
+        <v>5</v>
+      </c>
+      <c r="U146" t="n">
+        <v>1</v>
+      </c>
+      <c r="V146" t="n">
+        <v>5</v>
+      </c>
+      <c r="W146" t="n">
+        <v>1</v>
+      </c>
+      <c r="X146" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -16335,115 +16335,220 @@
       <c r="A146" s="5" t="n">
         <v>46101</v>
       </c>
-      <c r="B146" t="n">
+      <c r="B146" s="8" t="n">
         <v>12995467.00281003</v>
       </c>
-      <c r="C146" t="n">
-        <v>1</v>
-      </c>
-      <c r="D146" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" t="n">
+      <c r="C146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G146" t="n">
-        <v>1</v>
-      </c>
-      <c r="H146" t="n">
-        <v>1</v>
-      </c>
-      <c r="I146" t="n">
+      <c r="G146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J146" t="n">
-        <v>3</v>
-      </c>
-      <c r="K146" t="n">
-        <v>1</v>
-      </c>
-      <c r="L146" t="n">
-        <v>1</v>
-      </c>
-      <c r="M146" t="n">
-        <v>1</v>
-      </c>
-      <c r="N146" t="n">
-        <v>2</v>
-      </c>
-      <c r="O146" t="n">
-        <v>1</v>
-      </c>
-      <c r="P146" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>4</v>
-      </c>
-      <c r="R146" t="n">
-        <v>1</v>
-      </c>
-      <c r="S146" t="n">
-        <v>4</v>
-      </c>
-      <c r="T146" t="n">
-        <v>5</v>
-      </c>
-      <c r="U146" t="n">
-        <v>1</v>
-      </c>
-      <c r="V146" t="n">
-        <v>5</v>
-      </c>
-      <c r="W146" t="n">
-        <v>1</v>
-      </c>
-      <c r="X146" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y146" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ146" t="n">
+      <c r="J146" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N146" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P146" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q146" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S146" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T146" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V146" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W146" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X146" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y146" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI146" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ146" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
         <v>46104</v>
+      </c>
+      <c r="B147" t="n">
+        <v>12709147.00281002</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>57</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" t="n">
+        <v>8</v>
+      </c>
+      <c r="J147" t="n">
+        <v>3</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="n">
+        <v>1</v>
+      </c>
+      <c r="P147" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>4</v>
+      </c>
+      <c r="R147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="n">
+        <v>4</v>
+      </c>
+      <c r="T147" t="n">
+        <v>5</v>
+      </c>
+      <c r="U147" t="n">
+        <v>1</v>
+      </c>
+      <c r="V147" t="n">
+        <v>5</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1</v>
+      </c>
+      <c r="X147" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -16445,115 +16445,220 @@
       <c r="A147" s="5" t="n">
         <v>46104</v>
       </c>
-      <c r="B147" t="n">
+      <c r="B147" s="8" t="n">
         <v>12709147.00281002</v>
       </c>
-      <c r="C147" t="n">
-        <v>1</v>
-      </c>
-      <c r="D147" t="n">
-        <v>1</v>
-      </c>
-      <c r="E147" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" t="n">
+      <c r="C147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="8" t="n">
         <v>57</v>
       </c>
-      <c r="G147" t="n">
-        <v>1</v>
-      </c>
-      <c r="H147" t="n">
-        <v>1</v>
-      </c>
-      <c r="I147" t="n">
+      <c r="G147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I147" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J147" t="n">
-        <v>3</v>
-      </c>
-      <c r="K147" t="n">
-        <v>1</v>
-      </c>
-      <c r="L147" t="n">
-        <v>1</v>
-      </c>
-      <c r="M147" t="n">
-        <v>1</v>
-      </c>
-      <c r="N147" t="n">
-        <v>1</v>
-      </c>
-      <c r="O147" t="n">
-        <v>1</v>
-      </c>
-      <c r="P147" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>4</v>
-      </c>
-      <c r="R147" t="n">
-        <v>1</v>
-      </c>
-      <c r="S147" t="n">
-        <v>4</v>
-      </c>
-      <c r="T147" t="n">
-        <v>5</v>
-      </c>
-      <c r="U147" t="n">
-        <v>1</v>
-      </c>
-      <c r="V147" t="n">
-        <v>5</v>
-      </c>
-      <c r="W147" t="n">
-        <v>1</v>
-      </c>
-      <c r="X147" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y147" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI147" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ147" t="n">
+      <c r="J147" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P147" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q147" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T147" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V147" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W147" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X147" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y147" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI147" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ147" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
         <v>46105</v>
+      </c>
+      <c r="B148" t="n">
+        <v>12746786.50281003</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>56</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" t="n">
+        <v>8</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>2</v>
+      </c>
+      <c r="O148" t="n">
+        <v>1</v>
+      </c>
+      <c r="P148" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>4</v>
+      </c>
+      <c r="R148" t="n">
+        <v>1</v>
+      </c>
+      <c r="S148" t="n">
+        <v>4</v>
+      </c>
+      <c r="T148" t="n">
+        <v>5</v>
+      </c>
+      <c r="U148" t="n">
+        <v>1</v>
+      </c>
+      <c r="V148" t="n">
+        <v>5</v>
+      </c>
+      <c r="W148" t="n">
+        <v>1</v>
+      </c>
+      <c r="X148" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -16555,115 +16555,220 @@
       <c r="A148" s="5" t="n">
         <v>46105</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B148" s="8" t="n">
         <v>12746786.50281003</v>
       </c>
-      <c r="C148" t="n">
-        <v>1</v>
-      </c>
-      <c r="D148" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" t="n">
+      <c r="C148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="G148" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" t="n">
-        <v>1</v>
-      </c>
-      <c r="I148" t="n">
+      <c r="G148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J148" t="n">
-        <v>3</v>
-      </c>
-      <c r="K148" t="n">
-        <v>1</v>
-      </c>
-      <c r="L148" t="n">
-        <v>1</v>
-      </c>
-      <c r="M148" t="n">
-        <v>1</v>
-      </c>
-      <c r="N148" t="n">
-        <v>2</v>
-      </c>
-      <c r="O148" t="n">
-        <v>1</v>
-      </c>
-      <c r="P148" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>4</v>
-      </c>
-      <c r="R148" t="n">
-        <v>1</v>
-      </c>
-      <c r="S148" t="n">
-        <v>4</v>
-      </c>
-      <c r="T148" t="n">
-        <v>5</v>
-      </c>
-      <c r="U148" t="n">
-        <v>1</v>
-      </c>
-      <c r="V148" t="n">
-        <v>5</v>
-      </c>
-      <c r="W148" t="n">
-        <v>1</v>
-      </c>
-      <c r="X148" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y148" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ148" t="n">
+      <c r="J148" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P148" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q148" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S148" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T148" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V148" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W148" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X148" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y148" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI148" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ148" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
         <v>46106</v>
+      </c>
+      <c r="B149" t="n">
+        <v>12830872.00281002</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>56</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" t="n">
+        <v>8</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>2</v>
+      </c>
+      <c r="O149" t="n">
+        <v>1</v>
+      </c>
+      <c r="P149" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>4</v>
+      </c>
+      <c r="R149" t="n">
+        <v>1</v>
+      </c>
+      <c r="S149" t="n">
+        <v>4</v>
+      </c>
+      <c r="T149" t="n">
+        <v>5</v>
+      </c>
+      <c r="U149" t="n">
+        <v>1</v>
+      </c>
+      <c r="V149" t="n">
+        <v>5</v>
+      </c>
+      <c r="W149" t="n">
+        <v>1</v>
+      </c>
+      <c r="X149" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -16665,115 +16665,220 @@
       <c r="A149" s="5" t="n">
         <v>46106</v>
       </c>
-      <c r="B149" t="n">
+      <c r="B149" s="8" t="n">
         <v>12830872.00281002</v>
       </c>
-      <c r="C149" t="n">
-        <v>1</v>
-      </c>
-      <c r="D149" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" t="n">
+      <c r="C149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="8" t="n">
         <v>56</v>
       </c>
-      <c r="G149" t="n">
-        <v>1</v>
-      </c>
-      <c r="H149" t="n">
-        <v>1</v>
-      </c>
-      <c r="I149" t="n">
+      <c r="G149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J149" t="n">
-        <v>3</v>
-      </c>
-      <c r="K149" t="n">
-        <v>1</v>
-      </c>
-      <c r="L149" t="n">
-        <v>1</v>
-      </c>
-      <c r="M149" t="n">
-        <v>1</v>
-      </c>
-      <c r="N149" t="n">
-        <v>2</v>
-      </c>
-      <c r="O149" t="n">
-        <v>1</v>
-      </c>
-      <c r="P149" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>4</v>
-      </c>
-      <c r="R149" t="n">
-        <v>1</v>
-      </c>
-      <c r="S149" t="n">
-        <v>4</v>
-      </c>
-      <c r="T149" t="n">
-        <v>5</v>
-      </c>
-      <c r="U149" t="n">
-        <v>1</v>
-      </c>
-      <c r="V149" t="n">
-        <v>5</v>
-      </c>
-      <c r="W149" t="n">
-        <v>1</v>
-      </c>
-      <c r="X149" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y149" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI149" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ149" t="n">
+      <c r="J149" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N149" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P149" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q149" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S149" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T149" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V149" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W149" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X149" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y149" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI149" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ149" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
         <v>46107</v>
+      </c>
+      <c r="B150" t="n">
+        <v>12816386.00281002</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>58</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="n">
+        <v>8</v>
+      </c>
+      <c r="J150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" t="n">
+        <v>1</v>
+      </c>
+      <c r="N150" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" t="n">
+        <v>1</v>
+      </c>
+      <c r="P150" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>5</v>
+      </c>
+      <c r="R150" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" t="n">
+        <v>4</v>
+      </c>
+      <c r="T150" t="n">
+        <v>5</v>
+      </c>
+      <c r="U150" t="n">
+        <v>1</v>
+      </c>
+      <c r="V150" t="n">
+        <v>5</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1</v>
+      </c>
+      <c r="X150" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -16775,115 +16775,220 @@
       <c r="A150" s="5" t="n">
         <v>46107</v>
       </c>
-      <c r="B150" t="n">
+      <c r="B150" s="8" t="n">
         <v>12816386.00281002</v>
       </c>
-      <c r="C150" t="n">
-        <v>1</v>
-      </c>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" t="n">
-        <v>1</v>
-      </c>
-      <c r="F150" t="n">
+      <c r="C150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" s="8" t="n">
         <v>58</v>
       </c>
-      <c r="G150" t="n">
-        <v>1</v>
-      </c>
-      <c r="H150" t="n">
-        <v>1</v>
-      </c>
-      <c r="I150" t="n">
+      <c r="G150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J150" t="n">
-        <v>3</v>
-      </c>
-      <c r="K150" t="n">
-        <v>1</v>
-      </c>
-      <c r="L150" t="n">
-        <v>1</v>
-      </c>
-      <c r="M150" t="n">
-        <v>1</v>
-      </c>
-      <c r="N150" t="n">
-        <v>2</v>
-      </c>
-      <c r="O150" t="n">
-        <v>1</v>
-      </c>
-      <c r="P150" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>5</v>
-      </c>
-      <c r="R150" t="n">
-        <v>1</v>
-      </c>
-      <c r="S150" t="n">
-        <v>4</v>
-      </c>
-      <c r="T150" t="n">
-        <v>5</v>
-      </c>
-      <c r="U150" t="n">
-        <v>1</v>
-      </c>
-      <c r="V150" t="n">
-        <v>5</v>
-      </c>
-      <c r="W150" t="n">
-        <v>1</v>
-      </c>
-      <c r="X150" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ150" t="n">
+      <c r="J150" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N150" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P150" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q150" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S150" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T150" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V150" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W150" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X150" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y150" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI150" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ150" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
         <v>46108</v>
+      </c>
+      <c r="B151" t="n">
+        <v>12905709.00281002</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>61</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" t="n">
+        <v>8</v>
+      </c>
+      <c r="J151" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="n">
+        <v>1</v>
+      </c>
+      <c r="N151" t="n">
+        <v>2</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1</v>
+      </c>
+      <c r="P151" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>4</v>
+      </c>
+      <c r="R151" t="n">
+        <v>1</v>
+      </c>
+      <c r="S151" t="n">
+        <v>4</v>
+      </c>
+      <c r="T151" t="n">
+        <v>5</v>
+      </c>
+      <c r="U151" t="n">
+        <v>1</v>
+      </c>
+      <c r="V151" t="n">
+        <v>5</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1</v>
+      </c>
+      <c r="X151" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="152">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -16885,115 +16885,220 @@
       <c r="A151" s="5" t="n">
         <v>46108</v>
       </c>
-      <c r="B151" t="n">
+      <c r="B151" s="8" t="n">
         <v>12905709.00281002</v>
       </c>
-      <c r="C151" t="n">
-        <v>1</v>
-      </c>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" t="n">
+      <c r="C151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="G151" t="n">
-        <v>1</v>
-      </c>
-      <c r="H151" t="n">
-        <v>1</v>
-      </c>
-      <c r="I151" t="n">
+      <c r="G151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J151" t="n">
-        <v>3</v>
-      </c>
-      <c r="K151" t="n">
-        <v>1</v>
-      </c>
-      <c r="L151" t="n">
-        <v>1</v>
-      </c>
-      <c r="M151" t="n">
-        <v>1</v>
-      </c>
-      <c r="N151" t="n">
-        <v>2</v>
-      </c>
-      <c r="O151" t="n">
-        <v>1</v>
-      </c>
-      <c r="P151" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>4</v>
-      </c>
-      <c r="R151" t="n">
-        <v>1</v>
-      </c>
-      <c r="S151" t="n">
-        <v>4</v>
-      </c>
-      <c r="T151" t="n">
-        <v>5</v>
-      </c>
-      <c r="U151" t="n">
-        <v>1</v>
-      </c>
-      <c r="V151" t="n">
-        <v>5</v>
-      </c>
-      <c r="W151" t="n">
-        <v>1</v>
-      </c>
-      <c r="X151" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y151" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI151" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ151" t="n">
+      <c r="J151" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N151" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P151" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q151" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S151" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T151" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V151" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W151" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X151" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y151" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
         <v>46111</v>
+      </c>
+      <c r="B152" t="n">
+        <v>13042143.50281002</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" t="n">
+        <v>62</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" t="n">
+        <v>8</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="n">
+        <v>1</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1</v>
+      </c>
+      <c r="N152" t="n">
+        <v>2</v>
+      </c>
+      <c r="O152" t="n">
+        <v>1</v>
+      </c>
+      <c r="P152" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>5</v>
+      </c>
+      <c r="R152" t="n">
+        <v>1</v>
+      </c>
+      <c r="S152" t="n">
+        <v>4</v>
+      </c>
+      <c r="T152" t="n">
+        <v>5</v>
+      </c>
+      <c r="U152" t="n">
+        <v>1</v>
+      </c>
+      <c r="V152" t="n">
+        <v>5</v>
+      </c>
+      <c r="W152" t="n">
+        <v>1</v>
+      </c>
+      <c r="X152" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -16995,115 +16995,220 @@
       <c r="A152" s="5" t="n">
         <v>46111</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B152" s="8" t="n">
         <v>13042143.50281002</v>
       </c>
-      <c r="C152" t="n">
-        <v>1</v>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" t="n">
-        <v>1</v>
-      </c>
-      <c r="F152" t="n">
+      <c r="C152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="G152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" t="n">
-        <v>1</v>
-      </c>
-      <c r="I152" t="n">
+      <c r="G152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J152" t="n">
-        <v>3</v>
-      </c>
-      <c r="K152" t="n">
-        <v>1</v>
-      </c>
-      <c r="L152" t="n">
-        <v>1</v>
-      </c>
-      <c r="M152" t="n">
-        <v>1</v>
-      </c>
-      <c r="N152" t="n">
-        <v>2</v>
-      </c>
-      <c r="O152" t="n">
-        <v>1</v>
-      </c>
-      <c r="P152" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>5</v>
-      </c>
-      <c r="R152" t="n">
-        <v>1</v>
-      </c>
-      <c r="S152" t="n">
-        <v>4</v>
-      </c>
-      <c r="T152" t="n">
-        <v>5</v>
-      </c>
-      <c r="U152" t="n">
-        <v>1</v>
-      </c>
-      <c r="V152" t="n">
-        <v>5</v>
-      </c>
-      <c r="W152" t="n">
-        <v>1</v>
-      </c>
-      <c r="X152" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y152" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI152" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ152" t="n">
+      <c r="J152" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N152" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P152" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q152" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S152" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T152" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V152" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W152" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X152" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y152" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI152" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ152" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
         <v>46112</v>
+      </c>
+      <c r="B153" t="n">
+        <v>12945582.50281002</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" t="n">
+        <v>60</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" t="n">
+        <v>8</v>
+      </c>
+      <c r="J153" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" t="n">
+        <v>1</v>
+      </c>
+      <c r="P153" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>5</v>
+      </c>
+      <c r="R153" t="n">
+        <v>1</v>
+      </c>
+      <c r="S153" t="n">
+        <v>4</v>
+      </c>
+      <c r="T153" t="n">
+        <v>5</v>
+      </c>
+      <c r="U153" t="n">
+        <v>1</v>
+      </c>
+      <c r="V153" t="n">
+        <v>5</v>
+      </c>
+      <c r="W153" t="n">
+        <v>1</v>
+      </c>
+      <c r="X153" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -17105,115 +17105,220 @@
       <c r="A153" s="5" t="n">
         <v>46112</v>
       </c>
-      <c r="B153" t="n">
+      <c r="B153" s="8" t="n">
         <v>12945582.50281002</v>
       </c>
-      <c r="C153" t="n">
-        <v>1</v>
-      </c>
-      <c r="D153" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" t="n">
-        <v>1</v>
-      </c>
-      <c r="F153" t="n">
+      <c r="C153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G153" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" t="n">
-        <v>1</v>
-      </c>
-      <c r="I153" t="n">
+      <c r="G153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J153" t="n">
-        <v>3</v>
-      </c>
-      <c r="K153" t="n">
-        <v>1</v>
-      </c>
-      <c r="L153" t="n">
-        <v>1</v>
-      </c>
-      <c r="M153" t="n">
-        <v>1</v>
-      </c>
-      <c r="N153" t="n">
-        <v>1</v>
-      </c>
-      <c r="O153" t="n">
-        <v>1</v>
-      </c>
-      <c r="P153" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>5</v>
-      </c>
-      <c r="R153" t="n">
-        <v>1</v>
-      </c>
-      <c r="S153" t="n">
-        <v>4</v>
-      </c>
-      <c r="T153" t="n">
-        <v>5</v>
-      </c>
-      <c r="U153" t="n">
-        <v>1</v>
-      </c>
-      <c r="V153" t="n">
-        <v>5</v>
-      </c>
-      <c r="W153" t="n">
-        <v>1</v>
-      </c>
-      <c r="X153" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y153" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI153" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ153" t="n">
+      <c r="J153" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P153" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q153" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S153" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T153" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V153" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W153" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X153" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y153" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI153" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ153" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
         <v>46113</v>
+      </c>
+      <c r="B154" t="n">
+        <v>12848605.00281002</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" t="n">
+        <v>60</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" t="n">
+        <v>8</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>1</v>
+      </c>
+      <c r="N154" t="n">
+        <v>1</v>
+      </c>
+      <c r="O154" t="n">
+        <v>1</v>
+      </c>
+      <c r="P154" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>4</v>
+      </c>
+      <c r="R154" t="n">
+        <v>1</v>
+      </c>
+      <c r="S154" t="n">
+        <v>4</v>
+      </c>
+      <c r="T154" t="n">
+        <v>5</v>
+      </c>
+      <c r="U154" t="n">
+        <v>1</v>
+      </c>
+      <c r="V154" t="n">
+        <v>5</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1</v>
+      </c>
+      <c r="X154" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="155">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -17215,115 +17215,220 @@
       <c r="A154" s="5" t="n">
         <v>46113</v>
       </c>
-      <c r="B154" t="n">
+      <c r="B154" s="8" t="n">
         <v>12848605.00281002</v>
       </c>
-      <c r="C154" t="n">
-        <v>1</v>
-      </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="n">
-        <v>1</v>
-      </c>
-      <c r="F154" t="n">
+      <c r="C154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="G154" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" t="n">
-        <v>1</v>
-      </c>
-      <c r="I154" t="n">
+      <c r="G154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J154" t="n">
-        <v>3</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0</v>
-      </c>
-      <c r="L154" t="n">
-        <v>1</v>
-      </c>
-      <c r="M154" t="n">
-        <v>1</v>
-      </c>
-      <c r="N154" t="n">
-        <v>1</v>
-      </c>
-      <c r="O154" t="n">
-        <v>1</v>
-      </c>
-      <c r="P154" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>4</v>
-      </c>
-      <c r="R154" t="n">
-        <v>1</v>
-      </c>
-      <c r="S154" t="n">
-        <v>4</v>
-      </c>
-      <c r="T154" t="n">
-        <v>5</v>
-      </c>
-      <c r="U154" t="n">
-        <v>1</v>
-      </c>
-      <c r="V154" t="n">
-        <v>5</v>
-      </c>
-      <c r="W154" t="n">
-        <v>1</v>
-      </c>
-      <c r="X154" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y154" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI154" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ154" t="n">
+      <c r="J154" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P154" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q154" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S154" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T154" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V154" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W154" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X154" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y154" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI154" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ154" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
         <v>46114</v>
+      </c>
+      <c r="B155" t="n">
+        <v>12809669.23281003</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" t="n">
+        <v>62</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" t="n">
+        <v>8</v>
+      </c>
+      <c r="J155" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" t="n">
+        <v>1</v>
+      </c>
+      <c r="P155" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>4</v>
+      </c>
+      <c r="R155" t="n">
+        <v>1</v>
+      </c>
+      <c r="S155" t="n">
+        <v>4</v>
+      </c>
+      <c r="T155" t="n">
+        <v>5</v>
+      </c>
+      <c r="U155" t="n">
+        <v>1</v>
+      </c>
+      <c r="V155" t="n">
+        <v>5</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1</v>
+      </c>
+      <c r="X155" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -17325,109 +17325,109 @@
       <c r="A155" s="5" t="n">
         <v>46114</v>
       </c>
-      <c r="B155" t="n">
+      <c r="B155" s="8" t="n">
         <v>12809669.23281003</v>
       </c>
-      <c r="C155" t="n">
-        <v>1</v>
-      </c>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" t="n">
-        <v>1</v>
-      </c>
-      <c r="F155" t="n">
+      <c r="C155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="G155" t="n">
-        <v>1</v>
-      </c>
-      <c r="H155" t="n">
-        <v>1</v>
-      </c>
-      <c r="I155" t="n">
+      <c r="G155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J155" t="n">
-        <v>3</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M155" t="n">
-        <v>1</v>
-      </c>
-      <c r="N155" t="n">
-        <v>1</v>
-      </c>
-      <c r="O155" t="n">
-        <v>1</v>
-      </c>
-      <c r="P155" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>4</v>
-      </c>
-      <c r="R155" t="n">
-        <v>1</v>
-      </c>
-      <c r="S155" t="n">
-        <v>4</v>
-      </c>
-      <c r="T155" t="n">
-        <v>5</v>
-      </c>
-      <c r="U155" t="n">
-        <v>1</v>
-      </c>
-      <c r="V155" t="n">
-        <v>5</v>
-      </c>
-      <c r="W155" t="n">
-        <v>1</v>
-      </c>
-      <c r="X155" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ155" t="n">
+      <c r="J155" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q155" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S155" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T155" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V155" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W155" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X155" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y155" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI155" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ155" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17439,6 +17439,111 @@
     <row r="157">
       <c r="A157" s="5" t="n">
         <v>46119</v>
+      </c>
+      <c r="B157" t="n">
+        <v>12867513.67531002</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" t="n">
+        <v>61</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" t="n">
+        <v>8</v>
+      </c>
+      <c r="J157" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1</v>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" t="n">
+        <v>1</v>
+      </c>
+      <c r="O157" t="n">
+        <v>1</v>
+      </c>
+      <c r="P157" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>4</v>
+      </c>
+      <c r="R157" t="n">
+        <v>1</v>
+      </c>
+      <c r="S157" t="n">
+        <v>4</v>
+      </c>
+      <c r="T157" t="n">
+        <v>5</v>
+      </c>
+      <c r="U157" t="n">
+        <v>1</v>
+      </c>
+      <c r="V157" t="n">
+        <v>5</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1</v>
+      </c>
+      <c r="X157" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -17440,115 +17440,220 @@
       <c r="A157" s="5" t="n">
         <v>46119</v>
       </c>
-      <c r="B157" t="n">
+      <c r="B157" s="8" t="n">
         <v>12867513.67531002</v>
       </c>
-      <c r="C157" t="n">
-        <v>1</v>
-      </c>
-      <c r="D157" t="n">
-        <v>1</v>
-      </c>
-      <c r="E157" t="n">
-        <v>1</v>
-      </c>
-      <c r="F157" t="n">
+      <c r="C157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" s="8" t="n">
         <v>61</v>
       </c>
-      <c r="G157" t="n">
-        <v>1</v>
-      </c>
-      <c r="H157" t="n">
-        <v>1</v>
-      </c>
-      <c r="I157" t="n">
+      <c r="G157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J157" t="n">
-        <v>3</v>
-      </c>
-      <c r="K157" t="n">
-        <v>1</v>
-      </c>
-      <c r="L157" t="n">
-        <v>1</v>
-      </c>
-      <c r="M157" t="n">
-        <v>1</v>
-      </c>
-      <c r="N157" t="n">
-        <v>1</v>
-      </c>
-      <c r="O157" t="n">
-        <v>1</v>
-      </c>
-      <c r="P157" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>4</v>
-      </c>
-      <c r="R157" t="n">
-        <v>1</v>
-      </c>
-      <c r="S157" t="n">
-        <v>4</v>
-      </c>
-      <c r="T157" t="n">
-        <v>5</v>
-      </c>
-      <c r="U157" t="n">
-        <v>1</v>
-      </c>
-      <c r="V157" t="n">
-        <v>5</v>
-      </c>
-      <c r="W157" t="n">
-        <v>1</v>
-      </c>
-      <c r="X157" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y157" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ157" t="n">
+      <c r="J157" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P157" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q157" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S157" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T157" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V157" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W157" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X157" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y157" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n">
         <v>46120</v>
+      </c>
+      <c r="B158" t="n">
+        <v>13026878.91531002</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>64</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" t="n">
+        <v>8</v>
+      </c>
+      <c r="J158" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="n">
+        <v>1</v>
+      </c>
+      <c r="P158" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>4</v>
+      </c>
+      <c r="R158" t="n">
+        <v>1</v>
+      </c>
+      <c r="S158" t="n">
+        <v>4</v>
+      </c>
+      <c r="T158" t="n">
+        <v>5</v>
+      </c>
+      <c r="U158" t="n">
+        <v>1</v>
+      </c>
+      <c r="V158" t="n">
+        <v>5</v>
+      </c>
+      <c r="W158" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -17550,115 +17550,220 @@
       <c r="A158" s="5" t="n">
         <v>46120</v>
       </c>
-      <c r="B158" t="n">
+      <c r="B158" s="8" t="n">
         <v>13026878.91531002</v>
       </c>
-      <c r="C158" t="n">
-        <v>1</v>
-      </c>
-      <c r="D158" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" t="n">
-        <v>1</v>
-      </c>
-      <c r="F158" t="n">
+      <c r="C158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="G158" t="n">
-        <v>1</v>
-      </c>
-      <c r="H158" t="n">
-        <v>1</v>
-      </c>
-      <c r="I158" t="n">
+      <c r="G158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J158" t="n">
-        <v>3</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" t="n">
-        <v>1</v>
-      </c>
-      <c r="M158" t="n">
-        <v>1</v>
-      </c>
-      <c r="N158" t="n">
-        <v>1</v>
-      </c>
-      <c r="O158" t="n">
-        <v>1</v>
-      </c>
-      <c r="P158" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>4</v>
-      </c>
-      <c r="R158" t="n">
-        <v>1</v>
-      </c>
-      <c r="S158" t="n">
-        <v>4</v>
-      </c>
-      <c r="T158" t="n">
-        <v>5</v>
-      </c>
-      <c r="U158" t="n">
-        <v>1</v>
-      </c>
-      <c r="V158" t="n">
-        <v>5</v>
-      </c>
-      <c r="W158" t="n">
-        <v>0</v>
-      </c>
-      <c r="X158" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y158" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ158" t="n">
+      <c r="J158" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P158" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q158" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S158" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T158" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V158" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X158" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y158" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
         <v>46121</v>
+      </c>
+      <c r="B159" t="n">
+        <v>12946065.45431002</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>64</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" t="n">
+        <v>8</v>
+      </c>
+      <c r="J159" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>1</v>
+      </c>
+      <c r="P159" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>4</v>
+      </c>
+      <c r="R159" t="n">
+        <v>1</v>
+      </c>
+      <c r="S159" t="n">
+        <v>4</v>
+      </c>
+      <c r="T159" t="n">
+        <v>5</v>
+      </c>
+      <c r="U159" t="n">
+        <v>1</v>
+      </c>
+      <c r="V159" t="n">
+        <v>5</v>
+      </c>
+      <c r="W159" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -17660,115 +17660,220 @@
       <c r="A159" s="5" t="n">
         <v>46121</v>
       </c>
-      <c r="B159" t="n">
+      <c r="B159" s="8" t="n">
         <v>12946065.45431002</v>
       </c>
-      <c r="C159" t="n">
-        <v>1</v>
-      </c>
-      <c r="D159" t="n">
-        <v>1</v>
-      </c>
-      <c r="E159" t="n">
-        <v>1</v>
-      </c>
-      <c r="F159" t="n">
+      <c r="C159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="G159" t="n">
-        <v>1</v>
-      </c>
-      <c r="H159" t="n">
-        <v>1</v>
-      </c>
-      <c r="I159" t="n">
+      <c r="G159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J159" t="n">
-        <v>3</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0</v>
-      </c>
-      <c r="L159" t="n">
-        <v>1</v>
-      </c>
-      <c r="M159" t="n">
-        <v>1</v>
-      </c>
-      <c r="N159" t="n">
-        <v>1</v>
-      </c>
-      <c r="O159" t="n">
-        <v>1</v>
-      </c>
-      <c r="P159" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>4</v>
-      </c>
-      <c r="R159" t="n">
-        <v>1</v>
-      </c>
-      <c r="S159" t="n">
-        <v>4</v>
-      </c>
-      <c r="T159" t="n">
-        <v>5</v>
-      </c>
-      <c r="U159" t="n">
-        <v>1</v>
-      </c>
-      <c r="V159" t="n">
-        <v>5</v>
-      </c>
-      <c r="W159" t="n">
-        <v>0</v>
-      </c>
-      <c r="X159" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y159" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI159" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ159" t="n">
+      <c r="J159" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P159" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q159" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S159" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T159" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U159" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V159" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X159" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y159" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI159" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ159" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
         <v>46122</v>
+      </c>
+      <c r="B160" t="n">
+        <v>12974682.45431002</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>65</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" t="n">
+        <v>8</v>
+      </c>
+      <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>1</v>
+      </c>
+      <c r="N160" t="n">
+        <v>2</v>
+      </c>
+      <c r="O160" t="n">
+        <v>1</v>
+      </c>
+      <c r="P160" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>4</v>
+      </c>
+      <c r="R160" t="n">
+        <v>1</v>
+      </c>
+      <c r="S160" t="n">
+        <v>4</v>
+      </c>
+      <c r="T160" t="n">
+        <v>5</v>
+      </c>
+      <c r="U160" t="n">
+        <v>1</v>
+      </c>
+      <c r="V160" t="n">
+        <v>5</v>
+      </c>
+      <c r="W160" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="161">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -17770,115 +17770,220 @@
       <c r="A160" s="5" t="n">
         <v>46122</v>
       </c>
-      <c r="B160" t="n">
+      <c r="B160" s="8" t="n">
         <v>12974682.45431002</v>
       </c>
-      <c r="C160" t="n">
-        <v>1</v>
-      </c>
-      <c r="D160" t="n">
-        <v>1</v>
-      </c>
-      <c r="E160" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" t="n">
+      <c r="C160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="G160" t="n">
-        <v>1</v>
-      </c>
-      <c r="H160" t="n">
-        <v>1</v>
-      </c>
-      <c r="I160" t="n">
+      <c r="G160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J160" t="n">
-        <v>3</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0</v>
-      </c>
-      <c r="L160" t="n">
-        <v>1</v>
-      </c>
-      <c r="M160" t="n">
-        <v>1</v>
-      </c>
-      <c r="N160" t="n">
-        <v>2</v>
-      </c>
-      <c r="O160" t="n">
-        <v>1</v>
-      </c>
-      <c r="P160" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>4</v>
-      </c>
-      <c r="R160" t="n">
-        <v>1</v>
-      </c>
-      <c r="S160" t="n">
-        <v>4</v>
-      </c>
-      <c r="T160" t="n">
-        <v>5</v>
-      </c>
-      <c r="U160" t="n">
-        <v>1</v>
-      </c>
-      <c r="V160" t="n">
-        <v>5</v>
-      </c>
-      <c r="W160" t="n">
-        <v>0</v>
-      </c>
-      <c r="X160" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y160" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI160" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ160" t="n">
+      <c r="J160" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N160" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P160" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q160" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S160" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T160" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U160" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V160" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X160" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y160" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI160" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ160" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
         <v>46125</v>
+      </c>
+      <c r="B161" t="n">
+        <v>13063554.95431002</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>65</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="n">
+        <v>1</v>
+      </c>
+      <c r="I161" t="n">
+        <v>8</v>
+      </c>
+      <c r="J161" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>1</v>
+      </c>
+      <c r="N161" t="n">
+        <v>2</v>
+      </c>
+      <c r="O161" t="n">
+        <v>1</v>
+      </c>
+      <c r="P161" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>4</v>
+      </c>
+      <c r="R161" t="n">
+        <v>1</v>
+      </c>
+      <c r="S161" t="n">
+        <v>4</v>
+      </c>
+      <c r="T161" t="n">
+        <v>5</v>
+      </c>
+      <c r="U161" t="n">
+        <v>1</v>
+      </c>
+      <c r="V161" t="n">
+        <v>5</v>
+      </c>
+      <c r="W161" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="162">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -17880,115 +17880,220 @@
       <c r="A161" s="5" t="n">
         <v>46125</v>
       </c>
-      <c r="B161" t="n">
+      <c r="B161" s="8" t="n">
         <v>13063554.95431002</v>
       </c>
-      <c r="C161" t="n">
-        <v>1</v>
-      </c>
-      <c r="D161" t="n">
-        <v>1</v>
-      </c>
-      <c r="E161" t="n">
-        <v>1</v>
-      </c>
-      <c r="F161" t="n">
+      <c r="C161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="G161" t="n">
-        <v>1</v>
-      </c>
-      <c r="H161" t="n">
-        <v>1</v>
-      </c>
-      <c r="I161" t="n">
+      <c r="G161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I161" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J161" t="n">
-        <v>3</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" t="n">
-        <v>1</v>
-      </c>
-      <c r="M161" t="n">
-        <v>1</v>
-      </c>
-      <c r="N161" t="n">
-        <v>2</v>
-      </c>
-      <c r="O161" t="n">
-        <v>1</v>
-      </c>
-      <c r="P161" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>4</v>
-      </c>
-      <c r="R161" t="n">
-        <v>1</v>
-      </c>
-      <c r="S161" t="n">
-        <v>4</v>
-      </c>
-      <c r="T161" t="n">
-        <v>5</v>
-      </c>
-      <c r="U161" t="n">
-        <v>1</v>
-      </c>
-      <c r="V161" t="n">
-        <v>5</v>
-      </c>
-      <c r="W161" t="n">
-        <v>0</v>
-      </c>
-      <c r="X161" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y161" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI161" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ161" t="n">
+      <c r="J161" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N161" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P161" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q161" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S161" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T161" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U161" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V161" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X161" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y161" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI161" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ161" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
         <v>46126</v>
+      </c>
+      <c r="B162" t="n">
+        <v>13234483.95431002</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>67</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="n">
+        <v>1</v>
+      </c>
+      <c r="I162" t="n">
+        <v>8</v>
+      </c>
+      <c r="J162" t="n">
+        <v>3</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>1</v>
+      </c>
+      <c r="N162" t="n">
+        <v>2</v>
+      </c>
+      <c r="O162" t="n">
+        <v>1</v>
+      </c>
+      <c r="P162" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>4</v>
+      </c>
+      <c r="R162" t="n">
+        <v>1</v>
+      </c>
+      <c r="S162" t="n">
+        <v>4</v>
+      </c>
+      <c r="T162" t="n">
+        <v>5</v>
+      </c>
+      <c r="U162" t="n">
+        <v>1</v>
+      </c>
+      <c r="V162" t="n">
+        <v>5</v>
+      </c>
+      <c r="W162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -17990,115 +17990,220 @@
       <c r="A162" s="5" t="n">
         <v>46126</v>
       </c>
-      <c r="B162" t="n">
+      <c r="B162" s="8" t="n">
         <v>13234483.95431002</v>
       </c>
-      <c r="C162" t="n">
-        <v>1</v>
-      </c>
-      <c r="D162" t="n">
-        <v>1</v>
-      </c>
-      <c r="E162" t="n">
-        <v>1</v>
-      </c>
-      <c r="F162" t="n">
+      <c r="C162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="G162" t="n">
-        <v>1</v>
-      </c>
-      <c r="H162" t="n">
-        <v>1</v>
-      </c>
-      <c r="I162" t="n">
+      <c r="G162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I162" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J162" t="n">
-        <v>3</v>
-      </c>
-      <c r="K162" t="n">
-        <v>0</v>
-      </c>
-      <c r="L162" t="n">
-        <v>1</v>
-      </c>
-      <c r="M162" t="n">
-        <v>1</v>
-      </c>
-      <c r="N162" t="n">
-        <v>2</v>
-      </c>
-      <c r="O162" t="n">
-        <v>1</v>
-      </c>
-      <c r="P162" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>4</v>
-      </c>
-      <c r="R162" t="n">
-        <v>1</v>
-      </c>
-      <c r="S162" t="n">
-        <v>4</v>
-      </c>
-      <c r="T162" t="n">
-        <v>5</v>
-      </c>
-      <c r="U162" t="n">
-        <v>1</v>
-      </c>
-      <c r="V162" t="n">
-        <v>5</v>
-      </c>
-      <c r="W162" t="n">
-        <v>0</v>
-      </c>
-      <c r="X162" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y162" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z162" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI162" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ162" t="n">
+      <c r="J162" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N162" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P162" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q162" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S162" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T162" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V162" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y162" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z162" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
         <v>46127</v>
+      </c>
+      <c r="B163" t="n">
+        <v>13278965.95431002</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>67</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" t="n">
+        <v>8</v>
+      </c>
+      <c r="J163" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" t="n">
+        <v>1</v>
+      </c>
+      <c r="N163" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" t="n">
+        <v>1</v>
+      </c>
+      <c r="P163" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>4</v>
+      </c>
+      <c r="R163" t="n">
+        <v>1</v>
+      </c>
+      <c r="S163" t="n">
+        <v>4</v>
+      </c>
+      <c r="T163" t="n">
+        <v>4</v>
+      </c>
+      <c r="U163" t="n">
+        <v>1</v>
+      </c>
+      <c r="V163" t="n">
+        <v>5</v>
+      </c>
+      <c r="W163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="164">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -18100,115 +18100,220 @@
       <c r="A163" s="5" t="n">
         <v>46127</v>
       </c>
-      <c r="B163" t="n">
+      <c r="B163" s="8" t="n">
         <v>13278965.95431002</v>
       </c>
-      <c r="C163" t="n">
-        <v>1</v>
-      </c>
-      <c r="D163" t="n">
-        <v>1</v>
-      </c>
-      <c r="E163" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" t="n">
+      <c r="C163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="G163" t="n">
-        <v>1</v>
-      </c>
-      <c r="H163" t="n">
-        <v>1</v>
-      </c>
-      <c r="I163" t="n">
+      <c r="G163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J163" t="n">
-        <v>3</v>
-      </c>
-      <c r="K163" t="n">
-        <v>0</v>
-      </c>
-      <c r="L163" t="n">
-        <v>1</v>
-      </c>
-      <c r="M163" t="n">
-        <v>1</v>
-      </c>
-      <c r="N163" t="n">
-        <v>2</v>
-      </c>
-      <c r="O163" t="n">
-        <v>1</v>
-      </c>
-      <c r="P163" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>4</v>
-      </c>
-      <c r="R163" t="n">
-        <v>1</v>
-      </c>
-      <c r="S163" t="n">
-        <v>4</v>
-      </c>
-      <c r="T163" t="n">
-        <v>4</v>
-      </c>
-      <c r="U163" t="n">
-        <v>1</v>
-      </c>
-      <c r="V163" t="n">
-        <v>5</v>
-      </c>
-      <c r="W163" t="n">
-        <v>0</v>
-      </c>
-      <c r="X163" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y163" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z163" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI163" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ163" t="n">
+      <c r="J163" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N163" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P163" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q163" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S163" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T163" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V163" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="W163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y163" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z163" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI163" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ163" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
         <v>46128</v>
+      </c>
+      <c r="B164" t="n">
+        <v>13374990.45431002</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" t="n">
+        <v>68</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" t="n">
+        <v>9</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" t="n">
+        <v>1</v>
+      </c>
+      <c r="P164" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>4</v>
+      </c>
+      <c r="R164" t="n">
+        <v>1</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
+        <v>4</v>
+      </c>
+      <c r="U164" t="n">
+        <v>1</v>
+      </c>
+      <c r="V164" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1</v>
+      </c>
+      <c r="X164" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="165">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -18210,115 +18210,220 @@
       <c r="A164" s="5" t="n">
         <v>46128</v>
       </c>
-      <c r="B164" t="n">
+      <c r="B164" s="8" t="n">
         <v>13374990.45431002</v>
       </c>
-      <c r="C164" t="n">
-        <v>1</v>
-      </c>
-      <c r="D164" t="n">
-        <v>1</v>
-      </c>
-      <c r="E164" t="n">
-        <v>1</v>
-      </c>
-      <c r="F164" t="n">
+      <c r="C164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="G164" t="n">
-        <v>1</v>
-      </c>
-      <c r="H164" t="n">
-        <v>1</v>
-      </c>
-      <c r="I164" t="n">
+      <c r="G164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J164" t="n">
-        <v>3</v>
-      </c>
-      <c r="K164" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" t="n">
-        <v>1</v>
-      </c>
-      <c r="M164" t="n">
-        <v>1</v>
-      </c>
-      <c r="N164" t="n">
-        <v>2</v>
-      </c>
-      <c r="O164" t="n">
-        <v>1</v>
-      </c>
-      <c r="P164" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q164" t="n">
-        <v>4</v>
-      </c>
-      <c r="R164" t="n">
-        <v>1</v>
-      </c>
-      <c r="S164" t="n">
-        <v>0</v>
-      </c>
-      <c r="T164" t="n">
-        <v>4</v>
-      </c>
-      <c r="U164" t="n">
-        <v>1</v>
-      </c>
-      <c r="V164" t="n">
-        <v>0</v>
-      </c>
-      <c r="W164" t="n">
-        <v>1</v>
-      </c>
-      <c r="X164" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y164" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z164" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI164" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ164" t="n">
+      <c r="J164" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N164" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P164" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q164" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X164" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y164" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z164" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI164" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ164" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
         <v>46129</v>
+      </c>
+      <c r="B165" t="n">
+        <v>13505696.53431002</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" t="n">
+        <v>70</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" t="n">
+        <v>9</v>
+      </c>
+      <c r="J165" t="n">
+        <v>3</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" t="n">
+        <v>2</v>
+      </c>
+      <c r="O165" t="n">
+        <v>1</v>
+      </c>
+      <c r="P165" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>5</v>
+      </c>
+      <c r="R165" t="n">
+        <v>1</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
+        <v>4</v>
+      </c>
+      <c r="U165" t="n">
+        <v>1</v>
+      </c>
+      <c r="V165" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" t="n">
+        <v>1</v>
+      </c>
+      <c r="X165" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="166">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -18320,115 +18320,220 @@
       <c r="A165" s="5" t="n">
         <v>46129</v>
       </c>
-      <c r="B165" t="n">
+      <c r="B165" s="8" t="n">
         <v>13505696.53431002</v>
       </c>
-      <c r="C165" t="n">
-        <v>1</v>
-      </c>
-      <c r="D165" t="n">
-        <v>1</v>
-      </c>
-      <c r="E165" t="n">
-        <v>1</v>
-      </c>
-      <c r="F165" t="n">
+      <c r="C165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="G165" t="n">
-        <v>1</v>
-      </c>
-      <c r="H165" t="n">
-        <v>1</v>
-      </c>
-      <c r="I165" t="n">
+      <c r="G165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J165" t="n">
-        <v>3</v>
-      </c>
-      <c r="K165" t="n">
-        <v>0</v>
-      </c>
-      <c r="L165" t="n">
-        <v>1</v>
-      </c>
-      <c r="M165" t="n">
-        <v>1</v>
-      </c>
-      <c r="N165" t="n">
-        <v>2</v>
-      </c>
-      <c r="O165" t="n">
-        <v>1</v>
-      </c>
-      <c r="P165" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>5</v>
-      </c>
-      <c r="R165" t="n">
-        <v>1</v>
-      </c>
-      <c r="S165" t="n">
-        <v>0</v>
-      </c>
-      <c r="T165" t="n">
-        <v>4</v>
-      </c>
-      <c r="U165" t="n">
-        <v>1</v>
-      </c>
-      <c r="V165" t="n">
-        <v>0</v>
-      </c>
-      <c r="W165" t="n">
-        <v>1</v>
-      </c>
-      <c r="X165" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y165" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z165" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI165" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ165" t="n">
+      <c r="J165" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N165" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P165" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q165" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X165" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y165" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z165" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
         <v>46132</v>
+      </c>
+      <c r="B166" t="n">
+        <v>13510618.53431002</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" t="n">
+        <v>69</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" t="n">
+        <v>9</v>
+      </c>
+      <c r="J166" t="n">
+        <v>3</v>
+      </c>
+      <c r="K166" t="n">
+        <v>1</v>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="n">
+        <v>1</v>
+      </c>
+      <c r="N166" t="n">
+        <v>2</v>
+      </c>
+      <c r="O166" t="n">
+        <v>1</v>
+      </c>
+      <c r="P166" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>5</v>
+      </c>
+      <c r="R166" t="n">
+        <v>1</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
+        <v>4</v>
+      </c>
+      <c r="U166" t="n">
+        <v>1</v>
+      </c>
+      <c r="V166" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" t="n">
+        <v>1</v>
+      </c>
+      <c r="X166" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -18430,115 +18430,220 @@
       <c r="A166" s="5" t="n">
         <v>46132</v>
       </c>
-      <c r="B166" t="n">
+      <c r="B166" s="8" t="n">
         <v>13510618.53431002</v>
       </c>
-      <c r="C166" t="n">
-        <v>1</v>
-      </c>
-      <c r="D166" t="n">
-        <v>1</v>
-      </c>
-      <c r="E166" t="n">
-        <v>1</v>
-      </c>
-      <c r="F166" t="n">
+      <c r="C166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="G166" t="n">
-        <v>1</v>
-      </c>
-      <c r="H166" t="n">
-        <v>1</v>
-      </c>
-      <c r="I166" t="n">
+      <c r="G166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J166" t="n">
-        <v>3</v>
-      </c>
-      <c r="K166" t="n">
-        <v>1</v>
-      </c>
-      <c r="L166" t="n">
-        <v>1</v>
-      </c>
-      <c r="M166" t="n">
-        <v>1</v>
-      </c>
-      <c r="N166" t="n">
-        <v>2</v>
-      </c>
-      <c r="O166" t="n">
-        <v>1</v>
-      </c>
-      <c r="P166" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>5</v>
-      </c>
-      <c r="R166" t="n">
-        <v>1</v>
-      </c>
-      <c r="S166" t="n">
-        <v>0</v>
-      </c>
-      <c r="T166" t="n">
-        <v>4</v>
-      </c>
-      <c r="U166" t="n">
-        <v>1</v>
-      </c>
-      <c r="V166" t="n">
-        <v>0</v>
-      </c>
-      <c r="W166" t="n">
-        <v>1</v>
-      </c>
-      <c r="X166" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y166" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z166" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI166" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ166" t="n">
+      <c r="J166" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N166" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P166" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q166" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X166" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y166" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z166" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI166" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ166" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n">
         <v>46133</v>
+      </c>
+      <c r="B167" t="n">
+        <v>13529103.34181002</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" t="n">
+        <v>68</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" t="n">
+        <v>9</v>
+      </c>
+      <c r="J167" t="n">
+        <v>3</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" t="n">
+        <v>2</v>
+      </c>
+      <c r="O167" t="n">
+        <v>1</v>
+      </c>
+      <c r="P167" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>5</v>
+      </c>
+      <c r="R167" t="n">
+        <v>1</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>4</v>
+      </c>
+      <c r="U167" t="n">
+        <v>1</v>
+      </c>
+      <c r="V167" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1</v>
+      </c>
+      <c r="X167" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -18540,115 +18540,220 @@
       <c r="A167" s="5" t="n">
         <v>46133</v>
       </c>
-      <c r="B167" t="n">
+      <c r="B167" s="8" t="n">
         <v>13529103.34181002</v>
       </c>
-      <c r="C167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D167" t="n">
-        <v>1</v>
-      </c>
-      <c r="E167" t="n">
-        <v>1</v>
-      </c>
-      <c r="F167" t="n">
+      <c r="C167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="G167" t="n">
-        <v>1</v>
-      </c>
-      <c r="H167" t="n">
-        <v>1</v>
-      </c>
-      <c r="I167" t="n">
+      <c r="G167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J167" t="n">
-        <v>3</v>
-      </c>
-      <c r="K167" t="n">
-        <v>1</v>
-      </c>
-      <c r="L167" t="n">
-        <v>1</v>
-      </c>
-      <c r="M167" t="n">
-        <v>1</v>
-      </c>
-      <c r="N167" t="n">
-        <v>2</v>
-      </c>
-      <c r="O167" t="n">
-        <v>1</v>
-      </c>
-      <c r="P167" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>5</v>
-      </c>
-      <c r="R167" t="n">
-        <v>1</v>
-      </c>
-      <c r="S167" t="n">
-        <v>0</v>
-      </c>
-      <c r="T167" t="n">
-        <v>4</v>
-      </c>
-      <c r="U167" t="n">
-        <v>1</v>
-      </c>
-      <c r="V167" t="n">
-        <v>0</v>
-      </c>
-      <c r="W167" t="n">
-        <v>1</v>
-      </c>
-      <c r="X167" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y167" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z167" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI167" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ167" t="n">
+      <c r="J167" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N167" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P167" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q167" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X167" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y167" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z167" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ167" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
         <v>46134</v>
+      </c>
+      <c r="B168" t="n">
+        <v>13686674.34181002</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" t="n">
+        <v>69</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" t="n">
+        <v>9</v>
+      </c>
+      <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" t="n">
+        <v>2</v>
+      </c>
+      <c r="O168" t="n">
+        <v>1</v>
+      </c>
+      <c r="P168" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>5</v>
+      </c>
+      <c r="R168" t="n">
+        <v>1</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>4</v>
+      </c>
+      <c r="U168" t="n">
+        <v>1</v>
+      </c>
+      <c r="V168" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" t="n">
+        <v>1</v>
+      </c>
+      <c r="X168" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="169">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -18650,115 +18650,220 @@
       <c r="A168" s="5" t="n">
         <v>46134</v>
       </c>
-      <c r="B168" t="n">
+      <c r="B168" s="8" t="n">
         <v>13686674.34181002</v>
       </c>
-      <c r="C168" t="n">
-        <v>1</v>
-      </c>
-      <c r="D168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E168" t="n">
-        <v>1</v>
-      </c>
-      <c r="F168" t="n">
+      <c r="C168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="G168" t="n">
-        <v>1</v>
-      </c>
-      <c r="H168" t="n">
-        <v>1</v>
-      </c>
-      <c r="I168" t="n">
+      <c r="G168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J168" t="n">
-        <v>3</v>
-      </c>
-      <c r="K168" t="n">
-        <v>1</v>
-      </c>
-      <c r="L168" t="n">
-        <v>1</v>
-      </c>
-      <c r="M168" t="n">
-        <v>1</v>
-      </c>
-      <c r="N168" t="n">
-        <v>2</v>
-      </c>
-      <c r="O168" t="n">
-        <v>1</v>
-      </c>
-      <c r="P168" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>5</v>
-      </c>
-      <c r="R168" t="n">
-        <v>1</v>
-      </c>
-      <c r="S168" t="n">
-        <v>0</v>
-      </c>
-      <c r="T168" t="n">
-        <v>4</v>
-      </c>
-      <c r="U168" t="n">
-        <v>1</v>
-      </c>
-      <c r="V168" t="n">
-        <v>0</v>
-      </c>
-      <c r="W168" t="n">
-        <v>1</v>
-      </c>
-      <c r="X168" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y168" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z168" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI168" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ168" t="n">
+      <c r="J168" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N168" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P168" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q168" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X168" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y168" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z168" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI168" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ168" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
         <v>46135</v>
+      </c>
+      <c r="B169" t="n">
+        <v>13574218.34181002</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" t="n">
+        <v>69</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" t="n">
+        <v>8</v>
+      </c>
+      <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" t="n">
+        <v>2</v>
+      </c>
+      <c r="O169" t="n">
+        <v>1</v>
+      </c>
+      <c r="P169" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>5</v>
+      </c>
+      <c r="R169" t="n">
+        <v>1</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>4</v>
+      </c>
+      <c r="U169" t="n">
+        <v>1</v>
+      </c>
+      <c r="V169" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" t="n">
+        <v>1</v>
+      </c>
+      <c r="X169" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="170">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -18760,115 +18760,220 @@
       <c r="A169" s="5" t="n">
         <v>46135</v>
       </c>
-      <c r="B169" t="n">
+      <c r="B169" s="8" t="n">
         <v>13574218.34181002</v>
       </c>
-      <c r="C169" t="n">
-        <v>1</v>
-      </c>
-      <c r="D169" t="n">
-        <v>1</v>
-      </c>
-      <c r="E169" t="n">
-        <v>1</v>
-      </c>
-      <c r="F169" t="n">
+      <c r="C169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="G169" t="n">
-        <v>1</v>
-      </c>
-      <c r="H169" t="n">
-        <v>1</v>
-      </c>
-      <c r="I169" t="n">
+      <c r="G169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J169" t="n">
-        <v>3</v>
-      </c>
-      <c r="K169" t="n">
-        <v>0</v>
-      </c>
-      <c r="L169" t="n">
-        <v>1</v>
-      </c>
-      <c r="M169" t="n">
-        <v>1</v>
-      </c>
-      <c r="N169" t="n">
-        <v>2</v>
-      </c>
-      <c r="O169" t="n">
-        <v>1</v>
-      </c>
-      <c r="P169" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>5</v>
-      </c>
-      <c r="R169" t="n">
-        <v>1</v>
-      </c>
-      <c r="S169" t="n">
-        <v>0</v>
-      </c>
-      <c r="T169" t="n">
-        <v>4</v>
-      </c>
-      <c r="U169" t="n">
-        <v>1</v>
-      </c>
-      <c r="V169" t="n">
-        <v>0</v>
-      </c>
-      <c r="W169" t="n">
-        <v>1</v>
-      </c>
-      <c r="X169" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y169" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z169" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ169" t="n">
+      <c r="J169" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N169" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P169" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q169" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X169" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y169" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z169" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI169" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ169" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
         <v>46136</v>
+      </c>
+      <c r="B170" t="n">
+        <v>13521411.88681002</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>68</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" t="n">
+        <v>9</v>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>1</v>
+      </c>
+      <c r="N170" t="n">
+        <v>2</v>
+      </c>
+      <c r="O170" t="n">
+        <v>1</v>
+      </c>
+      <c r="P170" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>5</v>
+      </c>
+      <c r="R170" t="n">
+        <v>1</v>
+      </c>
+      <c r="S170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
+        <v>4</v>
+      </c>
+      <c r="U170" t="n">
+        <v>1</v>
+      </c>
+      <c r="V170" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1</v>
+      </c>
+      <c r="X170" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="171">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -18870,115 +18870,220 @@
       <c r="A170" s="5" t="n">
         <v>46136</v>
       </c>
-      <c r="B170" t="n">
+      <c r="B170" s="8" t="n">
         <v>13521411.88681002</v>
       </c>
-      <c r="C170" t="n">
-        <v>1</v>
-      </c>
-      <c r="D170" t="n">
-        <v>1</v>
-      </c>
-      <c r="E170" t="n">
-        <v>1</v>
-      </c>
-      <c r="F170" t="n">
+      <c r="C170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="G170" t="n">
-        <v>1</v>
-      </c>
-      <c r="H170" t="n">
-        <v>1</v>
-      </c>
-      <c r="I170" t="n">
+      <c r="G170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J170" t="n">
-        <v>3</v>
-      </c>
-      <c r="K170" t="n">
-        <v>1</v>
-      </c>
-      <c r="L170" t="n">
-        <v>1</v>
-      </c>
-      <c r="M170" t="n">
-        <v>1</v>
-      </c>
-      <c r="N170" t="n">
-        <v>2</v>
-      </c>
-      <c r="O170" t="n">
-        <v>1</v>
-      </c>
-      <c r="P170" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>5</v>
-      </c>
-      <c r="R170" t="n">
-        <v>1</v>
-      </c>
-      <c r="S170" t="n">
-        <v>0</v>
-      </c>
-      <c r="T170" t="n">
-        <v>4</v>
-      </c>
-      <c r="U170" t="n">
-        <v>1</v>
-      </c>
-      <c r="V170" t="n">
-        <v>0</v>
-      </c>
-      <c r="W170" t="n">
-        <v>1</v>
-      </c>
-      <c r="X170" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y170" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z170" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI170" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ170" t="n">
+      <c r="J170" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N170" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P170" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q170" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X170" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y170" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z170" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI170" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ170" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n">
         <v>46139</v>
+      </c>
+      <c r="B171" t="n">
+        <v>13427488.69681002</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>68</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" t="n">
+        <v>8</v>
+      </c>
+      <c r="J171" t="n">
+        <v>3</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
+        <v>2</v>
+      </c>
+      <c r="O171" t="n">
+        <v>1</v>
+      </c>
+      <c r="P171" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>5</v>
+      </c>
+      <c r="R171" t="n">
+        <v>1</v>
+      </c>
+      <c r="S171" t="n">
+        <v>4</v>
+      </c>
+      <c r="T171" t="n">
+        <v>4</v>
+      </c>
+      <c r="U171" t="n">
+        <v>1</v>
+      </c>
+      <c r="V171" t="n">
+        <v>0</v>
+      </c>
+      <c r="W171" t="n">
+        <v>1</v>
+      </c>
+      <c r="X171" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -18980,109 +18980,109 @@
       <c r="A171" s="5" t="n">
         <v>46139</v>
       </c>
-      <c r="B171" t="n">
+      <c r="B171" s="8" t="n">
         <v>13427488.69681002</v>
       </c>
-      <c r="C171" t="n">
-        <v>1</v>
-      </c>
-      <c r="D171" t="n">
-        <v>1</v>
-      </c>
-      <c r="E171" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" t="n">
+      <c r="C171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="G171" t="n">
-        <v>1</v>
-      </c>
-      <c r="H171" t="n">
-        <v>1</v>
-      </c>
-      <c r="I171" t="n">
+      <c r="G171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J171" t="n">
-        <v>3</v>
-      </c>
-      <c r="K171" t="n">
-        <v>1</v>
-      </c>
-      <c r="L171" t="n">
-        <v>1</v>
-      </c>
-      <c r="M171" t="n">
-        <v>1</v>
-      </c>
-      <c r="N171" t="n">
-        <v>2</v>
-      </c>
-      <c r="O171" t="n">
-        <v>1</v>
-      </c>
-      <c r="P171" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>5</v>
-      </c>
-      <c r="R171" t="n">
-        <v>1</v>
-      </c>
-      <c r="S171" t="n">
-        <v>4</v>
-      </c>
-      <c r="T171" t="n">
-        <v>4</v>
-      </c>
-      <c r="U171" t="n">
-        <v>1</v>
-      </c>
-      <c r="V171" t="n">
-        <v>0</v>
-      </c>
-      <c r="W171" t="n">
-        <v>1</v>
-      </c>
-      <c r="X171" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y171" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z171" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI171" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ171" t="n">
+      <c r="J171" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P171" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q171" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S171" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T171" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X171" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y171" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z171" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI171" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ171" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19094,6 +19094,111 @@
     <row r="173">
       <c r="A173" s="5" t="n">
         <v>46141</v>
+      </c>
+      <c r="B173" t="n">
+        <v>13565930.49981002</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>67</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" t="n">
+        <v>9</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>1</v>
+      </c>
+      <c r="N173" t="n">
+        <v>2</v>
+      </c>
+      <c r="O173" t="n">
+        <v>1</v>
+      </c>
+      <c r="P173" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>5</v>
+      </c>
+      <c r="R173" t="n">
+        <v>1</v>
+      </c>
+      <c r="S173" t="n">
+        <v>4</v>
+      </c>
+      <c r="T173" t="n">
+        <v>4</v>
+      </c>
+      <c r="U173" t="n">
+        <v>1</v>
+      </c>
+      <c r="V173" t="n">
+        <v>0</v>
+      </c>
+      <c r="W173" t="n">
+        <v>1</v>
+      </c>
+      <c r="X173" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -19095,109 +19095,109 @@
       <c r="A173" s="5" t="n">
         <v>46141</v>
       </c>
-      <c r="B173" t="n">
+      <c r="B173" s="8" t="n">
         <v>13565930.49981002</v>
       </c>
-      <c r="C173" t="n">
-        <v>1</v>
-      </c>
-      <c r="D173" t="n">
-        <v>1</v>
-      </c>
-      <c r="E173" t="n">
-        <v>1</v>
-      </c>
-      <c r="F173" t="n">
+      <c r="C173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="G173" t="n">
-        <v>1</v>
-      </c>
-      <c r="H173" t="n">
-        <v>1</v>
-      </c>
-      <c r="I173" t="n">
+      <c r="G173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J173" t="n">
-        <v>3</v>
-      </c>
-      <c r="K173" t="n">
-        <v>1</v>
-      </c>
-      <c r="L173" t="n">
-        <v>1</v>
-      </c>
-      <c r="M173" t="n">
-        <v>1</v>
-      </c>
-      <c r="N173" t="n">
-        <v>2</v>
-      </c>
-      <c r="O173" t="n">
-        <v>1</v>
-      </c>
-      <c r="P173" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q173" t="n">
-        <v>5</v>
-      </c>
-      <c r="R173" t="n">
-        <v>1</v>
-      </c>
-      <c r="S173" t="n">
-        <v>4</v>
-      </c>
-      <c r="T173" t="n">
-        <v>4</v>
-      </c>
-      <c r="U173" t="n">
-        <v>1</v>
-      </c>
-      <c r="V173" t="n">
-        <v>0</v>
-      </c>
-      <c r="W173" t="n">
-        <v>1</v>
-      </c>
-      <c r="X173" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y173" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z173" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA173" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB173" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC173" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD173" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE173" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF173" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG173" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH173" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI173" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ173" t="n">
+      <c r="J173" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N173" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P173" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q173" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S173" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T173" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X173" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y173" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z173" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI173" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ173" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19209,6 +19209,111 @@
     <row r="175">
       <c r="A175" s="5" t="n">
         <v>46148</v>
+      </c>
+      <c r="B175" t="n">
+        <v>13664420.29581002</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>67</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8</v>
+      </c>
+      <c r="J175" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1</v>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>2</v>
+      </c>
+      <c r="O175" t="n">
+        <v>1</v>
+      </c>
+      <c r="P175" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>5</v>
+      </c>
+      <c r="R175" t="n">
+        <v>1</v>
+      </c>
+      <c r="S175" t="n">
+        <v>4</v>
+      </c>
+      <c r="T175" t="n">
+        <v>4</v>
+      </c>
+      <c r="U175" t="n">
+        <v>1</v>
+      </c>
+      <c r="V175" t="n">
+        <v>0</v>
+      </c>
+      <c r="W175" t="n">
+        <v>1</v>
+      </c>
+      <c r="X175" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="176">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -19210,115 +19210,220 @@
       <c r="A175" s="5" t="n">
         <v>46148</v>
       </c>
-      <c r="B175" t="n">
+      <c r="B175" s="8" t="n">
         <v>13664420.29581002</v>
       </c>
-      <c r="C175" t="n">
-        <v>1</v>
-      </c>
-      <c r="D175" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" t="n">
-        <v>1</v>
-      </c>
-      <c r="F175" t="n">
+      <c r="C175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="G175" t="n">
-        <v>1</v>
-      </c>
-      <c r="H175" t="n">
-        <v>1</v>
-      </c>
-      <c r="I175" t="n">
+      <c r="G175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I175" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J175" t="n">
-        <v>3</v>
-      </c>
-      <c r="K175" t="n">
-        <v>1</v>
-      </c>
-      <c r="L175" t="n">
-        <v>1</v>
-      </c>
-      <c r="M175" t="n">
-        <v>1</v>
-      </c>
-      <c r="N175" t="n">
-        <v>2</v>
-      </c>
-      <c r="O175" t="n">
-        <v>1</v>
-      </c>
-      <c r="P175" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q175" t="n">
-        <v>5</v>
-      </c>
-      <c r="R175" t="n">
-        <v>1</v>
-      </c>
-      <c r="S175" t="n">
-        <v>4</v>
-      </c>
-      <c r="T175" t="n">
-        <v>4</v>
-      </c>
-      <c r="U175" t="n">
-        <v>1</v>
-      </c>
-      <c r="V175" t="n">
-        <v>0</v>
-      </c>
-      <c r="W175" t="n">
-        <v>1</v>
-      </c>
-      <c r="X175" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y175" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z175" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA175" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB175" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC175" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD175" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE175" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF175" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG175" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH175" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI175" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ175" t="n">
+      <c r="J175" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P175" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q175" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S175" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T175" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X175" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y175" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z175" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI175" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ175" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n">
         <v>46149</v>
+      </c>
+      <c r="B176" t="n">
+        <v>13686347.29581002</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" t="n">
+        <v>68</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="n">
+        <v>1</v>
+      </c>
+      <c r="I176" t="n">
+        <v>8</v>
+      </c>
+      <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="n">
+        <v>1</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>1</v>
+      </c>
+      <c r="N176" t="n">
+        <v>2</v>
+      </c>
+      <c r="O176" t="n">
+        <v>1</v>
+      </c>
+      <c r="P176" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>5</v>
+      </c>
+      <c r="R176" t="n">
+        <v>1</v>
+      </c>
+      <c r="S176" t="n">
+        <v>4</v>
+      </c>
+      <c r="T176" t="n">
+        <v>4</v>
+      </c>
+      <c r="U176" t="n">
+        <v>1</v>
+      </c>
+      <c r="V176" t="n">
+        <v>0</v>
+      </c>
+      <c r="W176" t="n">
+        <v>1</v>
+      </c>
+      <c r="X176" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -19320,115 +19320,220 @@
       <c r="A176" s="5" t="n">
         <v>46149</v>
       </c>
-      <c r="B176" t="n">
+      <c r="B176" s="8" t="n">
         <v>13686347.29581002</v>
       </c>
-      <c r="C176" t="n">
-        <v>1</v>
-      </c>
-      <c r="D176" t="n">
-        <v>1</v>
-      </c>
-      <c r="E176" t="n">
-        <v>1</v>
-      </c>
-      <c r="F176" t="n">
+      <c r="C176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="8" t="n">
         <v>68</v>
       </c>
-      <c r="G176" t="n">
-        <v>1</v>
-      </c>
-      <c r="H176" t="n">
-        <v>1</v>
-      </c>
-      <c r="I176" t="n">
+      <c r="G176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I176" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J176" t="n">
-        <v>3</v>
-      </c>
-      <c r="K176" t="n">
-        <v>1</v>
-      </c>
-      <c r="L176" t="n">
-        <v>1</v>
-      </c>
-      <c r="M176" t="n">
-        <v>1</v>
-      </c>
-      <c r="N176" t="n">
-        <v>2</v>
-      </c>
-      <c r="O176" t="n">
-        <v>1</v>
-      </c>
-      <c r="P176" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q176" t="n">
-        <v>5</v>
-      </c>
-      <c r="R176" t="n">
-        <v>1</v>
-      </c>
-      <c r="S176" t="n">
-        <v>4</v>
-      </c>
-      <c r="T176" t="n">
-        <v>4</v>
-      </c>
-      <c r="U176" t="n">
-        <v>1</v>
-      </c>
-      <c r="V176" t="n">
-        <v>0</v>
-      </c>
-      <c r="W176" t="n">
-        <v>1</v>
-      </c>
-      <c r="X176" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y176" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z176" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA176" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB176" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC176" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD176" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE176" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF176" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG176" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH176" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI176" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ176" t="n">
+      <c r="J176" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N176" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P176" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q176" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S176" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T176" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X176" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y176" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z176" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI176" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ176" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n">
         <v>46150</v>
+      </c>
+      <c r="B177" t="n">
+        <v>13680619.29581002</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" t="n">
+        <v>69</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I177" t="n">
+        <v>8</v>
+      </c>
+      <c r="J177" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>1</v>
+      </c>
+      <c r="N177" t="n">
+        <v>2</v>
+      </c>
+      <c r="O177" t="n">
+        <v>1</v>
+      </c>
+      <c r="P177" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>5</v>
+      </c>
+      <c r="R177" t="n">
+        <v>1</v>
+      </c>
+      <c r="S177" t="n">
+        <v>4</v>
+      </c>
+      <c r="T177" t="n">
+        <v>5</v>
+      </c>
+      <c r="U177" t="n">
+        <v>1</v>
+      </c>
+      <c r="V177" t="n">
+        <v>0</v>
+      </c>
+      <c r="W177" t="n">
+        <v>1</v>
+      </c>
+      <c r="X177" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="178">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -19430,115 +19430,220 @@
       <c r="A177" s="5" t="n">
         <v>46150</v>
       </c>
-      <c r="B177" t="n">
+      <c r="B177" s="8" t="n">
         <v>13680619.29581002</v>
       </c>
-      <c r="C177" t="n">
-        <v>1</v>
-      </c>
-      <c r="D177" t="n">
-        <v>1</v>
-      </c>
-      <c r="E177" t="n">
-        <v>1</v>
-      </c>
-      <c r="F177" t="n">
+      <c r="C177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="G177" t="n">
-        <v>1</v>
-      </c>
-      <c r="H177" t="n">
-        <v>1</v>
-      </c>
-      <c r="I177" t="n">
+      <c r="G177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I177" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J177" t="n">
-        <v>3</v>
-      </c>
-      <c r="K177" t="n">
-        <v>1</v>
-      </c>
-      <c r="L177" t="n">
-        <v>1</v>
-      </c>
-      <c r="M177" t="n">
-        <v>1</v>
-      </c>
-      <c r="N177" t="n">
-        <v>2</v>
-      </c>
-      <c r="O177" t="n">
-        <v>1</v>
-      </c>
-      <c r="P177" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q177" t="n">
-        <v>5</v>
-      </c>
-      <c r="R177" t="n">
-        <v>1</v>
-      </c>
-      <c r="S177" t="n">
-        <v>4</v>
-      </c>
-      <c r="T177" t="n">
-        <v>5</v>
-      </c>
-      <c r="U177" t="n">
-        <v>1</v>
-      </c>
-      <c r="V177" t="n">
-        <v>0</v>
-      </c>
-      <c r="W177" t="n">
-        <v>1</v>
-      </c>
-      <c r="X177" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y177" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z177" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA177" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB177" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC177" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD177" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE177" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF177" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG177" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH177" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI177" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ177" t="n">
+      <c r="J177" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N177" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P177" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q177" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S177" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T177" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X177" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y177" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z177" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI177" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ177" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n">
         <v>46153</v>
+      </c>
+      <c r="B178" t="n">
+        <v>13832730.38331002</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" t="n">
+        <v>71</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" t="n">
+        <v>9</v>
+      </c>
+      <c r="J178" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N178" t="n">
+        <v>2</v>
+      </c>
+      <c r="O178" t="n">
+        <v>1</v>
+      </c>
+      <c r="P178" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>5</v>
+      </c>
+      <c r="R178" t="n">
+        <v>1</v>
+      </c>
+      <c r="S178" t="n">
+        <v>4</v>
+      </c>
+      <c r="T178" t="n">
+        <v>5</v>
+      </c>
+      <c r="U178" t="n">
+        <v>1</v>
+      </c>
+      <c r="V178" t="n">
+        <v>0</v>
+      </c>
+      <c r="W178" t="n">
+        <v>1</v>
+      </c>
+      <c r="X178" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -19540,115 +19540,220 @@
       <c r="A178" s="5" t="n">
         <v>46153</v>
       </c>
-      <c r="B178" t="n">
+      <c r="B178" s="8" t="n">
         <v>13832730.38331002</v>
       </c>
-      <c r="C178" t="n">
-        <v>1</v>
-      </c>
-      <c r="D178" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" t="n">
-        <v>1</v>
-      </c>
-      <c r="F178" t="n">
+      <c r="C178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="G178" t="n">
-        <v>1</v>
-      </c>
-      <c r="H178" t="n">
-        <v>1</v>
-      </c>
-      <c r="I178" t="n">
+      <c r="G178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I178" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J178" t="n">
-        <v>3</v>
-      </c>
-      <c r="K178" t="n">
-        <v>0</v>
-      </c>
-      <c r="L178" t="n">
-        <v>1</v>
-      </c>
-      <c r="M178" t="n">
-        <v>1</v>
-      </c>
-      <c r="N178" t="n">
-        <v>2</v>
-      </c>
-      <c r="O178" t="n">
-        <v>1</v>
-      </c>
-      <c r="P178" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>5</v>
-      </c>
-      <c r="R178" t="n">
-        <v>1</v>
-      </c>
-      <c r="S178" t="n">
-        <v>4</v>
-      </c>
-      <c r="T178" t="n">
-        <v>5</v>
-      </c>
-      <c r="U178" t="n">
-        <v>1</v>
-      </c>
-      <c r="V178" t="n">
-        <v>0</v>
-      </c>
-      <c r="W178" t="n">
-        <v>1</v>
-      </c>
-      <c r="X178" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y178" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z178" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI178" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ178" t="n">
+      <c r="J178" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N178" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P178" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q178" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S178" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T178" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X178" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y178" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z178" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI178" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ178" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">
         <v>46154</v>
+      </c>
+      <c r="B179" t="n">
+        <v>13866687.31931002</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>72</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" t="n">
+        <v>9</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>1</v>
+      </c>
+      <c r="N179" t="n">
+        <v>2</v>
+      </c>
+      <c r="O179" t="n">
+        <v>1</v>
+      </c>
+      <c r="P179" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>5</v>
+      </c>
+      <c r="R179" t="n">
+        <v>1</v>
+      </c>
+      <c r="S179" t="n">
+        <v>4</v>
+      </c>
+      <c r="T179" t="n">
+        <v>5</v>
+      </c>
+      <c r="U179" t="n">
+        <v>1</v>
+      </c>
+      <c r="V179" t="n">
+        <v>0</v>
+      </c>
+      <c r="W179" t="n">
+        <v>1</v>
+      </c>
+      <c r="X179" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -19650,115 +19650,220 @@
       <c r="A179" s="5" t="n">
         <v>46154</v>
       </c>
-      <c r="B179" t="n">
+      <c r="B179" s="8" t="n">
         <v>13866687.31931002</v>
       </c>
-      <c r="C179" t="n">
-        <v>1</v>
-      </c>
-      <c r="D179" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" t="n">
-        <v>1</v>
-      </c>
-      <c r="F179" t="n">
+      <c r="C179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" t="n">
-        <v>1</v>
-      </c>
-      <c r="I179" t="n">
+      <c r="G179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J179" t="n">
-        <v>3</v>
-      </c>
-      <c r="K179" t="n">
-        <v>0</v>
-      </c>
-      <c r="L179" t="n">
-        <v>1</v>
-      </c>
-      <c r="M179" t="n">
-        <v>1</v>
-      </c>
-      <c r="N179" t="n">
-        <v>2</v>
-      </c>
-      <c r="O179" t="n">
-        <v>1</v>
-      </c>
-      <c r="P179" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>5</v>
-      </c>
-      <c r="R179" t="n">
-        <v>1</v>
-      </c>
-      <c r="S179" t="n">
-        <v>4</v>
-      </c>
-      <c r="T179" t="n">
-        <v>5</v>
-      </c>
-      <c r="U179" t="n">
-        <v>1</v>
-      </c>
-      <c r="V179" t="n">
-        <v>0</v>
-      </c>
-      <c r="W179" t="n">
-        <v>1</v>
-      </c>
-      <c r="X179" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y179" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z179" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI179" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ179" t="n">
+      <c r="J179" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N179" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P179" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q179" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S179" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T179" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X179" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y179" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z179" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
         <v>46155</v>
+      </c>
+      <c r="B180" t="n">
+        <v>14023094.04831002</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" t="n">
+        <v>72</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="n">
+        <v>1</v>
+      </c>
+      <c r="I180" t="n">
+        <v>9</v>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="n">
+        <v>1</v>
+      </c>
+      <c r="N180" t="n">
+        <v>2</v>
+      </c>
+      <c r="O180" t="n">
+        <v>1</v>
+      </c>
+      <c r="P180" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>5</v>
+      </c>
+      <c r="R180" t="n">
+        <v>1</v>
+      </c>
+      <c r="S180" t="n">
+        <v>4</v>
+      </c>
+      <c r="T180" t="n">
+        <v>5</v>
+      </c>
+      <c r="U180" t="n">
+        <v>1</v>
+      </c>
+      <c r="V180" t="n">
+        <v>0</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1</v>
+      </c>
+      <c r="X180" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -19760,115 +19760,220 @@
       <c r="A180" s="5" t="n">
         <v>46155</v>
       </c>
-      <c r="B180" t="n">
+      <c r="B180" s="8" t="n">
         <v>14023094.04831002</v>
       </c>
-      <c r="C180" t="n">
-        <v>1</v>
-      </c>
-      <c r="D180" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" t="n">
-        <v>1</v>
-      </c>
-      <c r="F180" t="n">
+      <c r="C180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="G180" t="n">
-        <v>1</v>
-      </c>
-      <c r="H180" t="n">
-        <v>1</v>
-      </c>
-      <c r="I180" t="n">
+      <c r="G180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I180" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J180" t="n">
-        <v>3</v>
-      </c>
-      <c r="K180" t="n">
-        <v>0</v>
-      </c>
-      <c r="L180" t="n">
-        <v>1</v>
-      </c>
-      <c r="M180" t="n">
-        <v>1</v>
-      </c>
-      <c r="N180" t="n">
-        <v>2</v>
-      </c>
-      <c r="O180" t="n">
-        <v>1</v>
-      </c>
-      <c r="P180" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>5</v>
-      </c>
-      <c r="R180" t="n">
-        <v>1</v>
-      </c>
-      <c r="S180" t="n">
-        <v>4</v>
-      </c>
-      <c r="T180" t="n">
-        <v>5</v>
-      </c>
-      <c r="U180" t="n">
-        <v>1</v>
-      </c>
-      <c r="V180" t="n">
-        <v>0</v>
-      </c>
-      <c r="W180" t="n">
-        <v>1</v>
-      </c>
-      <c r="X180" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y180" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z180" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI180" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ180" t="n">
+      <c r="J180" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N180" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P180" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q180" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S180" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T180" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X180" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y180" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z180" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI180" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ180" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n">
         <v>46156</v>
+      </c>
+      <c r="B181" t="n">
+        <v>13849566.04831002</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" t="n">
+        <v>73</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" t="n">
+        <v>8</v>
+      </c>
+      <c r="J181" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
+        <v>1</v>
+      </c>
+      <c r="N181" t="n">
+        <v>2</v>
+      </c>
+      <c r="O181" t="n">
+        <v>1</v>
+      </c>
+      <c r="P181" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>5</v>
+      </c>
+      <c r="R181" t="n">
+        <v>1</v>
+      </c>
+      <c r="S181" t="n">
+        <v>4</v>
+      </c>
+      <c r="T181" t="n">
+        <v>5</v>
+      </c>
+      <c r="U181" t="n">
+        <v>1</v>
+      </c>
+      <c r="V181" t="n">
+        <v>0</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1</v>
+      </c>
+      <c r="X181" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="182">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -19870,115 +19870,220 @@
       <c r="A181" s="5" t="n">
         <v>46156</v>
       </c>
-      <c r="B181" t="n">
+      <c r="B181" s="8" t="n">
         <v>13849566.04831002</v>
       </c>
-      <c r="C181" t="n">
-        <v>1</v>
-      </c>
-      <c r="D181" t="n">
-        <v>1</v>
-      </c>
-      <c r="E181" t="n">
-        <v>1</v>
-      </c>
-      <c r="F181" t="n">
+      <c r="C181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="8" t="n">
         <v>73</v>
       </c>
-      <c r="G181" t="n">
-        <v>1</v>
-      </c>
-      <c r="H181" t="n">
-        <v>1</v>
-      </c>
-      <c r="I181" t="n">
+      <c r="G181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="J181" t="n">
-        <v>3</v>
-      </c>
-      <c r="K181" t="n">
-        <v>0</v>
-      </c>
-      <c r="L181" t="n">
-        <v>1</v>
-      </c>
-      <c r="M181" t="n">
-        <v>1</v>
-      </c>
-      <c r="N181" t="n">
-        <v>2</v>
-      </c>
-      <c r="O181" t="n">
-        <v>1</v>
-      </c>
-      <c r="P181" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>5</v>
-      </c>
-      <c r="R181" t="n">
-        <v>1</v>
-      </c>
-      <c r="S181" t="n">
-        <v>4</v>
-      </c>
-      <c r="T181" t="n">
-        <v>5</v>
-      </c>
-      <c r="U181" t="n">
-        <v>1</v>
-      </c>
-      <c r="V181" t="n">
-        <v>0</v>
-      </c>
-      <c r="W181" t="n">
-        <v>1</v>
-      </c>
-      <c r="X181" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y181" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z181" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI181" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ181" t="n">
+      <c r="J181" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N181" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P181" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q181" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S181" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T181" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X181" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y181" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z181" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI181" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n">
         <v>46157</v>
+      </c>
+      <c r="B182" t="n">
+        <v>13747773.55631002</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>71</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" t="n">
+        <v>9</v>
+      </c>
+      <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="n">
+        <v>1</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="n">
+        <v>1</v>
+      </c>
+      <c r="N182" t="n">
+        <v>2</v>
+      </c>
+      <c r="O182" t="n">
+        <v>1</v>
+      </c>
+      <c r="P182" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>5</v>
+      </c>
+      <c r="R182" t="n">
+        <v>1</v>
+      </c>
+      <c r="S182" t="n">
+        <v>4</v>
+      </c>
+      <c r="T182" t="n">
+        <v>5</v>
+      </c>
+      <c r="U182" t="n">
+        <v>1</v>
+      </c>
+      <c r="V182" t="n">
+        <v>0</v>
+      </c>
+      <c r="W182" t="n">
+        <v>1</v>
+      </c>
+      <c r="X182" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="183">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -19980,109 +19980,109 @@
       <c r="A182" s="5" t="n">
         <v>46157</v>
       </c>
-      <c r="B182" t="n">
+      <c r="B182" s="8" t="n">
         <v>13747773.55631002</v>
       </c>
-      <c r="C182" t="n">
-        <v>1</v>
-      </c>
-      <c r="D182" t="n">
-        <v>1</v>
-      </c>
-      <c r="E182" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" t="n">
+      <c r="C182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="G182" t="n">
-        <v>1</v>
-      </c>
-      <c r="H182" t="n">
-        <v>1</v>
-      </c>
-      <c r="I182" t="n">
+      <c r="G182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J182" t="n">
-        <v>3</v>
-      </c>
-      <c r="K182" t="n">
-        <v>1</v>
-      </c>
-      <c r="L182" t="n">
-        <v>1</v>
-      </c>
-      <c r="M182" t="n">
-        <v>1</v>
-      </c>
-      <c r="N182" t="n">
-        <v>2</v>
-      </c>
-      <c r="O182" t="n">
-        <v>1</v>
-      </c>
-      <c r="P182" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>5</v>
-      </c>
-      <c r="R182" t="n">
-        <v>1</v>
-      </c>
-      <c r="S182" t="n">
-        <v>4</v>
-      </c>
-      <c r="T182" t="n">
-        <v>5</v>
-      </c>
-      <c r="U182" t="n">
-        <v>1</v>
-      </c>
-      <c r="V182" t="n">
-        <v>0</v>
-      </c>
-      <c r="W182" t="n">
-        <v>1</v>
-      </c>
-      <c r="X182" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y182" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z182" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI182" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ182" t="n">
+      <c r="J182" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N182" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P182" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q182" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S182" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T182" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V182" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X182" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y182" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z182" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA182" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB182" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC182" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD182" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE182" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF182" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG182" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH182" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI182" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ182" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20109,6 +20109,111 @@
     <row r="187">
       <c r="A187" s="5" t="n">
         <v>46164</v>
+      </c>
+      <c r="B187" t="n">
+        <v>13765041.94381004</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>70</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" t="n">
+        <v>1</v>
+      </c>
+      <c r="I187" t="n">
+        <v>9</v>
+      </c>
+      <c r="J187" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="n">
+        <v>1</v>
+      </c>
+      <c r="N187" t="n">
+        <v>2</v>
+      </c>
+      <c r="O187" t="n">
+        <v>1</v>
+      </c>
+      <c r="P187" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>5</v>
+      </c>
+      <c r="R187" t="n">
+        <v>1</v>
+      </c>
+      <c r="S187" t="n">
+        <v>4</v>
+      </c>
+      <c r="T187" t="n">
+        <v>5</v>
+      </c>
+      <c r="U187" t="n">
+        <v>1</v>
+      </c>
+      <c r="V187" t="n">
+        <v>0</v>
+      </c>
+      <c r="W187" t="n">
+        <v>1</v>
+      </c>
+      <c r="X187" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="188">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -20110,115 +20110,220 @@
       <c r="A187" s="5" t="n">
         <v>46164</v>
       </c>
-      <c r="B187" t="n">
+      <c r="B187" s="8" t="n">
         <v>13765041.94381004</v>
       </c>
-      <c r="C187" t="n">
-        <v>1</v>
-      </c>
-      <c r="D187" t="n">
-        <v>1</v>
-      </c>
-      <c r="E187" t="n">
-        <v>1</v>
-      </c>
-      <c r="F187" t="n">
+      <c r="C187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="G187" t="n">
-        <v>1</v>
-      </c>
-      <c r="H187" t="n">
-        <v>1</v>
-      </c>
-      <c r="I187" t="n">
+      <c r="G187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I187" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="J187" t="n">
-        <v>3</v>
-      </c>
-      <c r="K187" t="n">
-        <v>0</v>
-      </c>
-      <c r="L187" t="n">
-        <v>1</v>
-      </c>
-      <c r="M187" t="n">
-        <v>1</v>
-      </c>
-      <c r="N187" t="n">
-        <v>2</v>
-      </c>
-      <c r="O187" t="n">
-        <v>1</v>
-      </c>
-      <c r="P187" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>5</v>
-      </c>
-      <c r="R187" t="n">
-        <v>1</v>
-      </c>
-      <c r="S187" t="n">
-        <v>4</v>
-      </c>
-      <c r="T187" t="n">
-        <v>5</v>
-      </c>
-      <c r="U187" t="n">
-        <v>1</v>
-      </c>
-      <c r="V187" t="n">
-        <v>0</v>
-      </c>
-      <c r="W187" t="n">
-        <v>1</v>
-      </c>
-      <c r="X187" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y187" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z187" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI187" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ187" t="n">
+      <c r="J187" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N187" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P187" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q187" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S187" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T187" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X187" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y187" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z187" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n">
         <v>46167</v>
+      </c>
+      <c r="B188" t="n">
+        <v>13833813.82381004</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" t="n">
+        <v>68</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1</v>
+      </c>
+      <c r="I188" t="n">
+        <v>9</v>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="n">
+        <v>1</v>
+      </c>
+      <c r="N188" t="n">
+        <v>2</v>
+      </c>
+      <c r="O188" t="n">
+        <v>1</v>
+      </c>
+      <c r="P188" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>5</v>
+      </c>
+      <c r="R188" t="n">
+        <v>1</v>
+      </c>
+      <c r="S188" t="n">
+        <v>4</v>
+      </c>
+      <c r="T188" t="n">
+        <v>5</v>
+      </c>
+      <c r="U188" t="n">
+        <v>1</v>
+      </c>
+      <c r="V188" t="n">
+        <v>0</v>
+      </c>
+      <c r="W188" t="n">
+        <v>1</v>
+      </c>
+      <c r="X188" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="189">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -21437,115 +21437,115 @@
       <c r="A197" s="5" t="n">
         <v>46178</v>
       </c>
-      <c r="B197" t="n">
+      <c r="B197" s="0" t="n">
         <v>13819078.66131004</v>
       </c>
-      <c r="C197" t="n">
-        <v>1</v>
-      </c>
-      <c r="D197" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" t="n">
+      <c r="C197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="G197" t="n">
-        <v>1</v>
-      </c>
-      <c r="H197" t="n">
-        <v>1</v>
-      </c>
-      <c r="I197" t="n">
+      <c r="G197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="J197" t="n">
-        <v>3</v>
-      </c>
-      <c r="K197" t="n">
-        <v>1</v>
-      </c>
-      <c r="L197" t="n">
-        <v>1</v>
-      </c>
-      <c r="M197" t="n">
-        <v>1</v>
-      </c>
-      <c r="N197" t="n">
-        <v>2</v>
-      </c>
-      <c r="O197" t="n">
-        <v>1</v>
-      </c>
-      <c r="P197" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q197" t="n">
-        <v>5</v>
-      </c>
-      <c r="R197" t="n">
-        <v>1</v>
-      </c>
-      <c r="S197" t="n">
-        <v>4</v>
-      </c>
-      <c r="T197" t="n">
-        <v>5</v>
-      </c>
-      <c r="U197" t="n">
-        <v>1</v>
-      </c>
-      <c r="V197" t="n">
-        <v>0</v>
-      </c>
-      <c r="W197" t="n">
-        <v>1</v>
-      </c>
-      <c r="X197" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y197" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK197" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL197" t="n">
+      <c r="J197" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N197" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="O197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P197" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q197" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="R197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S197" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="T197" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="U197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X197" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y197" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL197" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21557,6 +21557,117 @@
     <row r="199">
       <c r="A199" s="5" t="n">
         <v>46182</v>
+      </c>
+      <c r="B199" t="n">
+        <v>13548213.08131004</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>73</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1</v>
+      </c>
+      <c r="I199" t="n">
+        <v>8</v>
+      </c>
+      <c r="J199" t="n">
+        <v>3</v>
+      </c>
+      <c r="K199" t="n">
+        <v>1</v>
+      </c>
+      <c r="L199" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="n">
+        <v>1</v>
+      </c>
+      <c r="N199" t="n">
+        <v>2</v>
+      </c>
+      <c r="O199" t="n">
+        <v>1</v>
+      </c>
+      <c r="P199" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>4</v>
+      </c>
+      <c r="R199" t="n">
+        <v>1</v>
+      </c>
+      <c r="S199" t="n">
+        <v>4</v>
+      </c>
+      <c r="T199" t="n">
+        <v>5</v>
+      </c>
+      <c r="U199" t="n">
+        <v>1</v>
+      </c>
+      <c r="V199" t="n">
+        <v>0</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1</v>
+      </c>
+      <c r="X199" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="200">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -23935,115 +23935,115 @@
       <c r="A208" s="5" t="n">
         <v>46196</v>
       </c>
-      <c r="B208" t="n">
-        <v>13807523.12123004</v>
-      </c>
-      <c r="C208" t="n">
-        <v>1</v>
-      </c>
-      <c r="D208" t="n">
-        <v>1</v>
-      </c>
-      <c r="E208" t="n">
-        <v>1</v>
-      </c>
-      <c r="F208" t="n">
-        <v>80</v>
-      </c>
-      <c r="G208" t="n">
-        <v>1</v>
-      </c>
-      <c r="H208" t="n">
-        <v>1</v>
-      </c>
-      <c r="I208" t="n">
+      <c r="B208" s="0" t="n">
+        <v>13536690.12123004</v>
+      </c>
+      <c r="C208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" s="0" t="n">
+        <v>81</v>
+      </c>
+      <c r="G208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I208" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="J208" t="n">
-        <v>3</v>
-      </c>
-      <c r="K208" t="n">
-        <v>1</v>
-      </c>
-      <c r="L208" t="n">
-        <v>1</v>
-      </c>
-      <c r="M208" t="n">
-        <v>1</v>
-      </c>
-      <c r="N208" t="n">
-        <v>2</v>
-      </c>
-      <c r="O208" t="n">
-        <v>1</v>
-      </c>
-      <c r="P208" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>4</v>
-      </c>
-      <c r="R208" t="n">
-        <v>1</v>
-      </c>
-      <c r="S208" t="n">
-        <v>4</v>
-      </c>
-      <c r="T208" t="n">
-        <v>5</v>
-      </c>
-      <c r="U208" t="n">
-        <v>1</v>
-      </c>
-      <c r="V208" t="n">
-        <v>0</v>
-      </c>
-      <c r="W208" t="n">
-        <v>1</v>
-      </c>
-      <c r="X208" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y208" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL208" t="n">
+      <c r="J208" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P208" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q208" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="R208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S208" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="T208" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="U208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="V208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X208" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y208" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL208" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\实习相关\东财FOF量化\课题\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8937FD-7CDA-4A11-A11A-7462BD58C8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1AFEBD-87C7-47AB-9CEF-6D659303A016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1AFEBD-87C7-47AB-9CEF-6D659303A016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7882FF5B-D1CB-4B12-ABE8-27B355397369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,11 @@
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -420,6 +425,12 @@
     <t>2025-12-31</t>
   </si>
   <si>
+    <t>GFEX.LC</t>
+  </si>
+  <si>
+    <t>SHFE.SN</t>
+  </si>
+  <si>
     <t>名称</t>
   </si>
   <si>
@@ -514,19 +525,9 @@
   </si>
   <si>
     <t>碳酸锂</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GFEX.LC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>锡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHFE.SN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -537,21 +538,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -575,38 +576,18 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{313CD1FF-4875-49B6-AB43-9E069E4E7C3A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -622,9 +603,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -638,38 +619,38 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="Yu Gothic Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -699,12 +680,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="Yu Gothic"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -734,40 +715,66 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -781,38 +788,20 @@
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
@@ -866,139 +855,143 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AL339"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.06640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1328125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="4" t="s">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="4" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="4" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="4" t="s">
+      <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="AK1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2">
         <v>10004885</v>
       </c>
       <c r="C2">
@@ -1110,11 +1103,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3">
         <v>10073446.370549999</v>
       </c>
       <c r="C3">
@@ -1226,11 +1219,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>9950664.3705499973</v>
       </c>
       <c r="C4">
@@ -1342,8 +1335,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C5">
@@ -1455,16 +1448,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>9928663.0175500046</v>
       </c>
       <c r="C7">
@@ -1576,11 +1569,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>9880580.0175499972</v>
       </c>
       <c r="C8">
@@ -1692,11 +1685,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>9940433.7735499963</v>
       </c>
       <c r="C9">
@@ -1808,11 +1801,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10">
         <v>9975825.7735499963</v>
       </c>
       <c r="C10">
@@ -1924,11 +1917,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>10194813.77355</v>
       </c>
       <c r="C11">
@@ -2040,11 +2033,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12">
         <v>10192355.12855</v>
       </c>
       <c r="C12">
@@ -2156,11 +2149,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13">
         <v>10100168.62855</v>
       </c>
       <c r="C13">
@@ -2272,11 +2265,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14">
         <v>10100685.62855</v>
       </c>
       <c r="C14">
@@ -2388,11 +2381,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A15" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15">
         <v>10134708.12855</v>
       </c>
       <c r="C15">
@@ -2504,11 +2497,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16">
         <v>10262262.57855</v>
       </c>
       <c r="C16">
@@ -2620,11 +2613,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17">
         <v>10217582.57855</v>
       </c>
       <c r="C17">
@@ -2736,11 +2729,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18">
         <v>10283719.57855</v>
       </c>
       <c r="C18">
@@ -2852,11 +2845,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A19" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19">
         <v>10206815.07855</v>
       </c>
       <c r="C19">
@@ -2968,11 +2961,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20">
         <v>10265776.57855</v>
       </c>
       <c r="C20">
@@ -3084,11 +3077,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A21" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21">
         <v>10283653.57855</v>
       </c>
       <c r="C21">
@@ -3200,11 +3193,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22">
         <v>10242921.57855</v>
       </c>
       <c r="C22">
@@ -3316,11 +3309,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23">
         <v>10114862.57855</v>
       </c>
       <c r="C23">
@@ -3432,11 +3425,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A24" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24">
         <v>10288912.57855</v>
       </c>
       <c r="C24">
@@ -3548,11 +3541,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A25" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25">
         <v>10339664.07855</v>
       </c>
       <c r="C25">
@@ -3664,11 +3657,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A26" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26">
         <v>10400420.57855</v>
       </c>
       <c r="C26">
@@ -3780,11 +3773,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A27" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27">
         <v>10591550.951549999</v>
       </c>
       <c r="C27">
@@ -3896,11 +3889,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A28" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28">
         <v>10673491.451549999</v>
       </c>
       <c r="C28">
@@ -4012,11 +4005,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A29" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29">
         <v>10475024.648150001</v>
       </c>
       <c r="C29">
@@ -4128,11 +4121,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A30" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30">
         <v>10386227.499150001</v>
       </c>
       <c r="C30">
@@ -4244,11 +4237,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A31" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31">
         <v>10537979.089149989</v>
       </c>
       <c r="C31">
@@ -4360,11 +4353,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32">
         <v>10352868.215150001</v>
       </c>
       <c r="C32">
@@ -4476,11 +4469,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33">
         <v>10473991.715150001</v>
       </c>
       <c r="C33">
@@ -4592,11 +4585,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A34" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34">
         <v>10497346.715150001</v>
       </c>
       <c r="C34">
@@ -4708,11 +4701,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35">
         <v>10464138.715150001</v>
       </c>
       <c r="C35">
@@ -4824,11 +4817,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36">
         <v>10577437.215149989</v>
       </c>
       <c r="C36">
@@ -4940,20 +4933,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A37" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="7">
-        <f>AVERAGE(B36,B38)</f>
+      <c r="B37">
         <v>10805755.670149995</v>
       </c>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A38" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38">
         <v>11034074.125150001</v>
       </c>
       <c r="C38">
@@ -5065,11 +5057,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39">
         <v>10841837.125150001</v>
       </c>
       <c r="C39">
@@ -5181,11 +5173,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A40" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40">
         <v>10922107.125150001</v>
       </c>
       <c r="C40">
@@ -5297,11 +5289,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A41" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41">
         <v>10867610.125150001</v>
       </c>
       <c r="C41">
@@ -5413,11 +5405,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A42" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42">
         <v>10994867.940400001</v>
       </c>
       <c r="C42">
@@ -5529,11 +5521,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43">
         <v>11014020.203400001</v>
       </c>
       <c r="C43">
@@ -5645,11 +5637,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A44" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44">
         <v>11008878.4109</v>
       </c>
       <c r="C44">
@@ -5761,11 +5753,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45">
         <v>10835939.8189</v>
       </c>
       <c r="C45">
@@ -5877,11 +5869,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46">
         <v>11021125.3189</v>
       </c>
       <c r="C46">
@@ -5993,11 +5985,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A47" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47">
         <v>10902542.556399999</v>
       </c>
       <c r="C47">
@@ -6109,11 +6101,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A48" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48">
         <v>10898407.556399999</v>
       </c>
       <c r="C48">
@@ -6225,11 +6217,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A49" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49">
         <v>10946930.732399991</v>
       </c>
       <c r="C49">
@@ -6341,11 +6333,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A50" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50">
         <v>11129609.5319</v>
       </c>
       <c r="C50">
@@ -6457,11 +6449,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A51" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51">
         <v>11099036.786900001</v>
       </c>
       <c r="C51">
@@ -6573,11 +6565,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+    <row r="52" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A52" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52">
         <v>11338113.941899991</v>
       </c>
       <c r="C52">
@@ -6689,11 +6681,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+    <row r="53" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A53" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53">
         <v>11273454.42939999</v>
       </c>
       <c r="C53">
@@ -6805,11 +6797,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
+    <row r="54" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A54" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54">
         <v>11287742.2634</v>
       </c>
       <c r="C54">
@@ -6921,11 +6913,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
+    <row r="55" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A55" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55">
         <v>11307206.57940001</v>
       </c>
       <c r="C55">
@@ -7037,11 +7029,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
+    <row r="56" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A56" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56">
         <v>11134776.1494</v>
       </c>
       <c r="C56">
@@ -7153,11 +7145,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
+    <row r="57" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A57" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57">
         <v>11112131.76190001</v>
       </c>
       <c r="C57">
@@ -7269,11 +7261,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
+    <row r="58" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A58" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58">
         <v>11187923.7619</v>
       </c>
       <c r="C58">
@@ -7385,11 +7377,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
+    <row r="59" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A59" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59">
         <v>11120916.7618999</v>
       </c>
       <c r="C59">
@@ -7501,11 +7493,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
+    <row r="60" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A60" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60">
         <v>11242074.5569</v>
       </c>
       <c r="C60">
@@ -7617,11 +7609,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
+    <row r="61" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A61" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61">
         <v>11240608.9419</v>
       </c>
       <c r="C61">
@@ -7733,11 +7725,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
+    <row r="62" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A62" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62">
         <v>11301255.9419</v>
       </c>
       <c r="C62">
@@ -7849,11 +7841,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
+    <row r="63" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A63" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63">
         <v>11359740.5319</v>
       </c>
       <c r="C63">
@@ -7965,11 +7957,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
+    <row r="64" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A64" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64">
         <v>11230872.45440001</v>
       </c>
       <c r="C64">
@@ -8081,11 +8073,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
+    <row r="65" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A65" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65">
         <v>11164587.372400001</v>
       </c>
       <c r="C65">
@@ -8197,11 +8189,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
+    <row r="66" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A66" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66">
         <v>11061010.769900011</v>
       </c>
       <c r="C66">
@@ -8313,11 +8305,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
+    <row r="67" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A67" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67">
         <v>11116226.32990001</v>
       </c>
       <c r="C67">
@@ -8429,11 +8421,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
+    <row r="68" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A68" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68">
         <v>11034265.97890001</v>
       </c>
       <c r="C68">
@@ -8545,11 +8537,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
+    <row r="69" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69">
         <v>10774873.17890002</v>
       </c>
       <c r="C69">
@@ -8661,11 +8653,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="70" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70">
         <v>10908612.688899999</v>
       </c>
       <c r="C70">
@@ -8777,11 +8769,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+    <row r="71" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A71" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71">
         <v>10946352.178900011</v>
       </c>
       <c r="C71">
@@ -8893,11 +8885,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+    <row r="72" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A72" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72">
         <v>10744433.577900009</v>
       </c>
       <c r="C72">
@@ -9009,11 +9001,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+    <row r="73" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A73" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B73" s="7">
+      <c r="B73">
         <v>10814085.308400011</v>
       </c>
       <c r="C73">
@@ -9125,11 +9117,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+    <row r="74" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A74" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74">
         <v>10956937.042900009</v>
       </c>
       <c r="C74">
@@ -9241,11 +9233,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
+    <row r="75" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A75" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75">
         <v>11151750.20290002</v>
       </c>
       <c r="C75">
@@ -9357,11 +9349,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+    <row r="76" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A76" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76">
         <v>11080289.2379</v>
       </c>
       <c r="C76">
@@ -9473,11 +9465,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+    <row r="77" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A77" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77">
         <v>11063655.60890002</v>
       </c>
       <c r="C77">
@@ -9589,11 +9581,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+    <row r="78" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A78" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78">
         <v>10866709.535900019</v>
       </c>
       <c r="C78">
@@ -9705,11 +9697,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
+    <row r="79" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A79" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79">
         <v>11066890.30740002</v>
       </c>
       <c r="C79">
@@ -9821,11 +9813,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+    <row r="80" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A80" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80">
         <v>11100820.64340001</v>
       </c>
       <c r="C80">
@@ -9937,11 +9929,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
+    <row r="81" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A81" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B81" s="7">
+      <c r="B81">
         <v>10965413.349400019</v>
       </c>
       <c r="C81">
@@ -10053,11 +10045,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
+    <row r="82" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A82" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B82" s="7">
+      <c r="B82">
         <v>11054158.947400009</v>
       </c>
       <c r="C82">
@@ -10169,11 +10161,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
+    <row r="83" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A83" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B83" s="7">
+      <c r="B83">
         <v>11047941.40465001</v>
       </c>
       <c r="C83">
@@ -10285,11 +10277,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
+    <row r="84" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A84" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84">
         <v>11091436.40465001</v>
       </c>
       <c r="C84">
@@ -10401,11 +10393,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
+    <row r="85" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A85" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B85" s="7">
+      <c r="B85">
         <v>11032493.40465001</v>
       </c>
       <c r="C85">
@@ -10517,11 +10509,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
+    <row r="86" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A86" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86">
         <v>10913705.77965001</v>
       </c>
       <c r="C86">
@@ -10633,11 +10625,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
+    <row r="87" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A87" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B87" s="7">
+      <c r="B87">
         <v>11095969.77965001</v>
       </c>
       <c r="C87">
@@ -10749,11 +10741,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
+    <row r="88" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A88" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88">
         <v>11130569.72783001</v>
       </c>
       <c r="C88">
@@ -10865,11 +10857,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
+    <row r="89" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A89" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B89" s="7">
+      <c r="B89">
         <v>11219463.608830011</v>
       </c>
       <c r="C89">
@@ -10981,11 +10973,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
+    <row r="90" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A90" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90">
         <v>11382396.268830011</v>
       </c>
       <c r="C90">
@@ -11097,11 +11089,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
+    <row r="91" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A91" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91">
         <v>11593908.463830009</v>
       </c>
       <c r="C91">
@@ -11213,11 +11205,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
+    <row r="92" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A92" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92">
         <v>11768617.177330021</v>
       </c>
       <c r="C92">
@@ -11329,11 +11321,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
+    <row r="93" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A93" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93">
         <v>11753551.547330011</v>
       </c>
       <c r="C93">
@@ -11445,11 +11437,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
+    <row r="94" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A94" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94">
         <v>11955538.88783001</v>
       </c>
       <c r="C94">
@@ -11561,11 +11553,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
+    <row r="95" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A95" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95">
         <v>11683700.38783</v>
       </c>
       <c r="C95">
@@ -11677,11 +11669,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
+    <row r="96" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A96" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96">
         <v>11646644.655830011</v>
       </c>
       <c r="C96">
@@ -11793,11 +11785,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
+    <row r="97" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A97" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97">
         <v>11513873.79283</v>
       </c>
       <c r="C97">
@@ -11909,11 +11901,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A98" s="5">
+    <row r="98" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A98" s="1">
         <v>46027</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98">
         <v>11715802.665829999</v>
       </c>
       <c r="C98">
@@ -12025,11 +12017,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A99" s="5">
+    <row r="99" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A99" s="1">
         <v>46028</v>
       </c>
-      <c r="B99" s="7">
+      <c r="B99">
         <v>11939244.552829999</v>
       </c>
       <c r="C99">
@@ -12141,11 +12133,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A100" s="5">
+    <row r="100" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A100" s="1">
         <v>46029</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100">
         <v>11918361.45483</v>
       </c>
       <c r="C100">
@@ -12257,11 +12249,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A101" s="5">
+    <row r="101" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A101" s="1">
         <v>46030</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101">
         <v>11874507.98683</v>
       </c>
       <c r="C101">
@@ -12373,11 +12365,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A102" s="5">
+    <row r="102" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A102" s="1">
         <v>46031</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102">
         <v>12080678.48683</v>
       </c>
       <c r="C102">
@@ -12489,8 +12481,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A103" s="5">
+    <row r="103" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A103" s="1">
         <v>46034</v>
       </c>
       <c r="B103">
@@ -12605,8 +12597,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A104" s="5">
+    <row r="104" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A104" s="1">
         <v>46035</v>
       </c>
       <c r="B104">
@@ -12721,8 +12713,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A105" s="5">
+    <row r="105" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A105" s="1">
         <v>46036</v>
       </c>
       <c r="B105">
@@ -12837,8 +12829,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A106" s="5">
+    <row r="106" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A106" s="1">
         <v>46037</v>
       </c>
       <c r="B106">
@@ -12953,8 +12945,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A107" s="5">
+    <row r="107" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A107" s="1">
         <v>46038</v>
       </c>
       <c r="B107">
@@ -13069,8 +13061,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A108" s="5">
+    <row r="108" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A108" s="1">
         <v>46041</v>
       </c>
       <c r="B108">
@@ -13185,8 +13177,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A109" s="5">
+    <row r="109" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A109" s="1">
         <v>46042</v>
       </c>
       <c r="B109">
@@ -13301,8 +13293,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A110" s="5">
+    <row r="110" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A110" s="1">
         <v>46043</v>
       </c>
       <c r="B110">
@@ -13417,8 +13409,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A111" s="5">
+    <row r="111" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A111" s="1">
         <v>46044</v>
       </c>
       <c r="B111">
@@ -13533,8 +13525,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A112" s="5">
+    <row r="112" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A112" s="1">
         <v>46045</v>
       </c>
       <c r="B112">
@@ -13649,8 +13641,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A113" s="5">
+    <row r="113" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A113" s="1">
         <v>46048</v>
       </c>
       <c r="B113">
@@ -13765,8 +13757,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A114" s="5">
+    <row r="114" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A114" s="1">
         <v>46049</v>
       </c>
       <c r="B114">
@@ -13881,8 +13873,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A115" s="5">
+    <row r="115" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A115" s="1">
         <v>46050</v>
       </c>
       <c r="B115">
@@ -13997,8 +13989,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A116" s="5">
+    <row r="116" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A116" s="1">
         <v>46051</v>
       </c>
       <c r="B116">
@@ -14113,8 +14105,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A117" s="5">
+    <row r="117" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A117" s="1">
         <v>46052</v>
       </c>
       <c r="B117">
@@ -14229,8 +14221,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A118" s="5">
+    <row r="118" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A118" s="1">
         <v>46055</v>
       </c>
       <c r="B118">
@@ -14345,8 +14337,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A119" s="5">
+    <row r="119" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A119" s="1">
         <v>46056</v>
       </c>
       <c r="B119">
@@ -14461,8 +14453,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A120" s="5">
+    <row r="120" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A120" s="1">
         <v>46057</v>
       </c>
       <c r="B120">
@@ -14577,8 +14569,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A121" s="5">
+    <row r="121" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A121" s="1">
         <v>46058</v>
       </c>
       <c r="B121">
@@ -14693,8 +14685,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A122" s="5">
+    <row r="122" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A122" s="1">
         <v>46059</v>
       </c>
       <c r="B122">
@@ -14809,8 +14801,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A123" s="5">
+    <row r="123" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A123" s="1">
         <v>46062</v>
       </c>
       <c r="B123">
@@ -14925,8 +14917,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A124" s="5">
+    <row r="124" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A124" s="1">
         <v>46063</v>
       </c>
       <c r="B124">
@@ -15041,8 +15033,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A125" s="5">
+    <row r="125" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A125" s="1">
         <v>46064</v>
       </c>
       <c r="B125">
@@ -15157,8 +15149,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A126" s="5">
+    <row r="126" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A126" s="1">
         <v>46065</v>
       </c>
       <c r="B126">
@@ -15273,13 +15265,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A127" s="5">
+    <row r="127" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A127" s="1">
         <v>46066</v>
       </c>
     </row>
-    <row r="128" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A128" s="5">
+    <row r="128" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A128" s="1">
         <v>46077</v>
       </c>
       <c r="B128">
@@ -15394,8 +15386,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A129" s="5">
+    <row r="129" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A129" s="1">
         <v>46078</v>
       </c>
       <c r="B129">
@@ -15510,8 +15502,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A130" s="5">
+    <row r="130" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A130" s="1">
         <v>46079</v>
       </c>
       <c r="B130">
@@ -15626,8 +15618,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A131" s="5">
+    <row r="131" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A131" s="1">
         <v>46080</v>
       </c>
       <c r="B131">
@@ -15742,8 +15734,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A132" s="5">
+    <row r="132" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A132" s="1">
         <v>46083</v>
       </c>
       <c r="B132">
@@ -15858,8 +15850,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A133" s="5">
+    <row r="133" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A133" s="1">
         <v>46084</v>
       </c>
       <c r="B133">
@@ -15974,8 +15966,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A134" s="5">
+    <row r="134" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A134" s="1">
         <v>46085</v>
       </c>
       <c r="B134">
@@ -16090,8 +16082,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A135" s="5">
+    <row r="135" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A135" s="1">
         <v>46086</v>
       </c>
       <c r="B135">
@@ -16206,8 +16198,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A136" s="5">
+    <row r="136" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A136" s="1">
         <v>46087</v>
       </c>
       <c r="B136">
@@ -16322,8 +16314,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A137" s="5">
+    <row r="137" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A137" s="1">
         <v>46090</v>
       </c>
       <c r="B137">
@@ -16438,8 +16430,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A138" s="5">
+    <row r="138" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A138" s="1">
         <v>46091</v>
       </c>
       <c r="B138">
@@ -16554,8 +16546,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A139" s="5">
+    <row r="139" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A139" s="1">
         <v>46092</v>
       </c>
       <c r="B139">
@@ -16670,8 +16662,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A140" s="5">
+    <row r="140" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A140" s="1">
         <v>46093</v>
       </c>
       <c r="B140">
@@ -16786,8 +16778,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A141" s="5">
+    <row r="141" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A141" s="1">
         <v>46094</v>
       </c>
       <c r="B141">
@@ -16902,8 +16894,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A142" s="5">
+    <row r="142" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A142" s="1">
         <v>46097</v>
       </c>
       <c r="B142">
@@ -17018,8 +17010,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A143" s="5">
+    <row r="143" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A143" s="1">
         <v>46098</v>
       </c>
       <c r="B143">
@@ -17134,8 +17126,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A144" s="5">
+    <row r="144" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A144" s="1">
         <v>46099</v>
       </c>
       <c r="B144">
@@ -17250,8 +17242,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A145" s="5">
+    <row r="145" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A145" s="1">
         <v>46100</v>
       </c>
       <c r="B145">
@@ -17366,8 +17358,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A146" s="5">
+    <row r="146" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A146" s="1">
         <v>46101</v>
       </c>
       <c r="B146">
@@ -17482,8 +17474,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A147" s="5">
+    <row r="147" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A147" s="1">
         <v>46104</v>
       </c>
       <c r="B147">
@@ -17598,8 +17590,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A148" s="5">
+    <row r="148" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A148" s="1">
         <v>46105</v>
       </c>
       <c r="B148">
@@ -17714,8 +17706,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A149" s="5">
+    <row r="149" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A149" s="1">
         <v>46106</v>
       </c>
       <c r="B149">
@@ -17830,8 +17822,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A150" s="5">
+    <row r="150" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A150" s="1">
         <v>46107</v>
       </c>
       <c r="B150">
@@ -17946,8 +17938,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A151" s="5">
+    <row r="151" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A151" s="1">
         <v>46108</v>
       </c>
       <c r="B151">
@@ -18062,8 +18054,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A152" s="5">
+    <row r="152" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A152" s="1">
         <v>46111</v>
       </c>
       <c r="B152">
@@ -18178,8 +18170,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A153" s="5">
+    <row r="153" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A153" s="1">
         <v>46112</v>
       </c>
       <c r="B153">
@@ -18294,8 +18286,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A154" s="5">
+    <row r="154" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A154" s="1">
         <v>46113</v>
       </c>
       <c r="B154">
@@ -18410,8 +18402,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A155" s="5">
+    <row r="155" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A155" s="1">
         <v>46114</v>
       </c>
       <c r="B155">
@@ -18526,11 +18518,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A156" s="5">
+    <row r="156" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A156" s="1">
         <v>46115</v>
       </c>
-      <c r="B156" s="7">
+      <c r="B156">
         <v>12836356.675310001</v>
       </c>
       <c r="C156">
@@ -18642,8 +18634,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A157" s="5">
+    <row r="157" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A157" s="1">
         <v>46119</v>
       </c>
       <c r="B157">
@@ -18758,8 +18750,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A158" s="5">
+    <row r="158" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A158" s="1">
         <v>46120</v>
       </c>
       <c r="B158">
@@ -18874,8 +18866,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A159" s="5">
+    <row r="159" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A159" s="1">
         <v>46121</v>
       </c>
       <c r="B159">
@@ -18990,8 +18982,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A160" s="5">
+    <row r="160" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A160" s="1">
         <v>46122</v>
       </c>
       <c r="B160">
@@ -19106,8 +19098,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A161" s="5">
+    <row r="161" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A161" s="1">
         <v>46125</v>
       </c>
       <c r="B161">
@@ -19222,8 +19214,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A162" s="5">
+    <row r="162" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A162" s="1">
         <v>46126</v>
       </c>
       <c r="B162">
@@ -19338,8 +19330,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A163" s="5">
+    <row r="163" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A163" s="1">
         <v>46127</v>
       </c>
       <c r="B163">
@@ -19454,8 +19446,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A164" s="5">
+    <row r="164" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A164" s="1">
         <v>46128</v>
       </c>
       <c r="B164">
@@ -19570,8 +19562,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A165" s="5">
+    <row r="165" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A165" s="1">
         <v>46129</v>
       </c>
       <c r="B165">
@@ -19686,8 +19678,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A166" s="5">
+    <row r="166" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A166" s="1">
         <v>46132</v>
       </c>
       <c r="B166">
@@ -19802,8 +19794,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A167" s="5">
+    <row r="167" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A167" s="1">
         <v>46133</v>
       </c>
       <c r="B167">
@@ -19918,8 +19910,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A168" s="5">
+    <row r="168" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A168" s="1">
         <v>46134</v>
       </c>
       <c r="B168">
@@ -20034,8 +20026,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A169" s="5">
+    <row r="169" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A169" s="1">
         <v>46135</v>
       </c>
       <c r="B169">
@@ -20150,8 +20142,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A170" s="5">
+    <row r="170" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A170" s="1">
         <v>46136</v>
       </c>
       <c r="B170">
@@ -20266,8 +20258,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A171" s="5">
+    <row r="171" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A171" s="1">
         <v>46139</v>
       </c>
       <c r="B171">
@@ -20382,11 +20374,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A172" s="5">
+    <row r="172" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A172" s="1">
         <v>46140</v>
       </c>
-      <c r="B172" s="2">
+      <c r="B172">
         <v>13436995.499810001</v>
       </c>
       <c r="C172">
@@ -20498,8 +20490,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A173" s="5">
+    <row r="173" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A173" s="1">
         <v>46141</v>
       </c>
       <c r="B173">
@@ -20614,14 +20606,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A174" s="5">
+    <row r="174" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A174" s="1">
         <v>46142</v>
       </c>
-      <c r="B174" s="7">
+      <c r="B174">
         <v>13563229.499810001</v>
       </c>
-      <c r="C174" s="2">
+      <c r="C174">
         <v>1</v>
       </c>
       <c r="D174">
@@ -20730,8 +20722,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A175" s="5">
+    <row r="175" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A175" s="1">
         <v>46148</v>
       </c>
       <c r="B175">
@@ -20846,8 +20838,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A176" s="5">
+    <row r="176" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A176" s="1">
         <v>46149</v>
       </c>
       <c r="B176">
@@ -20962,8 +20954,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A177" s="5">
+    <row r="177" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A177" s="1">
         <v>46150</v>
       </c>
       <c r="B177">
@@ -21078,8 +21070,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A178" s="5">
+    <row r="178" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A178" s="1">
         <v>46153</v>
       </c>
       <c r="B178">
@@ -21194,8 +21186,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A179" s="5">
+    <row r="179" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A179" s="1">
         <v>46154</v>
       </c>
       <c r="B179">
@@ -21310,8 +21302,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A180" s="5">
+    <row r="180" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A180" s="1">
         <v>46155</v>
       </c>
       <c r="B180">
@@ -21426,8 +21418,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A181" s="5">
+    <row r="181" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A181" s="1">
         <v>46156</v>
       </c>
       <c r="B181">
@@ -21542,8 +21534,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A182" s="5">
+    <row r="182" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A182" s="1">
         <v>46157</v>
       </c>
       <c r="B182">
@@ -21658,11 +21650,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A183" s="5">
+    <row r="183" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A183" s="1">
         <v>46160</v>
       </c>
-      <c r="B183" s="6">
+      <c r="B183">
         <v>13880797.103809999</v>
       </c>
       <c r="C183">
@@ -21774,11 +21766,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A184" s="5">
+    <row r="184" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A184" s="1">
         <v>46161</v>
       </c>
-      <c r="B184" s="6">
+      <c r="B184">
         <v>14012302.12881</v>
       </c>
       <c r="C184">
@@ -21890,11 +21882,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A185" s="5">
+    <row r="185" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A185" s="1">
         <v>46162</v>
       </c>
-      <c r="B185" s="6">
+      <c r="B185">
         <v>13979272.12881</v>
       </c>
       <c r="C185">
@@ -22006,11 +21998,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A186" s="5">
+    <row r="186" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A186" s="1">
         <v>46163</v>
       </c>
-      <c r="B186" s="2">
+      <c r="B186">
         <v>13742692.12881</v>
       </c>
       <c r="C186">
@@ -22122,8 +22114,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A187" s="5">
+    <row r="187" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A187" s="1">
         <v>46164</v>
       </c>
       <c r="B187">
@@ -22238,8 +22230,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A188" s="5">
+    <row r="188" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A188" s="1">
         <v>46167</v>
       </c>
       <c r="B188">
@@ -22354,11 +22346,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A189" s="5">
+    <row r="189" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A189" s="1">
         <v>46168</v>
       </c>
-      <c r="B189" s="6">
+      <c r="B189">
         <v>13811498.82381</v>
       </c>
       <c r="C189">
@@ -22470,11 +22462,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A190" s="5">
+    <row r="190" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A190" s="1">
         <v>46169</v>
       </c>
-      <c r="B190" s="6">
+      <c r="B190">
         <v>13798510.898809999</v>
       </c>
       <c r="C190">
@@ -22586,11 +22578,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A191" s="5">
+    <row r="191" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A191" s="1">
         <v>46170</v>
       </c>
-      <c r="B191" s="6">
+      <c r="B191">
         <v>13861443.66131</v>
       </c>
       <c r="C191">
@@ -22702,14 +22694,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A192" s="5">
+    <row r="192" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A192" s="1">
         <v>46171</v>
       </c>
-      <c r="B192" s="7">
+      <c r="B192">
         <v>13875543.66131</v>
       </c>
-      <c r="C192" s="2">
+      <c r="C192">
         <v>1</v>
       </c>
       <c r="D192">
@@ -22818,14 +22810,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A193" s="5">
+    <row r="193" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A193" s="1">
         <v>46174</v>
       </c>
-      <c r="B193" s="7">
+      <c r="B193">
         <v>13882698.66131</v>
       </c>
-      <c r="C193" s="2">
+      <c r="C193">
         <v>1</v>
       </c>
       <c r="D193">
@@ -22934,14 +22926,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A194" s="5">
+    <row r="194" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A194" s="1">
         <v>46175</v>
       </c>
-      <c r="B194" s="7">
+      <c r="B194">
         <v>13998043.66131</v>
       </c>
-      <c r="C194" s="2">
+      <c r="C194">
         <v>1</v>
       </c>
       <c r="D194">
@@ -23050,20 +23042,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A195" s="5">
+    <row r="195" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A195" s="1">
         <v>46176</v>
       </c>
-      <c r="C195" s="2"/>
-    </row>
-    <row r="196" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A196" s="5">
+    </row>
+    <row r="196" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A196" s="1">
         <v>46177</v>
       </c>
-      <c r="B196" s="7">
+      <c r="B196">
         <v>13955898.66131</v>
       </c>
-      <c r="C196" s="2">
+      <c r="C196">
         <v>1</v>
       </c>
       <c r="D196">
@@ -23172,11 +23163,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A197" s="5">
+    <row r="197" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A197" s="1">
         <v>46178</v>
       </c>
-      <c r="B197" s="6">
+      <c r="B197">
         <v>13819078.66131</v>
       </c>
       <c r="C197">
@@ -23288,11 +23279,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A198" s="5">
+    <row r="198" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A198" s="1">
         <v>46181</v>
       </c>
-      <c r="B198" s="2">
+      <c r="B198">
         <v>13578368.58131</v>
       </c>
       <c r="C198">
@@ -23404,11 +23395,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A199" s="5">
+    <row r="199" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A199" s="1">
         <v>46182</v>
       </c>
-      <c r="B199" s="6">
+      <c r="B199">
         <v>13548213.08131</v>
       </c>
       <c r="C199">
@@ -23520,11 +23511,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A200" s="5">
+    <row r="200" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A200" s="1">
         <v>46183</v>
       </c>
-      <c r="B200" s="2">
+      <c r="B200">
         <v>13338150.08131</v>
       </c>
       <c r="C200">
@@ -23636,11 +23627,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A201" s="5">
+    <row r="201" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A201" s="1">
         <v>46184</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201">
         <v>13246720.08131</v>
       </c>
       <c r="C201">
@@ -23752,11 +23743,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A202" s="5">
+    <row r="202" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A202" s="1">
         <v>46185</v>
       </c>
-      <c r="B202" s="2">
+      <c r="B202">
         <v>13353149.08131</v>
       </c>
       <c r="C202">
@@ -23868,11 +23859,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A203" s="5">
+    <row r="203" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A203" s="1">
         <v>46188</v>
       </c>
-      <c r="B203" s="2">
+      <c r="B203">
         <v>13524441.08131</v>
       </c>
       <c r="C203">
@@ -23984,11 +23975,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A204" s="5">
+    <row r="204" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A204" s="1">
         <v>46189</v>
       </c>
-      <c r="B204" s="2">
+      <c r="B204">
         <v>13653311.08131</v>
       </c>
       <c r="C204">
@@ -24018,7 +24009,7 @@
       <c r="K204">
         <v>1</v>
       </c>
-      <c r="L204" s="2">
+      <c r="L204">
         <v>1</v>
       </c>
       <c r="M204">
@@ -24100,8 +24091,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A205" s="5">
+    <row r="205" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A205" s="1">
         <v>46190</v>
       </c>
       <c r="B205">
@@ -24216,8 +24207,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A206" s="5">
+    <row r="206" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A206" s="1">
         <v>46191</v>
       </c>
       <c r="B206">
@@ -24332,8 +24323,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A207" s="5">
+    <row r="207" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A207" s="1">
         <v>46195</v>
       </c>
       <c r="B207">
@@ -24448,11 +24439,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A208" s="5">
+    <row r="208" spans="1:38" x14ac:dyDescent="0.4">
+      <c r="A208" s="1">
         <v>46196</v>
       </c>
-      <c r="B208" s="6">
+      <c r="B208">
         <v>13536690.121230001</v>
       </c>
       <c r="C208">
@@ -24564,679 +24555,678 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A209" s="5">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A209" s="1">
         <v>46197</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A210" s="5">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A210" s="1">
         <v>46198</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A211" s="5">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A211" s="1">
         <v>46199</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A212" s="5">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A212" s="1">
         <v>46202</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A213" s="5">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A213" s="1">
         <v>46203</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A214" s="5">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A214" s="1">
         <v>46204</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A215" s="5">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A215" s="1">
         <v>46205</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A216" s="5">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A216" s="1">
         <v>46206</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A217" s="5">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A217" s="1">
         <v>46209</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A218" s="5">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A218" s="1">
         <v>46210</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A219" s="5">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A219" s="1">
         <v>46211</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A220" s="5">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A220" s="1">
         <v>46212</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A221" s="5">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A221" s="1">
         <v>46213</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A222" s="5">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A222" s="1">
         <v>46216</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A223" s="5">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A223" s="1">
         <v>46217</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A224" s="5">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A224" s="1">
         <v>46218</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A225" s="5">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A225" s="1">
         <v>46219</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A226" s="5">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A226" s="1">
         <v>46220</v>
       </c>
     </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A227" s="5">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A227" s="1">
         <v>46223</v>
       </c>
     </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A228" s="5">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A228" s="1">
         <v>46224</v>
       </c>
     </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A229" s="5">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A229" s="1">
         <v>46225</v>
       </c>
     </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A230" s="5">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A230" s="1">
         <v>46226</v>
       </c>
     </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A231" s="5">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A231" s="1">
         <v>46227</v>
       </c>
     </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A232" s="5">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A232" s="1">
         <v>46230</v>
       </c>
     </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A233" s="5">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A233" s="1">
         <v>46231</v>
       </c>
     </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A234" s="5">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A234" s="1">
         <v>46232</v>
       </c>
     </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A235" s="5">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A235" s="1">
         <v>46233</v>
       </c>
     </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A236" s="5">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A236" s="1">
         <v>46234</v>
       </c>
     </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A237" s="5">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A237" s="1">
         <v>46237</v>
       </c>
     </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A238" s="5">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A238" s="1">
         <v>46238</v>
       </c>
     </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A239" s="5">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A239" s="1">
         <v>46239</v>
       </c>
     </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A240" s="5">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A240" s="1">
         <v>46240</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A241" s="5">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A241" s="1">
         <v>46241</v>
       </c>
     </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A242" s="5">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A242" s="1">
         <v>46244</v>
       </c>
     </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A243" s="5">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A243" s="1">
         <v>46245</v>
       </c>
     </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A244" s="5">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A244" s="1">
         <v>46246</v>
       </c>
     </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A245" s="5">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A245" s="1">
         <v>46247</v>
       </c>
     </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A246" s="5">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A246" s="1">
         <v>46248</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A247" s="5">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A247" s="1">
         <v>46251</v>
       </c>
     </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A248" s="5">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A248" s="1">
         <v>46252</v>
       </c>
     </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A249" s="5">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A249" s="1">
         <v>46253</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A250" s="5">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A250" s="1">
         <v>46254</v>
       </c>
     </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A251" s="5">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A251" s="1">
         <v>46255</v>
       </c>
     </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A252" s="5">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A252" s="1">
         <v>46258</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A253" s="5">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A253" s="1">
         <v>46259</v>
       </c>
     </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A254" s="5">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A254" s="1">
         <v>46260</v>
       </c>
     </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A255" s="5">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A255" s="1">
         <v>46261</v>
       </c>
     </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A256" s="5">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A256" s="1">
         <v>46262</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A257" s="5">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A257" s="1">
         <v>46265</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A258" s="5">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A258" s="1">
         <v>46266</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A259" s="5">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A259" s="1">
         <v>46267</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A260" s="5">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A260" s="1">
         <v>46268</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A261" s="5">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A261" s="1">
         <v>46269</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A262" s="5">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A262" s="1">
         <v>46272</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A263" s="5">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A263" s="1">
         <v>46273</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A264" s="5">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A264" s="1">
         <v>46274</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A265" s="5">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A265" s="1">
         <v>46275</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A266" s="5">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A266" s="1">
         <v>46276</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A267" s="5">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A267" s="1">
         <v>46279</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A268" s="5">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A268" s="1">
         <v>46280</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A269" s="5">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A269" s="1">
         <v>46281</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A270" s="5">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A270" s="1">
         <v>46282</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A271" s="5">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A271" s="1">
         <v>46283</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A272" s="5">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A272" s="1">
         <v>46286</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A273" s="5">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A273" s="1">
         <v>46287</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A274" s="5">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A274" s="1">
         <v>46288</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A275" s="5">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A275" s="1">
         <v>46289</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A276" s="5">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A276" s="1">
         <v>46293</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A277" s="5">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A277" s="1">
         <v>46294</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A278" s="5">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A278" s="1">
         <v>46295</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A279" s="5">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A279" s="1">
         <v>46303</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A280" s="5">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A280" s="1">
         <v>46304</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A281" s="5">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A281" s="1">
         <v>46307</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A282" s="5">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A282" s="1">
         <v>46308</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A283" s="5">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A283" s="1">
         <v>46309</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A284" s="5">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A284" s="1">
         <v>46310</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A285" s="5">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A285" s="1">
         <v>46311</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A286" s="5">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A286" s="1">
         <v>46314</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A287" s="5">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A287" s="1">
         <v>46315</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A288" s="5">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A288" s="1">
         <v>46316</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A289" s="5">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A289" s="1">
         <v>46317</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A290" s="5">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A290" s="1">
         <v>46318</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A291" s="5">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A291" s="1">
         <v>46321</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A292" s="5">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A292" s="1">
         <v>46322</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A293" s="5">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A293" s="1">
         <v>46323</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A294" s="5">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A294" s="1">
         <v>46324</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A295" s="5">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A295" s="1">
         <v>46325</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A296" s="5">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A296" s="1">
         <v>46328</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A297" s="5">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A297" s="1">
         <v>46329</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A298" s="5">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A298" s="1">
         <v>46330</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A299" s="5">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A299" s="1">
         <v>46331</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A300" s="5">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A300" s="1">
         <v>46332</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A301" s="5">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A301" s="1">
         <v>46335</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A302" s="5">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A302" s="1">
         <v>46336</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A303" s="5">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A303" s="1">
         <v>46337</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A304" s="5">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A304" s="1">
         <v>46338</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A305" s="5">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A305" s="1">
         <v>46339</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A306" s="5">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A306" s="1">
         <v>46342</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A307" s="5">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A307" s="1">
         <v>46343</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A308" s="5">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A308" s="1">
         <v>46344</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A309" s="5">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A309" s="1">
         <v>46345</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A310" s="5">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A310" s="1">
         <v>46346</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A311" s="5">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A311" s="1">
         <v>46349</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A312" s="5">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A312" s="1">
         <v>46350</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A313" s="5">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A313" s="1">
         <v>46351</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A314" s="5">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A314" s="1">
         <v>46352</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A315" s="5">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A315" s="1">
         <v>46353</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A316" s="5">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A316" s="1">
         <v>46356</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A317" s="5">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A317" s="1">
         <v>46357</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A318" s="5">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A318" s="1">
         <v>46358</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A319" s="5">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A319" s="1">
         <v>46359</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A320" s="5">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A320" s="1">
         <v>46360</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A321" s="5">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A321" s="1">
         <v>46363</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A322" s="5">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A322" s="1">
         <v>46364</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A323" s="5">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A323" s="1">
         <v>46365</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A324" s="5">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A324" s="1">
         <v>46366</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A325" s="5">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A325" s="1">
         <v>46367</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A326" s="5">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A326" s="1">
         <v>46370</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A327" s="5">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A327" s="1">
         <v>46371</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A328" s="5">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A328" s="1">
         <v>46372</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A329" s="5">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A329" s="1">
         <v>46373</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A330" s="5">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A330" s="1">
         <v>46374</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A331" s="5">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A331" s="1">
         <v>46377</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A332" s="5">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A332" s="1">
         <v>46378</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A333" s="5">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A333" s="1">
         <v>46379</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A334" s="5">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A334" s="1">
         <v>46380</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A335" s="5">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A335" s="1">
         <v>46381</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A336" s="5">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A336" s="1">
         <v>46384</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A337" s="5">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A337" s="1">
         <v>46385</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A338" s="5">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A338" s="1">
         <v>46386</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A339" s="5">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A339" s="1">
         <v>46387</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88A424C6-6840-4809-BD95-0591528FAF59}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C1">
         <v>2026</v>
@@ -25275,9 +25265,9 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -25319,9 +25309,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -25363,9 +25353,9 @@
         <v>8.8987420086615796E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -25407,9 +25397,9 @@
         <v>7.5582594349350385E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -25451,9 +25441,9 @@
         <v>0.1190967209733966</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
@@ -25495,9 +25485,9 @@
         <v>6.4858733759538045E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -25539,9 +25529,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -25583,9 +25573,9 @@
         <v>2.2581975665085581E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -25627,9 +25617,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -25671,9 +25661,9 @@
         <v>4.0833161476593119E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
@@ -25715,9 +25705,9 @@
         <v>4.5679521550835232E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -25759,9 +25749,9 @@
         <v>9.5277376778717254E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
@@ -25803,9 +25793,9 @@
         <v>3.4955660961022893E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
@@ -25847,9 +25837,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B15" t="s">
         <v>20</v>
@@ -25891,9 +25881,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s">
         <v>21</v>
@@ -25935,9 +25925,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -25979,9 +25969,9 @@
         <v>4.8154258610022677E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
@@ -26023,9 +26013,9 @@
         <v>2.2685089709218391E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s">
         <v>24</v>
@@ -26067,9 +26057,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B20" t="s">
         <v>25</v>
@@ -26111,9 +26101,9 @@
         <v>3.1552897504640132E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
@@ -26155,9 +26145,9 @@
         <v>8.9709218395545465E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
@@ -26199,9 +26189,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
@@ -26243,9 +26233,9 @@
         <v>5.2072592287069501E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B24" t="s">
         <v>29</v>
@@ -26287,9 +26277,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
@@ -26331,9 +26321,9 @@
         <v>2.6294081253866779E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
         <v>31</v>
@@ -26375,9 +26365,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s">
         <v>32</v>
@@ -26419,9 +26409,9 @@
         <v>3.41307486079604E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
@@ -26463,9 +26453,9 @@
         <v>3.371829243142916E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
@@ -26507,9 +26497,9 @@
         <v>5.3206846772530417E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
         <v>35</v>
@@ -26551,12 +26541,12 @@
         <v>2.0622808826562179E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>164</v>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" t="s">
+        <v>132</v>
       </c>
       <c r="C31">
         <v>2.6773761713520746E-2</v>
@@ -26595,12 +26585,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
         <v>166</v>
+      </c>
+      <c r="B32" t="s">
+        <v>133</v>
       </c>
       <c r="C32">
         <v>2.4207942882641675E-2</v>
@@ -26640,19 +26630,17 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85FCC748-DA24-457F-89A6-C26F79D9A684}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -24490,6 +24490,117 @@
       <c r="A210" s="1" t="n">
         <v>46198</v>
       </c>
+      <c r="B210" t="n">
+        <v>13625371.03623004</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" t="n">
+        <v>78</v>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="n">
+        <v>1</v>
+      </c>
+      <c r="I210" t="n">
+        <v>8</v>
+      </c>
+      <c r="J210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" t="n">
+        <v>1</v>
+      </c>
+      <c r="L210" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" t="n">
+        <v>1</v>
+      </c>
+      <c r="N210" t="n">
+        <v>2</v>
+      </c>
+      <c r="O210" t="n">
+        <v>1</v>
+      </c>
+      <c r="P210" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>4</v>
+      </c>
+      <c r="R210" t="n">
+        <v>1</v>
+      </c>
+      <c r="S210" t="n">
+        <v>4</v>
+      </c>
+      <c r="T210" t="n">
+        <v>5</v>
+      </c>
+      <c r="U210" t="n">
+        <v>1</v>
+      </c>
+      <c r="V210" t="n">
+        <v>0</v>
+      </c>
+      <c r="W210" t="n">
+        <v>1</v>
+      </c>
+      <c r="X210" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -24606,6 +24606,117 @@
       <c r="A211" s="1" t="n">
         <v>46199</v>
       </c>
+      <c r="B211" t="n">
+        <v>13595068.03623004</v>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" t="n">
+        <v>79</v>
+      </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" t="n">
+        <v>1</v>
+      </c>
+      <c r="I211" t="n">
+        <v>8</v>
+      </c>
+      <c r="J211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K211" t="n">
+        <v>1</v>
+      </c>
+      <c r="L211" t="n">
+        <v>1</v>
+      </c>
+      <c r="M211" t="n">
+        <v>1</v>
+      </c>
+      <c r="N211" t="n">
+        <v>1</v>
+      </c>
+      <c r="O211" t="n">
+        <v>1</v>
+      </c>
+      <c r="P211" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>4</v>
+      </c>
+      <c r="R211" t="n">
+        <v>1</v>
+      </c>
+      <c r="S211" t="n">
+        <v>4</v>
+      </c>
+      <c r="T211" t="n">
+        <v>5</v>
+      </c>
+      <c r="U211" t="n">
+        <v>1</v>
+      </c>
+      <c r="V211" t="n">
+        <v>0</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1</v>
+      </c>
+      <c r="X211" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -24727,6 +24727,117 @@
       <c r="A213" s="1" t="n">
         <v>46203</v>
       </c>
+      <c r="B213" t="n">
+        <v>13764152.03623003</v>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1</v>
+      </c>
+      <c r="F213" t="n">
+        <v>78</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" t="n">
+        <v>8</v>
+      </c>
+      <c r="J213" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="n">
+        <v>1</v>
+      </c>
+      <c r="N213" t="n">
+        <v>1</v>
+      </c>
+      <c r="O213" t="n">
+        <v>1</v>
+      </c>
+      <c r="P213" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>4</v>
+      </c>
+      <c r="R213" t="n">
+        <v>1</v>
+      </c>
+      <c r="S213" t="n">
+        <v>4</v>
+      </c>
+      <c r="T213" t="n">
+        <v>5</v>
+      </c>
+      <c r="U213" t="n">
+        <v>1</v>
+      </c>
+      <c r="V213" t="n">
+        <v>0</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1</v>
+      </c>
+      <c r="X213" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -24728,19 +24728,19 @@
         <v>46203</v>
       </c>
       <c r="B213" t="n">
-        <v>13764152.03623003</v>
+        <v>13754456.86815003</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E213" t="n">
         <v>1</v>
       </c>
       <c r="F213" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G213" t="n">
         <v>1</v>
@@ -24761,7 +24761,7 @@
         <v>1</v>
       </c>
       <c r="M213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N213" t="n">
         <v>1</v>
@@ -24797,7 +24797,7 @@
         <v>4</v>
       </c>
       <c r="Y213" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z213" t="n">
         <v>0</v>

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -24843,6 +24843,117 @@
       <c r="A214" s="1" t="n">
         <v>46204</v>
       </c>
+      <c r="B214" t="n">
+        <v>13492598.56571004</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" t="n">
+        <v>78</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" t="n">
+        <v>8</v>
+      </c>
+      <c r="J214" t="n">
+        <v>3</v>
+      </c>
+      <c r="K214" t="n">
+        <v>1</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>1</v>
+      </c>
+      <c r="N214" t="n">
+        <v>1</v>
+      </c>
+      <c r="O214" t="n">
+        <v>1</v>
+      </c>
+      <c r="P214" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>4</v>
+      </c>
+      <c r="R214" t="n">
+        <v>1</v>
+      </c>
+      <c r="S214" t="n">
+        <v>4</v>
+      </c>
+      <c r="T214" t="n">
+        <v>5</v>
+      </c>
+      <c r="U214" t="n">
+        <v>1</v>
+      </c>
+      <c r="V214" t="n">
+        <v>0</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1</v>
+      </c>
+      <c r="X214" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -24959,6 +24959,117 @@
       <c r="A215" s="1" t="n">
         <v>46205</v>
       </c>
+      <c r="B215" t="n">
+        <v>13462998.56571004</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1</v>
+      </c>
+      <c r="F215" t="n">
+        <v>73</v>
+      </c>
+      <c r="G215" t="n">
+        <v>1</v>
+      </c>
+      <c r="H215" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" t="n">
+        <v>8</v>
+      </c>
+      <c r="J215" t="n">
+        <v>3</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" t="n">
+        <v>1</v>
+      </c>
+      <c r="O215" t="n">
+        <v>1</v>
+      </c>
+      <c r="P215" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>4</v>
+      </c>
+      <c r="R215" t="n">
+        <v>1</v>
+      </c>
+      <c r="S215" t="n">
+        <v>4</v>
+      </c>
+      <c r="T215" t="n">
+        <v>5</v>
+      </c>
+      <c r="U215" t="n">
+        <v>1</v>
+      </c>
+      <c r="V215" t="n">
+        <v>0</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1</v>
+      </c>
+      <c r="X215" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -25075,6 +25075,117 @@
       <c r="A216" s="1" t="n">
         <v>46206</v>
       </c>
+      <c r="B216" t="n">
+        <v>13508287.56571004</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1</v>
+      </c>
+      <c r="F216" t="n">
+        <v>71</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" t="n">
+        <v>1</v>
+      </c>
+      <c r="I216" t="n">
+        <v>8</v>
+      </c>
+      <c r="J216" t="n">
+        <v>3</v>
+      </c>
+      <c r="K216" t="n">
+        <v>1</v>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>1</v>
+      </c>
+      <c r="N216" t="n">
+        <v>1</v>
+      </c>
+      <c r="O216" t="n">
+        <v>1</v>
+      </c>
+      <c r="P216" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>4</v>
+      </c>
+      <c r="R216" t="n">
+        <v>1</v>
+      </c>
+      <c r="S216" t="n">
+        <v>4</v>
+      </c>
+      <c r="T216" t="n">
+        <v>5</v>
+      </c>
+      <c r="U216" t="n">
+        <v>1</v>
+      </c>
+      <c r="V216" t="n">
+        <v>0</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1</v>
+      </c>
+      <c r="X216" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -25191,6 +25191,117 @@
       <c r="A217" s="1" t="n">
         <v>46209</v>
       </c>
+      <c r="B217" t="n">
+        <v>13569008.56571004</v>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" t="n">
+        <v>72</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1</v>
+      </c>
+      <c r="H217" t="n">
+        <v>1</v>
+      </c>
+      <c r="I217" t="n">
+        <v>8</v>
+      </c>
+      <c r="J217" t="n">
+        <v>3</v>
+      </c>
+      <c r="K217" t="n">
+        <v>1</v>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>1</v>
+      </c>
+      <c r="N217" t="n">
+        <v>1</v>
+      </c>
+      <c r="O217" t="n">
+        <v>1</v>
+      </c>
+      <c r="P217" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>4</v>
+      </c>
+      <c r="R217" t="n">
+        <v>1</v>
+      </c>
+      <c r="S217" t="n">
+        <v>4</v>
+      </c>
+      <c r="T217" t="n">
+        <v>5</v>
+      </c>
+      <c r="U217" t="n">
+        <v>1</v>
+      </c>
+      <c r="V217" t="n">
+        <v>0</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1</v>
+      </c>
+      <c r="X217" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -25307,6 +25307,117 @@
       <c r="A218" s="1" t="n">
         <v>46210</v>
       </c>
+      <c r="B218" t="n">
+        <v>13569008.56571004</v>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" t="n">
+        <v>72</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1</v>
+      </c>
+      <c r="H218" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" t="n">
+        <v>8</v>
+      </c>
+      <c r="J218" t="n">
+        <v>3</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1</v>
+      </c>
+      <c r="L218" t="n">
+        <v>1</v>
+      </c>
+      <c r="M218" t="n">
+        <v>1</v>
+      </c>
+      <c r="N218" t="n">
+        <v>1</v>
+      </c>
+      <c r="O218" t="n">
+        <v>1</v>
+      </c>
+      <c r="P218" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q218" t="n">
+        <v>4</v>
+      </c>
+      <c r="R218" t="n">
+        <v>1</v>
+      </c>
+      <c r="S218" t="n">
+        <v>4</v>
+      </c>
+      <c r="T218" t="n">
+        <v>5</v>
+      </c>
+      <c r="U218" t="n">
+        <v>1</v>
+      </c>
+      <c r="V218" t="n">
+        <v>0</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1</v>
+      </c>
+      <c r="X218" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -25308,7 +25308,7 @@
         <v>46210</v>
       </c>
       <c r="B218" t="n">
-        <v>13569008.56571004</v>
+        <v>13490016.56571004</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -25320,7 +25320,7 @@
         <v>1</v>
       </c>
       <c r="F218" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G218" t="n">
         <v>1</v>

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -25423,6 +25423,117 @@
       <c r="A219" s="1" t="n">
         <v>46211</v>
       </c>
+      <c r="B219" t="n">
+        <v>13542241.56571004</v>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" t="n">
+        <v>74</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" t="n">
+        <v>8</v>
+      </c>
+      <c r="J219" t="n">
+        <v>3</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1</v>
+      </c>
+      <c r="L219" t="n">
+        <v>1</v>
+      </c>
+      <c r="M219" t="n">
+        <v>1</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="n">
+        <v>1</v>
+      </c>
+      <c r="P219" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q219" t="n">
+        <v>4</v>
+      </c>
+      <c r="R219" t="n">
+        <v>1</v>
+      </c>
+      <c r="S219" t="n">
+        <v>4</v>
+      </c>
+      <c r="T219" t="n">
+        <v>5</v>
+      </c>
+      <c r="U219" t="n">
+        <v>1</v>
+      </c>
+      <c r="V219" t="n">
+        <v>0</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1</v>
+      </c>
+      <c r="X219" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -25544,6 +25544,117 @@
       <c r="A221" s="1" t="n">
         <v>46213</v>
       </c>
+      <c r="B221" t="n">
+        <v>13617695.56571005</v>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" t="n">
+        <v>74</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="n">
+        <v>8</v>
+      </c>
+      <c r="J221" t="n">
+        <v>3</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
+        <v>1</v>
+      </c>
+      <c r="M221" t="n">
+        <v>1</v>
+      </c>
+      <c r="N221" t="n">
+        <v>1</v>
+      </c>
+      <c r="O221" t="n">
+        <v>1</v>
+      </c>
+      <c r="P221" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q221" t="n">
+        <v>4</v>
+      </c>
+      <c r="R221" t="n">
+        <v>1</v>
+      </c>
+      <c r="S221" t="n">
+        <v>4</v>
+      </c>
+      <c r="T221" t="n">
+        <v>5</v>
+      </c>
+      <c r="U221" t="n">
+        <v>1</v>
+      </c>
+      <c r="V221" t="n">
+        <v>0</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1</v>
+      </c>
+      <c r="X221" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -25545,7 +25545,7 @@
         <v>46213</v>
       </c>
       <c r="B221" t="n">
-        <v>13617695.56571005</v>
+        <v>13527134.56571005</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
@@ -25557,7 +25557,7 @@
         <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G221" t="n">
         <v>1</v>
@@ -25578,7 +25578,7 @@
         <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N221" t="n">
         <v>1</v>

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -25660,6 +25660,117 @@
       <c r="A222" s="1" t="n">
         <v>46216</v>
       </c>
+      <c r="B222" t="n">
+        <v>13322884.56571005</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1</v>
+      </c>
+      <c r="F222" t="n">
+        <v>80</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" t="n">
+        <v>1</v>
+      </c>
+      <c r="I222" t="n">
+        <v>8</v>
+      </c>
+      <c r="J222" t="n">
+        <v>3</v>
+      </c>
+      <c r="K222" t="n">
+        <v>1</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="n">
+        <v>1</v>
+      </c>
+      <c r="N222" t="n">
+        <v>1</v>
+      </c>
+      <c r="O222" t="n">
+        <v>1</v>
+      </c>
+      <c r="P222" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q222" t="n">
+        <v>4</v>
+      </c>
+      <c r="R222" t="n">
+        <v>1</v>
+      </c>
+      <c r="S222" t="n">
+        <v>4</v>
+      </c>
+      <c r="T222" t="n">
+        <v>5</v>
+      </c>
+      <c r="U222" t="n">
+        <v>1</v>
+      </c>
+      <c r="V222" t="n">
+        <v>0</v>
+      </c>
+      <c r="W222" t="n">
+        <v>1</v>
+      </c>
+      <c r="X222" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -25776,6 +25776,117 @@
       <c r="A223" s="1" t="n">
         <v>46217</v>
       </c>
+      <c r="B223" t="n">
+        <v>13373303.56571003</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1</v>
+      </c>
+      <c r="F223" t="n">
+        <v>81</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1</v>
+      </c>
+      <c r="H223" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" t="n">
+        <v>8</v>
+      </c>
+      <c r="J223" t="n">
+        <v>3</v>
+      </c>
+      <c r="K223" t="n">
+        <v>1</v>
+      </c>
+      <c r="L223" t="n">
+        <v>1</v>
+      </c>
+      <c r="M223" t="n">
+        <v>1</v>
+      </c>
+      <c r="N223" t="n">
+        <v>1</v>
+      </c>
+      <c r="O223" t="n">
+        <v>1</v>
+      </c>
+      <c r="P223" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q223" t="n">
+        <v>4</v>
+      </c>
+      <c r="R223" t="n">
+        <v>1</v>
+      </c>
+      <c r="S223" t="n">
+        <v>4</v>
+      </c>
+      <c r="T223" t="n">
+        <v>5</v>
+      </c>
+      <c r="U223" t="n">
+        <v>1</v>
+      </c>
+      <c r="V223" t="n">
+        <v>0</v>
+      </c>
+      <c r="W223" t="n">
+        <v>1</v>
+      </c>
+      <c r="X223" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -25892,6 +25892,117 @@
       <c r="A224" s="1" t="n">
         <v>46218</v>
       </c>
+      <c r="B224" t="n">
+        <v>13476168.56571005</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="n">
+        <v>1</v>
+      </c>
+      <c r="F224" t="n">
+        <v>81</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" t="n">
+        <v>1</v>
+      </c>
+      <c r="I224" t="n">
+        <v>8</v>
+      </c>
+      <c r="J224" t="n">
+        <v>3</v>
+      </c>
+      <c r="K224" t="n">
+        <v>1</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="n">
+        <v>1</v>
+      </c>
+      <c r="N224" t="n">
+        <v>1</v>
+      </c>
+      <c r="O224" t="n">
+        <v>1</v>
+      </c>
+      <c r="P224" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q224" t="n">
+        <v>4</v>
+      </c>
+      <c r="R224" t="n">
+        <v>1</v>
+      </c>
+      <c r="S224" t="n">
+        <v>4</v>
+      </c>
+      <c r="T224" t="n">
+        <v>5</v>
+      </c>
+      <c r="U224" t="n">
+        <v>1</v>
+      </c>
+      <c r="V224" t="n">
+        <v>0</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1</v>
+      </c>
+      <c r="X224" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -26008,6 +26008,117 @@
       <c r="A225" s="1" t="n">
         <v>46219</v>
       </c>
+      <c r="B225" t="n">
+        <v>13434028.56571005</v>
+      </c>
+      <c r="C225" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="n">
+        <v>1</v>
+      </c>
+      <c r="F225" t="n">
+        <v>81</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+      <c r="H225" t="n">
+        <v>1</v>
+      </c>
+      <c r="I225" t="n">
+        <v>8</v>
+      </c>
+      <c r="J225" t="n">
+        <v>3</v>
+      </c>
+      <c r="K225" t="n">
+        <v>1</v>
+      </c>
+      <c r="L225" t="n">
+        <v>1</v>
+      </c>
+      <c r="M225" t="n">
+        <v>1</v>
+      </c>
+      <c r="N225" t="n">
+        <v>1</v>
+      </c>
+      <c r="O225" t="n">
+        <v>1</v>
+      </c>
+      <c r="P225" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q225" t="n">
+        <v>4</v>
+      </c>
+      <c r="R225" t="n">
+        <v>1</v>
+      </c>
+      <c r="S225" t="n">
+        <v>4</v>
+      </c>
+      <c r="T225" t="n">
+        <v>5</v>
+      </c>
+      <c r="U225" t="n">
+        <v>1</v>
+      </c>
+      <c r="V225" t="n">
+        <v>0</v>
+      </c>
+      <c r="W225" t="n">
+        <v>1</v>
+      </c>
+      <c r="X225" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -26124,6 +26124,117 @@
       <c r="A226" s="1" t="n">
         <v>46220</v>
       </c>
+      <c r="B226" t="n">
+        <v>13297128.56571005</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" t="n">
+        <v>81</v>
+      </c>
+      <c r="G226" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" t="n">
+        <v>8</v>
+      </c>
+      <c r="J226" t="n">
+        <v>3</v>
+      </c>
+      <c r="K226" t="n">
+        <v>1</v>
+      </c>
+      <c r="L226" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" t="n">
+        <v>1</v>
+      </c>
+      <c r="N226" t="n">
+        <v>1</v>
+      </c>
+      <c r="O226" t="n">
+        <v>1</v>
+      </c>
+      <c r="P226" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q226" t="n">
+        <v>4</v>
+      </c>
+      <c r="R226" t="n">
+        <v>1</v>
+      </c>
+      <c r="S226" t="n">
+        <v>4</v>
+      </c>
+      <c r="T226" t="n">
+        <v>5</v>
+      </c>
+      <c r="U226" t="n">
+        <v>1</v>
+      </c>
+      <c r="V226" t="n">
+        <v>0</v>
+      </c>
+      <c r="W226" t="n">
+        <v>1</v>
+      </c>
+      <c r="X226" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -26240,6 +26240,117 @@
       <c r="A227" s="1" t="n">
         <v>46223</v>
       </c>
+      <c r="B227" t="n">
+        <v>13104030.31771003</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" t="n">
+        <v>81</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1</v>
+      </c>
+      <c r="I227" t="n">
+        <v>8</v>
+      </c>
+      <c r="J227" t="n">
+        <v>3</v>
+      </c>
+      <c r="K227" t="n">
+        <v>1</v>
+      </c>
+      <c r="L227" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" t="n">
+        <v>1</v>
+      </c>
+      <c r="N227" t="n">
+        <v>1</v>
+      </c>
+      <c r="O227" t="n">
+        <v>1</v>
+      </c>
+      <c r="P227" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>4</v>
+      </c>
+      <c r="R227" t="n">
+        <v>1</v>
+      </c>
+      <c r="S227" t="n">
+        <v>4</v>
+      </c>
+      <c r="T227" t="n">
+        <v>5</v>
+      </c>
+      <c r="U227" t="n">
+        <v>1</v>
+      </c>
+      <c r="V227" t="n">
+        <v>0</v>
+      </c>
+      <c r="W227" t="n">
+        <v>1</v>
+      </c>
+      <c r="X227" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -26356,6 +26356,117 @@
       <c r="A228" s="1" t="n">
         <v>46224</v>
       </c>
+      <c r="B228" t="n">
+        <v>13137297.31771005</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" t="n">
+        <v>82</v>
+      </c>
+      <c r="G228" t="n">
+        <v>1</v>
+      </c>
+      <c r="H228" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" t="n">
+        <v>8</v>
+      </c>
+      <c r="J228" t="n">
+        <v>3</v>
+      </c>
+      <c r="K228" t="n">
+        <v>1</v>
+      </c>
+      <c r="L228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" t="n">
+        <v>1</v>
+      </c>
+      <c r="N228" t="n">
+        <v>1</v>
+      </c>
+      <c r="O228" t="n">
+        <v>1</v>
+      </c>
+      <c r="P228" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q228" t="n">
+        <v>4</v>
+      </c>
+      <c r="R228" t="n">
+        <v>1</v>
+      </c>
+      <c r="S228" t="n">
+        <v>4</v>
+      </c>
+      <c r="T228" t="n">
+        <v>5</v>
+      </c>
+      <c r="U228" t="n">
+        <v>1</v>
+      </c>
+      <c r="V228" t="n">
+        <v>0</v>
+      </c>
+      <c r="W228" t="n">
+        <v>1</v>
+      </c>
+      <c r="X228" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -26472,6 +26472,117 @@
       <c r="A229" s="1" t="n">
         <v>46225</v>
       </c>
+      <c r="B229" t="n">
+        <v>13435502.31771005</v>
+      </c>
+      <c r="C229" t="n">
+        <v>1</v>
+      </c>
+      <c r="D229" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" t="n">
+        <v>82</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1</v>
+      </c>
+      <c r="H229" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" t="n">
+        <v>8</v>
+      </c>
+      <c r="J229" t="n">
+        <v>3</v>
+      </c>
+      <c r="K229" t="n">
+        <v>1</v>
+      </c>
+      <c r="L229" t="n">
+        <v>1</v>
+      </c>
+      <c r="M229" t="n">
+        <v>2</v>
+      </c>
+      <c r="N229" t="n">
+        <v>1</v>
+      </c>
+      <c r="O229" t="n">
+        <v>1</v>
+      </c>
+      <c r="P229" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q229" t="n">
+        <v>4</v>
+      </c>
+      <c r="R229" t="n">
+        <v>1</v>
+      </c>
+      <c r="S229" t="n">
+        <v>4</v>
+      </c>
+      <c r="T229" t="n">
+        <v>5</v>
+      </c>
+      <c r="U229" t="n">
+        <v>1</v>
+      </c>
+      <c r="V229" t="n">
+        <v>0</v>
+      </c>
+      <c r="W229" t="n">
+        <v>1</v>
+      </c>
+      <c r="X229" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -26588,6 +26588,117 @@
       <c r="A230" s="1" t="n">
         <v>46226</v>
       </c>
+      <c r="B230" t="n">
+        <v>13476808.31771005</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" t="n">
+        <v>84</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" t="n">
+        <v>8</v>
+      </c>
+      <c r="J230" t="n">
+        <v>3</v>
+      </c>
+      <c r="K230" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="n">
+        <v>2</v>
+      </c>
+      <c r="N230" t="n">
+        <v>1</v>
+      </c>
+      <c r="O230" t="n">
+        <v>1</v>
+      </c>
+      <c r="P230" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q230" t="n">
+        <v>4</v>
+      </c>
+      <c r="R230" t="n">
+        <v>1</v>
+      </c>
+      <c r="S230" t="n">
+        <v>4</v>
+      </c>
+      <c r="T230" t="n">
+        <v>5</v>
+      </c>
+      <c r="U230" t="n">
+        <v>1</v>
+      </c>
+      <c r="V230" t="n">
+        <v>0</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1</v>
+      </c>
+      <c r="X230" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -26704,6 +26704,117 @@
       <c r="A231" s="1" t="n">
         <v>46227</v>
       </c>
+      <c r="B231" t="n">
+        <v>13429425.31771005</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1</v>
+      </c>
+      <c r="F231" t="n">
+        <v>83</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" t="n">
+        <v>8</v>
+      </c>
+      <c r="J231" t="n">
+        <v>3</v>
+      </c>
+      <c r="K231" t="n">
+        <v>1</v>
+      </c>
+      <c r="L231" t="n">
+        <v>1</v>
+      </c>
+      <c r="M231" t="n">
+        <v>2</v>
+      </c>
+      <c r="N231" t="n">
+        <v>1</v>
+      </c>
+      <c r="O231" t="n">
+        <v>1</v>
+      </c>
+      <c r="P231" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q231" t="n">
+        <v>4</v>
+      </c>
+      <c r="R231" t="n">
+        <v>1</v>
+      </c>
+      <c r="S231" t="n">
+        <v>4</v>
+      </c>
+      <c r="T231" t="n">
+        <v>5</v>
+      </c>
+      <c r="U231" t="n">
+        <v>1</v>
+      </c>
+      <c r="V231" t="n">
+        <v>0</v>
+      </c>
+      <c r="W231" t="n">
+        <v>1</v>
+      </c>
+      <c r="X231" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y231" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL231" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -26820,6 +26820,117 @@
       <c r="A232" s="1" t="n">
         <v>46230</v>
       </c>
+      <c r="B232" t="n">
+        <v>13445995.74471003</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" t="n">
+        <v>82</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1</v>
+      </c>
+      <c r="H232" t="n">
+        <v>1</v>
+      </c>
+      <c r="I232" t="n">
+        <v>9</v>
+      </c>
+      <c r="J232" t="n">
+        <v>3</v>
+      </c>
+      <c r="K232" t="n">
+        <v>1</v>
+      </c>
+      <c r="L232" t="n">
+        <v>1</v>
+      </c>
+      <c r="M232" t="n">
+        <v>2</v>
+      </c>
+      <c r="N232" t="n">
+        <v>2</v>
+      </c>
+      <c r="O232" t="n">
+        <v>1</v>
+      </c>
+      <c r="P232" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q232" t="n">
+        <v>4</v>
+      </c>
+      <c r="R232" t="n">
+        <v>1</v>
+      </c>
+      <c r="S232" t="n">
+        <v>4</v>
+      </c>
+      <c r="T232" t="n">
+        <v>6</v>
+      </c>
+      <c r="U232" t="n">
+        <v>1</v>
+      </c>
+      <c r="V232" t="n">
+        <v>0</v>
+      </c>
+      <c r="W232" t="n">
+        <v>1</v>
+      </c>
+      <c r="X232" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y232" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL232" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -26936,6 +26936,117 @@
       <c r="A233" s="1" t="n">
         <v>46231</v>
       </c>
+      <c r="B233" t="n">
+        <v>13226730.74471005</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="n">
+        <v>1</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1</v>
+      </c>
+      <c r="F233" t="n">
+        <v>82</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" t="n">
+        <v>9</v>
+      </c>
+      <c r="J233" t="n">
+        <v>3</v>
+      </c>
+      <c r="K233" t="n">
+        <v>1</v>
+      </c>
+      <c r="L233" t="n">
+        <v>1</v>
+      </c>
+      <c r="M233" t="n">
+        <v>1</v>
+      </c>
+      <c r="N233" t="n">
+        <v>2</v>
+      </c>
+      <c r="O233" t="n">
+        <v>1</v>
+      </c>
+      <c r="P233" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>4</v>
+      </c>
+      <c r="R233" t="n">
+        <v>1</v>
+      </c>
+      <c r="S233" t="n">
+        <v>4</v>
+      </c>
+      <c r="T233" t="n">
+        <v>6</v>
+      </c>
+      <c r="U233" t="n">
+        <v>1</v>
+      </c>
+      <c r="V233" t="n">
+        <v>0</v>
+      </c>
+      <c r="W233" t="n">
+        <v>1</v>
+      </c>
+      <c r="X233" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y233" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL233" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -27052,6 +27052,117 @@
       <c r="A234" s="1" t="n">
         <v>46232</v>
       </c>
+      <c r="B234" t="n">
+        <v>13310691.74471005</v>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1</v>
+      </c>
+      <c r="F234" t="n">
+        <v>80</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+      <c r="H234" t="n">
+        <v>1</v>
+      </c>
+      <c r="I234" t="n">
+        <v>9</v>
+      </c>
+      <c r="J234" t="n">
+        <v>3</v>
+      </c>
+      <c r="K234" t="n">
+        <v>1</v>
+      </c>
+      <c r="L234" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" t="n">
+        <v>1</v>
+      </c>
+      <c r="N234" t="n">
+        <v>2</v>
+      </c>
+      <c r="O234" t="n">
+        <v>1</v>
+      </c>
+      <c r="P234" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>4</v>
+      </c>
+      <c r="R234" t="n">
+        <v>1</v>
+      </c>
+      <c r="S234" t="n">
+        <v>4</v>
+      </c>
+      <c r="T234" t="n">
+        <v>6</v>
+      </c>
+      <c r="U234" t="n">
+        <v>1</v>
+      </c>
+      <c r="V234" t="n">
+        <v>0</v>
+      </c>
+      <c r="W234" t="n">
+        <v>1</v>
+      </c>
+      <c r="X234" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y234" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL234" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -27168,6 +27168,117 @@
       <c r="A235" s="1" t="n">
         <v>46233</v>
       </c>
+      <c r="B235" t="n">
+        <v>13347611.74471005</v>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" t="n">
+        <v>1</v>
+      </c>
+      <c r="F235" t="n">
+        <v>80</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I235" t="n">
+        <v>9</v>
+      </c>
+      <c r="J235" t="n">
+        <v>3</v>
+      </c>
+      <c r="K235" t="n">
+        <v>1</v>
+      </c>
+      <c r="L235" t="n">
+        <v>1</v>
+      </c>
+      <c r="M235" t="n">
+        <v>1</v>
+      </c>
+      <c r="N235" t="n">
+        <v>2</v>
+      </c>
+      <c r="O235" t="n">
+        <v>1</v>
+      </c>
+      <c r="P235" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>4</v>
+      </c>
+      <c r="R235" t="n">
+        <v>1</v>
+      </c>
+      <c r="S235" t="n">
+        <v>4</v>
+      </c>
+      <c r="T235" t="n">
+        <v>6</v>
+      </c>
+      <c r="U235" t="n">
+        <v>1</v>
+      </c>
+      <c r="V235" t="n">
+        <v>0</v>
+      </c>
+      <c r="W235" t="n">
+        <v>1</v>
+      </c>
+      <c r="X235" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y235" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL235" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -27284,6 +27284,117 @@
       <c r="A236" s="1" t="n">
         <v>46234</v>
       </c>
+      <c r="B236" t="n">
+        <v>13434786.74471005</v>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1</v>
+      </c>
+      <c r="F236" t="n">
+        <v>80</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1</v>
+      </c>
+      <c r="H236" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" t="n">
+        <v>9</v>
+      </c>
+      <c r="J236" t="n">
+        <v>3</v>
+      </c>
+      <c r="K236" t="n">
+        <v>1</v>
+      </c>
+      <c r="L236" t="n">
+        <v>1</v>
+      </c>
+      <c r="M236" t="n">
+        <v>1</v>
+      </c>
+      <c r="N236" t="n">
+        <v>2</v>
+      </c>
+      <c r="O236" t="n">
+        <v>1</v>
+      </c>
+      <c r="P236" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>4</v>
+      </c>
+      <c r="R236" t="n">
+        <v>1</v>
+      </c>
+      <c r="S236" t="n">
+        <v>4</v>
+      </c>
+      <c r="T236" t="n">
+        <v>6</v>
+      </c>
+      <c r="U236" t="n">
+        <v>1</v>
+      </c>
+      <c r="V236" t="n">
+        <v>0</v>
+      </c>
+      <c r="W236" t="n">
+        <v>1</v>
+      </c>
+      <c r="X236" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y236" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL236" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -27400,6 +27400,117 @@
       <c r="A237" s="1" t="n">
         <v>46237</v>
       </c>
+      <c r="B237" t="n">
+        <v>13353503.74471005</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1</v>
+      </c>
+      <c r="F237" t="n">
+        <v>81</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1</v>
+      </c>
+      <c r="I237" t="n">
+        <v>9</v>
+      </c>
+      <c r="J237" t="n">
+        <v>3</v>
+      </c>
+      <c r="K237" t="n">
+        <v>1</v>
+      </c>
+      <c r="L237" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" t="n">
+        <v>1</v>
+      </c>
+      <c r="N237" t="n">
+        <v>2</v>
+      </c>
+      <c r="O237" t="n">
+        <v>1</v>
+      </c>
+      <c r="P237" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q237" t="n">
+        <v>4</v>
+      </c>
+      <c r="R237" t="n">
+        <v>1</v>
+      </c>
+      <c r="S237" t="n">
+        <v>4</v>
+      </c>
+      <c r="T237" t="n">
+        <v>6</v>
+      </c>
+      <c r="U237" t="n">
+        <v>1</v>
+      </c>
+      <c r="V237" t="n">
+        <v>0</v>
+      </c>
+      <c r="W237" t="n">
+        <v>1</v>
+      </c>
+      <c r="X237" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y237" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL237" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -27516,6 +27516,117 @@
       <c r="A238" s="1" t="n">
         <v>46238</v>
       </c>
+      <c r="B238" t="n">
+        <v>13532443.74471005</v>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1</v>
+      </c>
+      <c r="F238" t="n">
+        <v>81</v>
+      </c>
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H238" t="n">
+        <v>1</v>
+      </c>
+      <c r="I238" t="n">
+        <v>9</v>
+      </c>
+      <c r="J238" t="n">
+        <v>3</v>
+      </c>
+      <c r="K238" t="n">
+        <v>1</v>
+      </c>
+      <c r="L238" t="n">
+        <v>1</v>
+      </c>
+      <c r="M238" t="n">
+        <v>2</v>
+      </c>
+      <c r="N238" t="n">
+        <v>2</v>
+      </c>
+      <c r="O238" t="n">
+        <v>1</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q238" t="n">
+        <v>4</v>
+      </c>
+      <c r="R238" t="n">
+        <v>1</v>
+      </c>
+      <c r="S238" t="n">
+        <v>4</v>
+      </c>
+      <c r="T238" t="n">
+        <v>6</v>
+      </c>
+      <c r="U238" t="n">
+        <v>1</v>
+      </c>
+      <c r="V238" t="n">
+        <v>0</v>
+      </c>
+      <c r="W238" t="n">
+        <v>1</v>
+      </c>
+      <c r="X238" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y238" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL238" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -27632,6 +27632,117 @@
       <c r="A239" s="1" t="n">
         <v>46239</v>
       </c>
+      <c r="B239" t="n">
+        <v>13635795.74471003</v>
+      </c>
+      <c r="C239" t="n">
+        <v>1</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" t="n">
+        <v>81</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1</v>
+      </c>
+      <c r="H239" t="n">
+        <v>1</v>
+      </c>
+      <c r="I239" t="n">
+        <v>9</v>
+      </c>
+      <c r="J239" t="n">
+        <v>3</v>
+      </c>
+      <c r="K239" t="n">
+        <v>1</v>
+      </c>
+      <c r="L239" t="n">
+        <v>1</v>
+      </c>
+      <c r="M239" t="n">
+        <v>2</v>
+      </c>
+      <c r="N239" t="n">
+        <v>2</v>
+      </c>
+      <c r="O239" t="n">
+        <v>1</v>
+      </c>
+      <c r="P239" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q239" t="n">
+        <v>4</v>
+      </c>
+      <c r="R239" t="n">
+        <v>1</v>
+      </c>
+      <c r="S239" t="n">
+        <v>4</v>
+      </c>
+      <c r="T239" t="n">
+        <v>6</v>
+      </c>
+      <c r="U239" t="n">
+        <v>1</v>
+      </c>
+      <c r="V239" t="n">
+        <v>0</v>
+      </c>
+      <c r="W239" t="n">
+        <v>1</v>
+      </c>
+      <c r="X239" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -27748,6 +27748,117 @@
       <c r="A240" s="1" t="n">
         <v>46240</v>
       </c>
+      <c r="B240" t="n">
+        <v>13652225.74471005</v>
+      </c>
+      <c r="C240" t="n">
+        <v>1</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" t="n">
+        <v>81</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" t="n">
+        <v>9</v>
+      </c>
+      <c r="J240" t="n">
+        <v>3</v>
+      </c>
+      <c r="K240" t="n">
+        <v>1</v>
+      </c>
+      <c r="L240" t="n">
+        <v>1</v>
+      </c>
+      <c r="M240" t="n">
+        <v>2</v>
+      </c>
+      <c r="N240" t="n">
+        <v>2</v>
+      </c>
+      <c r="O240" t="n">
+        <v>1</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>4</v>
+      </c>
+      <c r="R240" t="n">
+        <v>1</v>
+      </c>
+      <c r="S240" t="n">
+        <v>4</v>
+      </c>
+      <c r="T240" t="n">
+        <v>6</v>
+      </c>
+      <c r="U240" t="n">
+        <v>1</v>
+      </c>
+      <c r="V240" t="n">
+        <v>0</v>
+      </c>
+      <c r="W240" t="n">
+        <v>1</v>
+      </c>
+      <c r="X240" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -27864,6 +27864,117 @@
       <c r="A241" s="1" t="n">
         <v>46241</v>
       </c>
+      <c r="B241" t="n">
+        <v>13792755.74471005</v>
+      </c>
+      <c r="C241" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" t="n">
+        <v>1</v>
+      </c>
+      <c r="E241" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" t="n">
+        <v>81</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1</v>
+      </c>
+      <c r="H241" t="n">
+        <v>1</v>
+      </c>
+      <c r="I241" t="n">
+        <v>9</v>
+      </c>
+      <c r="J241" t="n">
+        <v>3</v>
+      </c>
+      <c r="K241" t="n">
+        <v>1</v>
+      </c>
+      <c r="L241" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" t="n">
+        <v>2</v>
+      </c>
+      <c r="N241" t="n">
+        <v>2</v>
+      </c>
+      <c r="O241" t="n">
+        <v>1</v>
+      </c>
+      <c r="P241" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>5</v>
+      </c>
+      <c r="R241" t="n">
+        <v>1</v>
+      </c>
+      <c r="S241" t="n">
+        <v>5</v>
+      </c>
+      <c r="T241" t="n">
+        <v>6</v>
+      </c>
+      <c r="U241" t="n">
+        <v>1</v>
+      </c>
+      <c r="V241" t="n">
+        <v>0</v>
+      </c>
+      <c r="W241" t="n">
+        <v>1</v>
+      </c>
+      <c r="X241" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL241" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -27980,6 +27980,117 @@
       <c r="A242" s="1" t="n">
         <v>46244</v>
       </c>
+      <c r="B242" t="n">
+        <v>13850558.24471005</v>
+      </c>
+      <c r="C242" t="n">
+        <v>1</v>
+      </c>
+      <c r="D242" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" t="n">
+        <v>1</v>
+      </c>
+      <c r="F242" t="n">
+        <v>82</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" t="n">
+        <v>1</v>
+      </c>
+      <c r="I242" t="n">
+        <v>10</v>
+      </c>
+      <c r="J242" t="n">
+        <v>4</v>
+      </c>
+      <c r="K242" t="n">
+        <v>1</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="n">
+        <v>2</v>
+      </c>
+      <c r="N242" t="n">
+        <v>2</v>
+      </c>
+      <c r="O242" t="n">
+        <v>1</v>
+      </c>
+      <c r="P242" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>5</v>
+      </c>
+      <c r="R242" t="n">
+        <v>1</v>
+      </c>
+      <c r="S242" t="n">
+        <v>5</v>
+      </c>
+      <c r="T242" t="n">
+        <v>7</v>
+      </c>
+      <c r="U242" t="n">
+        <v>1</v>
+      </c>
+      <c r="V242" t="n">
+        <v>0</v>
+      </c>
+      <c r="W242" t="n">
+        <v>1</v>
+      </c>
+      <c r="X242" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL242" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -28096,6 +28096,117 @@
       <c r="A243" s="1" t="n">
         <v>46245</v>
       </c>
+      <c r="B243" t="n">
+        <v>13854890.11771006</v>
+      </c>
+      <c r="C243" t="n">
+        <v>1</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1</v>
+      </c>
+      <c r="F243" t="n">
+        <v>84</v>
+      </c>
+      <c r="G243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H243" t="n">
+        <v>1</v>
+      </c>
+      <c r="I243" t="n">
+        <v>10</v>
+      </c>
+      <c r="J243" t="n">
+        <v>4</v>
+      </c>
+      <c r="K243" t="n">
+        <v>1</v>
+      </c>
+      <c r="L243" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" t="n">
+        <v>2</v>
+      </c>
+      <c r="N243" t="n">
+        <v>2</v>
+      </c>
+      <c r="O243" t="n">
+        <v>1</v>
+      </c>
+      <c r="P243" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>5</v>
+      </c>
+      <c r="R243" t="n">
+        <v>1</v>
+      </c>
+      <c r="S243" t="n">
+        <v>5</v>
+      </c>
+      <c r="T243" t="n">
+        <v>7</v>
+      </c>
+      <c r="U243" t="n">
+        <v>1</v>
+      </c>
+      <c r="V243" t="n">
+        <v>0</v>
+      </c>
+      <c r="W243" t="n">
+        <v>1</v>
+      </c>
+      <c r="X243" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -28212,6 +28212,117 @@
       <c r="A244" s="1" t="n">
         <v>46246</v>
       </c>
+      <c r="B244" t="n">
+        <v>13875905.61771005</v>
+      </c>
+      <c r="C244" t="n">
+        <v>1</v>
+      </c>
+      <c r="D244" t="n">
+        <v>1</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" t="n">
+        <v>86</v>
+      </c>
+      <c r="G244" t="n">
+        <v>2</v>
+      </c>
+      <c r="H244" t="n">
+        <v>2</v>
+      </c>
+      <c r="I244" t="n">
+        <v>13</v>
+      </c>
+      <c r="J244" t="n">
+        <v>5</v>
+      </c>
+      <c r="K244" t="n">
+        <v>1</v>
+      </c>
+      <c r="L244" t="n">
+        <v>2</v>
+      </c>
+      <c r="M244" t="n">
+        <v>2</v>
+      </c>
+      <c r="N244" t="n">
+        <v>2</v>
+      </c>
+      <c r="O244" t="n">
+        <v>1</v>
+      </c>
+      <c r="P244" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>6</v>
+      </c>
+      <c r="R244" t="n">
+        <v>1</v>
+      </c>
+      <c r="S244" t="n">
+        <v>6</v>
+      </c>
+      <c r="T244" t="n">
+        <v>9</v>
+      </c>
+      <c r="U244" t="n">
+        <v>1</v>
+      </c>
+      <c r="V244" t="n">
+        <v>0</v>
+      </c>
+      <c r="W244" t="n">
+        <v>2</v>
+      </c>
+      <c r="X244" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL244" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -28333,6 +28333,117 @@
       <c r="A246" s="1" t="n">
         <v>46248</v>
       </c>
+      <c r="B246" t="n">
+        <v>13933214.20021005</v>
+      </c>
+      <c r="C246" t="n">
+        <v>1</v>
+      </c>
+      <c r="D246" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" t="n">
+        <v>1</v>
+      </c>
+      <c r="F246" t="n">
+        <v>86</v>
+      </c>
+      <c r="G246" t="n">
+        <v>4</v>
+      </c>
+      <c r="H246" t="n">
+        <v>2</v>
+      </c>
+      <c r="I246" t="n">
+        <v>14</v>
+      </c>
+      <c r="J246" t="n">
+        <v>5</v>
+      </c>
+      <c r="K246" t="n">
+        <v>1</v>
+      </c>
+      <c r="L246" t="n">
+        <v>2</v>
+      </c>
+      <c r="M246" t="n">
+        <v>2</v>
+      </c>
+      <c r="N246" t="n">
+        <v>2</v>
+      </c>
+      <c r="O246" t="n">
+        <v>2</v>
+      </c>
+      <c r="P246" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>7</v>
+      </c>
+      <c r="R246" t="n">
+        <v>1</v>
+      </c>
+      <c r="S246" t="n">
+        <v>7</v>
+      </c>
+      <c r="T246" t="n">
+        <v>9</v>
+      </c>
+      <c r="U246" t="n">
+        <v>2</v>
+      </c>
+      <c r="V246" t="n">
+        <v>0</v>
+      </c>
+      <c r="W246" t="n">
+        <v>2</v>
+      </c>
+      <c r="X246" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -28449,6 +28449,117 @@
       <c r="A247" s="1" t="n">
         <v>46251</v>
       </c>
+      <c r="B247" t="n">
+        <v>14154495.20021005</v>
+      </c>
+      <c r="C247" t="n">
+        <v>1</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1</v>
+      </c>
+      <c r="F247" t="n">
+        <v>83</v>
+      </c>
+      <c r="G247" t="n">
+        <v>4</v>
+      </c>
+      <c r="H247" t="n">
+        <v>2</v>
+      </c>
+      <c r="I247" t="n">
+        <v>14</v>
+      </c>
+      <c r="J247" t="n">
+        <v>5</v>
+      </c>
+      <c r="K247" t="n">
+        <v>1</v>
+      </c>
+      <c r="L247" t="n">
+        <v>2</v>
+      </c>
+      <c r="M247" t="n">
+        <v>2</v>
+      </c>
+      <c r="N247" t="n">
+        <v>2</v>
+      </c>
+      <c r="O247" t="n">
+        <v>2</v>
+      </c>
+      <c r="P247" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>7</v>
+      </c>
+      <c r="R247" t="n">
+        <v>1</v>
+      </c>
+      <c r="S247" t="n">
+        <v>7</v>
+      </c>
+      <c r="T247" t="n">
+        <v>10</v>
+      </c>
+      <c r="U247" t="n">
+        <v>2</v>
+      </c>
+      <c r="V247" t="n">
+        <v>0</v>
+      </c>
+      <c r="W247" t="n">
+        <v>2</v>
+      </c>
+      <c r="X247" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -28565,6 +28565,117 @@
       <c r="A248" s="1" t="n">
         <v>46252</v>
       </c>
+      <c r="B248" t="n">
+        <v>14223588.70021005</v>
+      </c>
+      <c r="C248" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" t="n">
+        <v>83</v>
+      </c>
+      <c r="G248" t="n">
+        <v>4</v>
+      </c>
+      <c r="H248" t="n">
+        <v>2</v>
+      </c>
+      <c r="I248" t="n">
+        <v>15</v>
+      </c>
+      <c r="J248" t="n">
+        <v>5</v>
+      </c>
+      <c r="K248" t="n">
+        <v>1</v>
+      </c>
+      <c r="L248" t="n">
+        <v>2</v>
+      </c>
+      <c r="M248" t="n">
+        <v>2</v>
+      </c>
+      <c r="N248" t="n">
+        <v>2</v>
+      </c>
+      <c r="O248" t="n">
+        <v>2</v>
+      </c>
+      <c r="P248" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>7</v>
+      </c>
+      <c r="R248" t="n">
+        <v>1</v>
+      </c>
+      <c r="S248" t="n">
+        <v>7</v>
+      </c>
+      <c r="T248" t="n">
+        <v>10</v>
+      </c>
+      <c r="U248" t="n">
+        <v>2</v>
+      </c>
+      <c r="V248" t="n">
+        <v>0</v>
+      </c>
+      <c r="W248" t="n">
+        <v>2</v>
+      </c>
+      <c r="X248" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -28681,6 +28681,117 @@
       <c r="A249" s="1" t="n">
         <v>46253</v>
       </c>
+      <c r="B249" t="n">
+        <v>13959807.19121005</v>
+      </c>
+      <c r="C249" t="n">
+        <v>1</v>
+      </c>
+      <c r="D249" t="n">
+        <v>1</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" t="n">
+        <v>82</v>
+      </c>
+      <c r="G249" t="n">
+        <v>4</v>
+      </c>
+      <c r="H249" t="n">
+        <v>2</v>
+      </c>
+      <c r="I249" t="n">
+        <v>15</v>
+      </c>
+      <c r="J249" t="n">
+        <v>5</v>
+      </c>
+      <c r="K249" t="n">
+        <v>1</v>
+      </c>
+      <c r="L249" t="n">
+        <v>2</v>
+      </c>
+      <c r="M249" t="n">
+        <v>2</v>
+      </c>
+      <c r="N249" t="n">
+        <v>2</v>
+      </c>
+      <c r="O249" t="n">
+        <v>2</v>
+      </c>
+      <c r="P249" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>7</v>
+      </c>
+      <c r="R249" t="n">
+        <v>1</v>
+      </c>
+      <c r="S249" t="n">
+        <v>7</v>
+      </c>
+      <c r="T249" t="n">
+        <v>9</v>
+      </c>
+      <c r="U249" t="n">
+        <v>2</v>
+      </c>
+      <c r="V249" t="n">
+        <v>0</v>
+      </c>
+      <c r="W249" t="n">
+        <v>2</v>
+      </c>
+      <c r="X249" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -28797,6 +28797,117 @@
       <c r="A250" s="1" t="n">
         <v>46254</v>
       </c>
+      <c r="B250" t="n">
+        <v>14080845.03621005</v>
+      </c>
+      <c r="C250" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" t="n">
+        <v>81</v>
+      </c>
+      <c r="G250" t="n">
+        <v>4</v>
+      </c>
+      <c r="H250" t="n">
+        <v>2</v>
+      </c>
+      <c r="I250" t="n">
+        <v>15</v>
+      </c>
+      <c r="J250" t="n">
+        <v>6</v>
+      </c>
+      <c r="K250" t="n">
+        <v>1</v>
+      </c>
+      <c r="L250" t="n">
+        <v>2</v>
+      </c>
+      <c r="M250" t="n">
+        <v>3</v>
+      </c>
+      <c r="N250" t="n">
+        <v>2</v>
+      </c>
+      <c r="O250" t="n">
+        <v>2</v>
+      </c>
+      <c r="P250" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>7</v>
+      </c>
+      <c r="R250" t="n">
+        <v>1</v>
+      </c>
+      <c r="S250" t="n">
+        <v>7</v>
+      </c>
+      <c r="T250" t="n">
+        <v>9</v>
+      </c>
+      <c r="U250" t="n">
+        <v>2</v>
+      </c>
+      <c r="V250" t="n">
+        <v>0</v>
+      </c>
+      <c r="W250" t="n">
+        <v>2</v>
+      </c>
+      <c r="X250" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -28913,6 +28913,117 @@
       <c r="A251" s="1" t="n">
         <v>46255</v>
       </c>
+      <c r="B251" t="n">
+        <v>14139932.97621005</v>
+      </c>
+      <c r="C251" t="n">
+        <v>1</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" t="n">
+        <v>80</v>
+      </c>
+      <c r="G251" t="n">
+        <v>4</v>
+      </c>
+      <c r="H251" t="n">
+        <v>2</v>
+      </c>
+      <c r="I251" t="n">
+        <v>15</v>
+      </c>
+      <c r="J251" t="n">
+        <v>6</v>
+      </c>
+      <c r="K251" t="n">
+        <v>1</v>
+      </c>
+      <c r="L251" t="n">
+        <v>2</v>
+      </c>
+      <c r="M251" t="n">
+        <v>3</v>
+      </c>
+      <c r="N251" t="n">
+        <v>2</v>
+      </c>
+      <c r="O251" t="n">
+        <v>2</v>
+      </c>
+      <c r="P251" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>7</v>
+      </c>
+      <c r="R251" t="n">
+        <v>1</v>
+      </c>
+      <c r="S251" t="n">
+        <v>7</v>
+      </c>
+      <c r="T251" t="n">
+        <v>9</v>
+      </c>
+      <c r="U251" t="n">
+        <v>2</v>
+      </c>
+      <c r="V251" t="n">
+        <v>0</v>
+      </c>
+      <c r="W251" t="n">
+        <v>2</v>
+      </c>
+      <c r="X251" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -29029,6 +29029,117 @@
       <c r="A252" s="1" t="n">
         <v>46258</v>
       </c>
+      <c r="B252" t="n">
+        <v>14242563.33621005</v>
+      </c>
+      <c r="C252" t="n">
+        <v>1</v>
+      </c>
+      <c r="D252" t="n">
+        <v>1</v>
+      </c>
+      <c r="E252" t="n">
+        <v>1</v>
+      </c>
+      <c r="F252" t="n">
+        <v>81</v>
+      </c>
+      <c r="G252" t="n">
+        <v>4</v>
+      </c>
+      <c r="H252" t="n">
+        <v>2</v>
+      </c>
+      <c r="I252" t="n">
+        <v>15</v>
+      </c>
+      <c r="J252" t="n">
+        <v>5</v>
+      </c>
+      <c r="K252" t="n">
+        <v>1</v>
+      </c>
+      <c r="L252" t="n">
+        <v>2</v>
+      </c>
+      <c r="M252" t="n">
+        <v>3</v>
+      </c>
+      <c r="N252" t="n">
+        <v>2</v>
+      </c>
+      <c r="O252" t="n">
+        <v>2</v>
+      </c>
+      <c r="P252" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>7</v>
+      </c>
+      <c r="R252" t="n">
+        <v>1</v>
+      </c>
+      <c r="S252" t="n">
+        <v>7</v>
+      </c>
+      <c r="T252" t="n">
+        <v>9</v>
+      </c>
+      <c r="U252" t="n">
+        <v>2</v>
+      </c>
+      <c r="V252" t="n">
+        <v>0</v>
+      </c>
+      <c r="W252" t="n">
+        <v>2</v>
+      </c>
+      <c r="X252" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -29145,6 +29145,117 @@
       <c r="A253" s="1" t="n">
         <v>46259</v>
       </c>
+      <c r="B253" t="n">
+        <v>14154121.60871005</v>
+      </c>
+      <c r="C253" t="n">
+        <v>1</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1</v>
+      </c>
+      <c r="F253" t="n">
+        <v>82</v>
+      </c>
+      <c r="G253" t="n">
+        <v>4</v>
+      </c>
+      <c r="H253" t="n">
+        <v>2</v>
+      </c>
+      <c r="I253" t="n">
+        <v>15</v>
+      </c>
+      <c r="J253" t="n">
+        <v>6</v>
+      </c>
+      <c r="K253" t="n">
+        <v>1</v>
+      </c>
+      <c r="L253" t="n">
+        <v>2</v>
+      </c>
+      <c r="M253" t="n">
+        <v>3</v>
+      </c>
+      <c r="N253" t="n">
+        <v>2</v>
+      </c>
+      <c r="O253" t="n">
+        <v>2</v>
+      </c>
+      <c r="P253" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q253" t="n">
+        <v>7</v>
+      </c>
+      <c r="R253" t="n">
+        <v>1</v>
+      </c>
+      <c r="S253" t="n">
+        <v>8</v>
+      </c>
+      <c r="T253" t="n">
+        <v>10</v>
+      </c>
+      <c r="U253" t="n">
+        <v>2</v>
+      </c>
+      <c r="V253" t="n">
+        <v>0</v>
+      </c>
+      <c r="W253" t="n">
+        <v>2</v>
+      </c>
+      <c r="X253" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -29261,6 +29261,117 @@
       <c r="A254" s="1" t="n">
         <v>46260</v>
       </c>
+      <c r="B254" t="n">
+        <v>14085786.44371005</v>
+      </c>
+      <c r="C254" t="n">
+        <v>1</v>
+      </c>
+      <c r="D254" t="n">
+        <v>1</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" t="n">
+        <v>83</v>
+      </c>
+      <c r="G254" t="n">
+        <v>4</v>
+      </c>
+      <c r="H254" t="n">
+        <v>2</v>
+      </c>
+      <c r="I254" t="n">
+        <v>16</v>
+      </c>
+      <c r="J254" t="n">
+        <v>6</v>
+      </c>
+      <c r="K254" t="n">
+        <v>1</v>
+      </c>
+      <c r="L254" t="n">
+        <v>2</v>
+      </c>
+      <c r="M254" t="n">
+        <v>3</v>
+      </c>
+      <c r="N254" t="n">
+        <v>3</v>
+      </c>
+      <c r="O254" t="n">
+        <v>2</v>
+      </c>
+      <c r="P254" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q254" t="n">
+        <v>7</v>
+      </c>
+      <c r="R254" t="n">
+        <v>1</v>
+      </c>
+      <c r="S254" t="n">
+        <v>8</v>
+      </c>
+      <c r="T254" t="n">
+        <v>11</v>
+      </c>
+      <c r="U254" t="n">
+        <v>2</v>
+      </c>
+      <c r="V254" t="n">
+        <v>0</v>
+      </c>
+      <c r="W254" t="n">
+        <v>2</v>
+      </c>
+      <c r="X254" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL254" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -29377,6 +29377,117 @@
       <c r="A255" s="1" t="n">
         <v>46261</v>
       </c>
+      <c r="B255" t="n">
+        <v>14053840.37371005</v>
+      </c>
+      <c r="C255" t="n">
+        <v>1</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1</v>
+      </c>
+      <c r="E255" t="n">
+        <v>1</v>
+      </c>
+      <c r="F255" t="n">
+        <v>83</v>
+      </c>
+      <c r="G255" t="n">
+        <v>4</v>
+      </c>
+      <c r="H255" t="n">
+        <v>2</v>
+      </c>
+      <c r="I255" t="n">
+        <v>16</v>
+      </c>
+      <c r="J255" t="n">
+        <v>6</v>
+      </c>
+      <c r="K255" t="n">
+        <v>1</v>
+      </c>
+      <c r="L255" t="n">
+        <v>2</v>
+      </c>
+      <c r="M255" t="n">
+        <v>3</v>
+      </c>
+      <c r="N255" t="n">
+        <v>3</v>
+      </c>
+      <c r="O255" t="n">
+        <v>2</v>
+      </c>
+      <c r="P255" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q255" t="n">
+        <v>7</v>
+      </c>
+      <c r="R255" t="n">
+        <v>1</v>
+      </c>
+      <c r="S255" t="n">
+        <v>8</v>
+      </c>
+      <c r="T255" t="n">
+        <v>11</v>
+      </c>
+      <c r="U255" t="n">
+        <v>2</v>
+      </c>
+      <c r="V255" t="n">
+        <v>0</v>
+      </c>
+      <c r="W255" t="n">
+        <v>2</v>
+      </c>
+      <c r="X255" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -29493,6 +29493,117 @@
       <c r="A256" s="1" t="n">
         <v>46262</v>
       </c>
+      <c r="B256" t="n">
+        <v>14174955.37371005</v>
+      </c>
+      <c r="C256" t="n">
+        <v>1</v>
+      </c>
+      <c r="D256" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" t="n">
+        <v>83</v>
+      </c>
+      <c r="G256" t="n">
+        <v>4</v>
+      </c>
+      <c r="H256" t="n">
+        <v>2</v>
+      </c>
+      <c r="I256" t="n">
+        <v>16</v>
+      </c>
+      <c r="J256" t="n">
+        <v>6</v>
+      </c>
+      <c r="K256" t="n">
+        <v>1</v>
+      </c>
+      <c r="L256" t="n">
+        <v>2</v>
+      </c>
+      <c r="M256" t="n">
+        <v>3</v>
+      </c>
+      <c r="N256" t="n">
+        <v>3</v>
+      </c>
+      <c r="O256" t="n">
+        <v>2</v>
+      </c>
+      <c r="P256" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q256" t="n">
+        <v>7</v>
+      </c>
+      <c r="R256" t="n">
+        <v>1</v>
+      </c>
+      <c r="S256" t="n">
+        <v>8</v>
+      </c>
+      <c r="T256" t="n">
+        <v>11</v>
+      </c>
+      <c r="U256" t="n">
+        <v>2</v>
+      </c>
+      <c r="V256" t="n">
+        <v>0</v>
+      </c>
+      <c r="W256" t="n">
+        <v>2</v>
+      </c>
+      <c r="X256" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -29515,7 +29515,7 @@
         <v>2</v>
       </c>
       <c r="I256" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J256" t="n">
         <v>6</v>
@@ -29539,13 +29539,13 @@
         <v>3</v>
       </c>
       <c r="Q256" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R256" t="n">
         <v>1</v>
       </c>
       <c r="S256" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T256" t="n">
         <v>11</v>

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -29609,6 +29609,117 @@
       <c r="A257" s="1" t="n">
         <v>46265</v>
       </c>
+      <c r="B257" t="n">
+        <v>14174955.37371005</v>
+      </c>
+      <c r="C257" t="n">
+        <v>1</v>
+      </c>
+      <c r="D257" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1</v>
+      </c>
+      <c r="F257" t="n">
+        <v>83</v>
+      </c>
+      <c r="G257" t="n">
+        <v>4</v>
+      </c>
+      <c r="H257" t="n">
+        <v>2</v>
+      </c>
+      <c r="I257" t="n">
+        <v>17</v>
+      </c>
+      <c r="J257" t="n">
+        <v>6</v>
+      </c>
+      <c r="K257" t="n">
+        <v>1</v>
+      </c>
+      <c r="L257" t="n">
+        <v>2</v>
+      </c>
+      <c r="M257" t="n">
+        <v>3</v>
+      </c>
+      <c r="N257" t="n">
+        <v>3</v>
+      </c>
+      <c r="O257" t="n">
+        <v>2</v>
+      </c>
+      <c r="P257" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>8</v>
+      </c>
+      <c r="R257" t="n">
+        <v>1</v>
+      </c>
+      <c r="S257" t="n">
+        <v>9</v>
+      </c>
+      <c r="T257" t="n">
+        <v>11</v>
+      </c>
+      <c r="U257" t="n">
+        <v>2</v>
+      </c>
+      <c r="V257" t="n">
+        <v>0</v>
+      </c>
+      <c r="W257" t="n">
+        <v>2</v>
+      </c>
+      <c r="X257" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -29725,6 +29725,117 @@
       <c r="A258" s="1" t="n">
         <v>46266</v>
       </c>
+      <c r="B258" t="n">
+        <v>14155878.00831005</v>
+      </c>
+      <c r="C258" t="n">
+        <v>1</v>
+      </c>
+      <c r="D258" t="n">
+        <v>1</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1</v>
+      </c>
+      <c r="F258" t="n">
+        <v>77</v>
+      </c>
+      <c r="G258" t="n">
+        <v>4</v>
+      </c>
+      <c r="H258" t="n">
+        <v>2</v>
+      </c>
+      <c r="I258" t="n">
+        <v>16</v>
+      </c>
+      <c r="J258" t="n">
+        <v>6</v>
+      </c>
+      <c r="K258" t="n">
+        <v>1</v>
+      </c>
+      <c r="L258" t="n">
+        <v>2</v>
+      </c>
+      <c r="M258" t="n">
+        <v>3</v>
+      </c>
+      <c r="N258" t="n">
+        <v>3</v>
+      </c>
+      <c r="O258" t="n">
+        <v>2</v>
+      </c>
+      <c r="P258" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>8</v>
+      </c>
+      <c r="R258" t="n">
+        <v>1</v>
+      </c>
+      <c r="S258" t="n">
+        <v>8</v>
+      </c>
+      <c r="T258" t="n">
+        <v>11</v>
+      </c>
+      <c r="U258" t="n">
+        <v>2</v>
+      </c>
+      <c r="V258" t="n">
+        <v>0</v>
+      </c>
+      <c r="W258" t="n">
+        <v>2</v>
+      </c>
+      <c r="X258" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -29841,6 +29841,117 @@
       <c r="A259" s="1" t="n">
         <v>46267</v>
       </c>
+      <c r="B259" t="n">
+        <v>14203421.89831005</v>
+      </c>
+      <c r="C259" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1</v>
+      </c>
+      <c r="F259" t="n">
+        <v>78</v>
+      </c>
+      <c r="G259" t="n">
+        <v>4</v>
+      </c>
+      <c r="H259" t="n">
+        <v>2</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>6</v>
+      </c>
+      <c r="K259" t="n">
+        <v>1</v>
+      </c>
+      <c r="L259" t="n">
+        <v>2</v>
+      </c>
+      <c r="M259" t="n">
+        <v>3</v>
+      </c>
+      <c r="N259" t="n">
+        <v>3</v>
+      </c>
+      <c r="O259" t="n">
+        <v>2</v>
+      </c>
+      <c r="P259" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>8</v>
+      </c>
+      <c r="R259" t="n">
+        <v>1</v>
+      </c>
+      <c r="S259" t="n">
+        <v>8</v>
+      </c>
+      <c r="T259" t="n">
+        <v>10</v>
+      </c>
+      <c r="U259" t="n">
+        <v>2</v>
+      </c>
+      <c r="V259" t="n">
+        <v>0</v>
+      </c>
+      <c r="W259" t="n">
+        <v>2</v>
+      </c>
+      <c r="X259" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -29957,6 +29957,117 @@
       <c r="A260" s="1" t="n">
         <v>46268</v>
       </c>
+      <c r="B260" t="n">
+        <v>14068898.16361004</v>
+      </c>
+      <c r="C260" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" t="n">
+        <v>80</v>
+      </c>
+      <c r="G260" t="n">
+        <v>4</v>
+      </c>
+      <c r="H260" t="n">
+        <v>2</v>
+      </c>
+      <c r="I260" t="n">
+        <v>17</v>
+      </c>
+      <c r="J260" t="n">
+        <v>7</v>
+      </c>
+      <c r="K260" t="n">
+        <v>1</v>
+      </c>
+      <c r="L260" t="n">
+        <v>2</v>
+      </c>
+      <c r="M260" t="n">
+        <v>3</v>
+      </c>
+      <c r="N260" t="n">
+        <v>3</v>
+      </c>
+      <c r="O260" t="n">
+        <v>2</v>
+      </c>
+      <c r="P260" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>8</v>
+      </c>
+      <c r="R260" t="n">
+        <v>1</v>
+      </c>
+      <c r="S260" t="n">
+        <v>8</v>
+      </c>
+      <c r="T260" t="n">
+        <v>11</v>
+      </c>
+      <c r="U260" t="n">
+        <v>2</v>
+      </c>
+      <c r="V260" t="n">
+        <v>0</v>
+      </c>
+      <c r="W260" t="n">
+        <v>2</v>
+      </c>
+      <c r="X260" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -30073,6 +30073,117 @@
       <c r="A261" s="1" t="n">
         <v>46269</v>
       </c>
+      <c r="B261" t="n">
+        <v>14267963.53201005</v>
+      </c>
+      <c r="C261" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1</v>
+      </c>
+      <c r="F261" t="n">
+        <v>78</v>
+      </c>
+      <c r="G261" t="n">
+        <v>4</v>
+      </c>
+      <c r="H261" t="n">
+        <v>2</v>
+      </c>
+      <c r="I261" t="n">
+        <v>17</v>
+      </c>
+      <c r="J261" t="n">
+        <v>7</v>
+      </c>
+      <c r="K261" t="n">
+        <v>1</v>
+      </c>
+      <c r="L261" t="n">
+        <v>2</v>
+      </c>
+      <c r="M261" t="n">
+        <v>3</v>
+      </c>
+      <c r="N261" t="n">
+        <v>3</v>
+      </c>
+      <c r="O261" t="n">
+        <v>2</v>
+      </c>
+      <c r="P261" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>8</v>
+      </c>
+      <c r="R261" t="n">
+        <v>1</v>
+      </c>
+      <c r="S261" t="n">
+        <v>9</v>
+      </c>
+      <c r="T261" t="n">
+        <v>11</v>
+      </c>
+      <c r="U261" t="n">
+        <v>2</v>
+      </c>
+      <c r="V261" t="n">
+        <v>0</v>
+      </c>
+      <c r="W261" t="n">
+        <v>2</v>
+      </c>
+      <c r="X261" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -30189,6 +30189,117 @@
       <c r="A262" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="B262" t="n">
+        <v>14246318.21831005</v>
+      </c>
+      <c r="C262" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1</v>
+      </c>
+      <c r="F262" t="n">
+        <v>78</v>
+      </c>
+      <c r="G262" t="n">
+        <v>4</v>
+      </c>
+      <c r="H262" t="n">
+        <v>2</v>
+      </c>
+      <c r="I262" t="n">
+        <v>18</v>
+      </c>
+      <c r="J262" t="n">
+        <v>7</v>
+      </c>
+      <c r="K262" t="n">
+        <v>1</v>
+      </c>
+      <c r="L262" t="n">
+        <v>2</v>
+      </c>
+      <c r="M262" t="n">
+        <v>3</v>
+      </c>
+      <c r="N262" t="n">
+        <v>3</v>
+      </c>
+      <c r="O262" t="n">
+        <v>2</v>
+      </c>
+      <c r="P262" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>8</v>
+      </c>
+      <c r="R262" t="n">
+        <v>1</v>
+      </c>
+      <c r="S262" t="n">
+        <v>9</v>
+      </c>
+      <c r="T262" t="n">
+        <v>11</v>
+      </c>
+      <c r="U262" t="n">
+        <v>2</v>
+      </c>
+      <c r="V262" t="n">
+        <v>0</v>
+      </c>
+      <c r="W262" t="n">
+        <v>2</v>
+      </c>
+      <c r="X262" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -30305,6 +30305,117 @@
       <c r="A263" s="1" t="n">
         <v>46273</v>
       </c>
+      <c r="B263" t="n">
+        <v>14333233.05831005</v>
+      </c>
+      <c r="C263" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1</v>
+      </c>
+      <c r="F263" t="n">
+        <v>77</v>
+      </c>
+      <c r="G263" t="n">
+        <v>4</v>
+      </c>
+      <c r="H263" t="n">
+        <v>2</v>
+      </c>
+      <c r="I263" t="n">
+        <v>18</v>
+      </c>
+      <c r="J263" t="n">
+        <v>7</v>
+      </c>
+      <c r="K263" t="n">
+        <v>1</v>
+      </c>
+      <c r="L263" t="n">
+        <v>2</v>
+      </c>
+      <c r="M263" t="n">
+        <v>3</v>
+      </c>
+      <c r="N263" t="n">
+        <v>3</v>
+      </c>
+      <c r="O263" t="n">
+        <v>2</v>
+      </c>
+      <c r="P263" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>8</v>
+      </c>
+      <c r="R263" t="n">
+        <v>1</v>
+      </c>
+      <c r="S263" t="n">
+        <v>9</v>
+      </c>
+      <c r="T263" t="n">
+        <v>12</v>
+      </c>
+      <c r="U263" t="n">
+        <v>2</v>
+      </c>
+      <c r="V263" t="n">
+        <v>0</v>
+      </c>
+      <c r="W263" t="n">
+        <v>2</v>
+      </c>
+      <c r="X263" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -30421,6 +30421,117 @@
       <c r="A264" s="1" t="n">
         <v>46274</v>
       </c>
+      <c r="B264" t="n">
+        <v>14377446.55831005</v>
+      </c>
+      <c r="C264" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" t="n">
+        <v>1</v>
+      </c>
+      <c r="F264" t="n">
+        <v>77</v>
+      </c>
+      <c r="G264" t="n">
+        <v>4</v>
+      </c>
+      <c r="H264" t="n">
+        <v>2</v>
+      </c>
+      <c r="I264" t="n">
+        <v>18</v>
+      </c>
+      <c r="J264" t="n">
+        <v>7</v>
+      </c>
+      <c r="K264" t="n">
+        <v>1</v>
+      </c>
+      <c r="L264" t="n">
+        <v>3</v>
+      </c>
+      <c r="M264" t="n">
+        <v>3</v>
+      </c>
+      <c r="N264" t="n">
+        <v>3</v>
+      </c>
+      <c r="O264" t="n">
+        <v>2</v>
+      </c>
+      <c r="P264" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>9</v>
+      </c>
+      <c r="R264" t="n">
+        <v>1</v>
+      </c>
+      <c r="S264" t="n">
+        <v>9</v>
+      </c>
+      <c r="T264" t="n">
+        <v>12</v>
+      </c>
+      <c r="U264" t="n">
+        <v>0</v>
+      </c>
+      <c r="V264" t="n">
+        <v>0</v>
+      </c>
+      <c r="W264" t="n">
+        <v>2</v>
+      </c>
+      <c r="X264" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL264" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -30537,6 +30537,117 @@
       <c r="A265" s="1" t="n">
         <v>46275</v>
       </c>
+      <c r="B265" t="n">
+        <v>14406141.63521005</v>
+      </c>
+      <c r="C265" t="n">
+        <v>1</v>
+      </c>
+      <c r="D265" t="n">
+        <v>1</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1</v>
+      </c>
+      <c r="F265" t="n">
+        <v>79</v>
+      </c>
+      <c r="G265" t="n">
+        <v>4</v>
+      </c>
+      <c r="H265" t="n">
+        <v>2</v>
+      </c>
+      <c r="I265" t="n">
+        <v>20</v>
+      </c>
+      <c r="J265" t="n">
+        <v>7</v>
+      </c>
+      <c r="K265" t="n">
+        <v>1</v>
+      </c>
+      <c r="L265" t="n">
+        <v>3</v>
+      </c>
+      <c r="M265" t="n">
+        <v>3</v>
+      </c>
+      <c r="N265" t="n">
+        <v>3</v>
+      </c>
+      <c r="O265" t="n">
+        <v>2</v>
+      </c>
+      <c r="P265" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>9</v>
+      </c>
+      <c r="R265" t="n">
+        <v>1</v>
+      </c>
+      <c r="S265" t="n">
+        <v>10</v>
+      </c>
+      <c r="T265" t="n">
+        <v>13</v>
+      </c>
+      <c r="U265" t="n">
+        <v>2</v>
+      </c>
+      <c r="V265" t="n">
+        <v>0</v>
+      </c>
+      <c r="W265" t="n">
+        <v>2</v>
+      </c>
+      <c r="X265" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -30653,6 +30653,117 @@
       <c r="A266" s="1" t="n">
         <v>46276</v>
       </c>
+      <c r="B266" t="n">
+        <v>14435093.67741005</v>
+      </c>
+      <c r="C266" t="n">
+        <v>1</v>
+      </c>
+      <c r="D266" t="n">
+        <v>1</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1</v>
+      </c>
+      <c r="F266" t="n">
+        <v>76</v>
+      </c>
+      <c r="G266" t="n">
+        <v>4</v>
+      </c>
+      <c r="H266" t="n">
+        <v>2</v>
+      </c>
+      <c r="I266" t="n">
+        <v>22</v>
+      </c>
+      <c r="J266" t="n">
+        <v>8</v>
+      </c>
+      <c r="K266" t="n">
+        <v>1</v>
+      </c>
+      <c r="L266" t="n">
+        <v>3</v>
+      </c>
+      <c r="M266" t="n">
+        <v>4</v>
+      </c>
+      <c r="N266" t="n">
+        <v>4</v>
+      </c>
+      <c r="O266" t="n">
+        <v>3</v>
+      </c>
+      <c r="P266" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>10</v>
+      </c>
+      <c r="R266" t="n">
+        <v>2</v>
+      </c>
+      <c r="S266" t="n">
+        <v>10</v>
+      </c>
+      <c r="T266" t="n">
+        <v>14</v>
+      </c>
+      <c r="U266" t="n">
+        <v>3</v>
+      </c>
+      <c r="V266" t="n">
+        <v>0</v>
+      </c>
+      <c r="W266" t="n">
+        <v>3</v>
+      </c>
+      <c r="X266" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">

--- a/kuaiqi.xlsx
+++ b/kuaiqi.xlsx
@@ -30769,6 +30769,117 @@
       <c r="A267" s="1" t="n">
         <v>46279</v>
       </c>
+      <c r="B267" t="n">
+        <v>14258681.91071005</v>
+      </c>
+      <c r="C267" t="n">
+        <v>1</v>
+      </c>
+      <c r="D267" t="n">
+        <v>1</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1</v>
+      </c>
+      <c r="F267" t="n">
+        <v>76</v>
+      </c>
+      <c r="G267" t="n">
+        <v>4</v>
+      </c>
+      <c r="H267" t="n">
+        <v>2</v>
+      </c>
+      <c r="I267" t="n">
+        <v>23</v>
+      </c>
+      <c r="J267" t="n">
+        <v>9</v>
+      </c>
+      <c r="K267" t="n">
+        <v>1</v>
+      </c>
+      <c r="L267" t="n">
+        <v>3</v>
+      </c>
+      <c r="M267" t="n">
+        <v>4</v>
+      </c>
+      <c r="N267" t="n">
+        <v>4</v>
+      </c>
+      <c r="O267" t="n">
+        <v>3</v>
+      </c>
+      <c r="P267" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>10</v>
+      </c>
+      <c r="R267" t="n">
+        <v>2</v>
+      </c>
+      <c r="S267" t="n">
+        <v>11</v>
+      </c>
+      <c r="T267" t="n">
+        <v>15</v>
+      </c>
+      <c r="U267" t="n">
+        <v>3</v>
+      </c>
+      <c r="V267" t="n">
+        <v>0</v>
+      </c>
+      <c r="W267" t="n">
+        <v>3</v>
+      </c>
+      <c r="X267" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
